--- a/stored_files/templates/DAINESE/DAINESE_TC_NHAP_CPN_template.xlsx
+++ b/stored_files/templates/DAINESE/DAINESE_TC_NHAP_CPN_template.xlsx
@@ -1862,7 +1862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HU224"/>
+  <dimension ref="A1:HU203"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.08984375" defaultRowHeight="15.5"/>
   <cols>
     <col width="5.36328125" customWidth="1" style="15" min="1" max="1"/>
@@ -2609,34 +2609,79 @@
       <c r="H14" s="56" t="n"/>
       <c r="I14" s="57" t="n"/>
       <c r="J14" s="125" t="n"/>
-      <c r="K14" s="126" t="n"/>
-      <c r="L14" s="59" t="n"/>
-      <c r="M14" s="60" t="n"/>
-      <c r="N14" s="57" t="n"/>
-      <c r="O14" s="59" t="n"/>
-      <c r="P14" s="57" t="n"/>
-      <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="57" t="n"/>
-      <c r="S14" s="57" t="n"/>
-      <c r="T14" s="57" t="n"/>
-      <c r="U14" s="57" t="n"/>
-      <c r="V14" s="57" t="n"/>
+      <c r="K14" s="126">
+        <f>SUM(K13:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="59">
+        <f>SUM(L13:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="60">
+        <f>SUM(M13:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="57">
+        <f>SUM(N13:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="59">
+        <f>SUM(O13:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="57">
+        <f>SUM(P13:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="57">
+        <f>SUM(Q13:Q13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="57">
+        <f>SUM(R13:R13)</f>
+        <v/>
+      </c>
+      <c r="S14" s="57">
+        <f>SUM(S13:S13)</f>
+        <v/>
+      </c>
+      <c r="T14" s="57">
+        <f>SUM(T13:T13)</f>
+        <v/>
+      </c>
+      <c r="U14" s="57">
+        <f>SUM(U13:U13)</f>
+        <v/>
+      </c>
+      <c r="V14" s="57">
+        <f>SUM(V13:V13)</f>
+        <v/>
+      </c>
       <c r="W14" s="57">
-        <f>SUM(K14:U14)</f>
+        <f>SUM(W13:W13)</f>
         <v/>
       </c>
-      <c r="X14" s="57" t="n"/>
-      <c r="Y14" s="57" t="n"/>
-      <c r="Z14" s="59" t="n"/>
+      <c r="X14" s="57">
+        <f>SUM(X13:X13)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="57">
+        <f>SUM(Y13:Y13)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="59">
+        <f>SUM(Z13:Z13)</f>
+        <v/>
+      </c>
       <c r="AA14" s="57">
-        <f>SUM(X14:Z14)</f>
+        <f>SUM(AA13:AA13)</f>
         <v/>
       </c>
       <c r="AB14" s="57">
-        <f>+W14+AA14</f>
+        <f>SUM(AB13:AB13)</f>
         <v/>
       </c>
-      <c r="AC14" s="56" t="n"/>
+      <c r="AC14" s="63" t="n"/>
       <c r="AD14" s="149" t="n"/>
       <c r="AE14" s="119" t="n"/>
       <c r="AF14" s="119" t="n"/>
@@ -2862,18 +2907,18 @@
       <c r="U15" s="57" t="n"/>
       <c r="V15" s="57" t="n"/>
       <c r="W15" s="57">
-        <f>SUM(K15:U15)</f>
+        <f>SUM(K36:U36)</f>
         <v/>
       </c>
       <c r="X15" s="57" t="n"/>
       <c r="Y15" s="57" t="n"/>
       <c r="Z15" s="59" t="n"/>
       <c r="AA15" s="57">
-        <f>SUM(X15:Z15)</f>
+        <f>SUM(X36:Z36)</f>
         <v/>
       </c>
       <c r="AB15" s="57">
-        <f>+W15+AA15</f>
+        <f>+W36+AA36</f>
         <v/>
       </c>
       <c r="AC15" s="56" t="n"/>
@@ -3090,7 +3135,7 @@
       <c r="I16" s="57" t="n"/>
       <c r="J16" s="125" t="n"/>
       <c r="K16" s="126" t="n"/>
-      <c r="L16" s="126" t="n"/>
+      <c r="L16" s="59" t="n"/>
       <c r="M16" s="60" t="n"/>
       <c r="N16" s="57" t="n"/>
       <c r="O16" s="59" t="n"/>
@@ -3102,21 +3147,21 @@
       <c r="U16" s="57" t="n"/>
       <c r="V16" s="57" t="n"/>
       <c r="W16" s="57">
-        <f>SUM(K16:U16)</f>
+        <f>SUM(K37:U37)</f>
         <v/>
       </c>
       <c r="X16" s="57" t="n"/>
       <c r="Y16" s="57" t="n"/>
-      <c r="Z16" s="60" t="n"/>
+      <c r="Z16" s="59" t="n"/>
       <c r="AA16" s="57">
-        <f>SUM(X16:Z16)</f>
+        <f>SUM(X37:Z37)</f>
         <v/>
       </c>
       <c r="AB16" s="57">
-        <f>+W16+AA16</f>
+        <f>+W37+AA37</f>
         <v/>
       </c>
-      <c r="AC16" s="127" t="n"/>
+      <c r="AC16" s="63" t="n"/>
       <c r="AD16" s="149" t="n"/>
       <c r="AE16" s="119" t="n"/>
       <c r="AF16" s="119" t="n"/>
@@ -3330,10 +3375,10 @@
       <c r="I17" s="57" t="n"/>
       <c r="J17" s="125" t="n"/>
       <c r="K17" s="126" t="n"/>
-      <c r="L17" s="126" t="n"/>
+      <c r="L17" s="59" t="n"/>
       <c r="M17" s="60" t="n"/>
       <c r="N17" s="57" t="n"/>
-      <c r="O17" s="126" t="n"/>
+      <c r="O17" s="59" t="n"/>
       <c r="P17" s="57" t="n"/>
       <c r="Q17" s="57" t="n"/>
       <c r="R17" s="57" t="n"/>
@@ -3342,21 +3387,21 @@
       <c r="U17" s="57" t="n"/>
       <c r="V17" s="57" t="n"/>
       <c r="W17" s="57">
-        <f>SUM(K17:U17)</f>
+        <f>SUM(K38:U38)</f>
         <v/>
       </c>
       <c r="X17" s="57" t="n"/>
       <c r="Y17" s="57" t="n"/>
-      <c r="Z17" s="60" t="n"/>
+      <c r="Z17" s="59" t="n"/>
       <c r="AA17" s="57">
-        <f>SUM(X17:Z17)</f>
+        <f>SUM(X38:Z38)</f>
         <v/>
       </c>
       <c r="AB17" s="57">
-        <f>+W17+AA17</f>
+        <f>+W38+AA38</f>
         <v/>
       </c>
-      <c r="AC17" s="127" t="n"/>
+      <c r="AC17" s="63" t="n"/>
       <c r="AD17" s="149" t="n"/>
       <c r="AE17" s="119" t="n"/>
       <c r="AF17" s="119" t="n"/>
@@ -3570,10 +3615,10 @@
       <c r="I18" s="57" t="n"/>
       <c r="J18" s="125" t="n"/>
       <c r="K18" s="126" t="n"/>
-      <c r="L18" s="126" t="n"/>
+      <c r="L18" s="59" t="n"/>
       <c r="M18" s="60" t="n"/>
       <c r="N18" s="57" t="n"/>
-      <c r="O18" s="126" t="n"/>
+      <c r="O18" s="59" t="n"/>
       <c r="P18" s="57" t="n"/>
       <c r="Q18" s="57" t="n"/>
       <c r="R18" s="57" t="n"/>
@@ -3582,21 +3627,21 @@
       <c r="U18" s="57" t="n"/>
       <c r="V18" s="57" t="n"/>
       <c r="W18" s="57">
-        <f>SUM(K18:U18)</f>
+        <f>SUM(K39:U39)</f>
         <v/>
       </c>
       <c r="X18" s="57" t="n"/>
       <c r="Y18" s="57" t="n"/>
       <c r="Z18" s="59" t="n"/>
       <c r="AA18" s="57">
-        <f>SUM(X18:Z18)</f>
+        <f>SUM(X39:Z39)</f>
         <v/>
       </c>
       <c r="AB18" s="57">
-        <f>+W18+AA18</f>
+        <f>+W39+AA39</f>
         <v/>
       </c>
-      <c r="AC18" s="56" t="n"/>
+      <c r="AC18" s="63" t="n"/>
       <c r="AD18" s="149" t="n"/>
       <c r="AE18" s="119" t="n"/>
       <c r="AF18" s="119" t="n"/>
@@ -3810,10 +3855,10 @@
       <c r="I19" s="57" t="n"/>
       <c r="J19" s="125" t="n"/>
       <c r="K19" s="126" t="n"/>
-      <c r="L19" s="126" t="n"/>
+      <c r="L19" s="59" t="n"/>
       <c r="M19" s="60" t="n"/>
       <c r="N19" s="57" t="n"/>
-      <c r="O19" s="126" t="n"/>
+      <c r="O19" s="59" t="n"/>
       <c r="P19" s="57" t="n"/>
       <c r="Q19" s="57" t="n"/>
       <c r="R19" s="57" t="n"/>
@@ -3822,21 +3867,21 @@
       <c r="U19" s="57" t="n"/>
       <c r="V19" s="57" t="n"/>
       <c r="W19" s="57">
-        <f>SUM(K19:U19)</f>
+        <f>SUM(K40:U40)</f>
         <v/>
       </c>
       <c r="X19" s="57" t="n"/>
       <c r="Y19" s="57" t="n"/>
       <c r="Z19" s="59" t="n"/>
       <c r="AA19" s="57">
-        <f>SUM(X19:Z19)</f>
+        <f>SUM(X40:Z40)</f>
         <v/>
       </c>
       <c r="AB19" s="57">
-        <f>+W19+AA19</f>
+        <f>+W40+AA40</f>
         <v/>
       </c>
-      <c r="AC19" s="56" t="n"/>
+      <c r="AC19" s="63" t="n"/>
       <c r="AD19" s="149" t="n"/>
       <c r="AE19" s="119" t="n"/>
       <c r="AF19" s="119" t="n"/>
@@ -4062,21 +4107,21 @@
       <c r="U20" s="57" t="n"/>
       <c r="V20" s="57" t="n"/>
       <c r="W20" s="57">
-        <f>SUM(K20:U20)</f>
+        <f>SUM(K41:U41)</f>
         <v/>
       </c>
       <c r="X20" s="57" t="n"/>
       <c r="Y20" s="57" t="n"/>
       <c r="Z20" s="59" t="n"/>
       <c r="AA20" s="57">
-        <f>SUM(X20:Z20)</f>
+        <f>SUM(X41:Z41)</f>
         <v/>
       </c>
       <c r="AB20" s="57">
-        <f>+W20+AA20</f>
+        <f>+W41+AA41</f>
         <v/>
       </c>
-      <c r="AC20" s="56" t="n"/>
+      <c r="AC20" s="63" t="n"/>
       <c r="AD20" s="149" t="n"/>
       <c r="AE20" s="119" t="n"/>
       <c r="AF20" s="119" t="n"/>
@@ -4302,21 +4347,21 @@
       <c r="U21" s="57" t="n"/>
       <c r="V21" s="57" t="n"/>
       <c r="W21" s="57">
-        <f>SUM(K21:U21)</f>
+        <f>SUM(K42:U42)</f>
         <v/>
       </c>
       <c r="X21" s="57" t="n"/>
       <c r="Y21" s="57" t="n"/>
       <c r="Z21" s="59" t="n"/>
       <c r="AA21" s="57">
-        <f>SUM(X21:Z21)</f>
+        <f>SUM(X42:Z42)</f>
         <v/>
       </c>
       <c r="AB21" s="57">
-        <f>+W21+AA21</f>
+        <f>+W42+AA42</f>
         <v/>
       </c>
-      <c r="AC21" s="56" t="n"/>
+      <c r="AC21" s="63" t="n"/>
       <c r="AD21" s="149" t="n"/>
       <c r="AE21" s="119" t="n"/>
       <c r="AF21" s="119" t="n"/>
@@ -4533,7 +4578,7 @@
       <c r="L22" s="59" t="n"/>
       <c r="M22" s="60" t="n"/>
       <c r="N22" s="57" t="n"/>
-      <c r="O22" s="126" t="n"/>
+      <c r="O22" s="59" t="n"/>
       <c r="P22" s="57" t="n"/>
       <c r="Q22" s="57" t="n"/>
       <c r="R22" s="57" t="n"/>
@@ -4542,21 +4587,21 @@
       <c r="U22" s="57" t="n"/>
       <c r="V22" s="57" t="n"/>
       <c r="W22" s="57">
-        <f>SUM(K22:U22)</f>
+        <f>SUM(K43:U43)</f>
         <v/>
       </c>
       <c r="X22" s="57" t="n"/>
       <c r="Y22" s="57" t="n"/>
       <c r="Z22" s="59" t="n"/>
       <c r="AA22" s="57">
-        <f>SUM(X22:Z22)</f>
+        <f>SUM(X43:Z43)</f>
         <v/>
       </c>
       <c r="AB22" s="57">
-        <f>+W22+AA22</f>
+        <f>+W43+AA43</f>
         <v/>
       </c>
-      <c r="AC22" s="56" t="n"/>
+      <c r="AC22" s="63" t="n"/>
       <c r="AD22" s="149" t="n"/>
       <c r="AE22" s="119" t="n"/>
       <c r="AF22" s="119" t="n"/>
@@ -4773,7 +4818,7 @@
       <c r="L23" s="59" t="n"/>
       <c r="M23" s="60" t="n"/>
       <c r="N23" s="57" t="n"/>
-      <c r="O23" s="126" t="n"/>
+      <c r="O23" s="59" t="n"/>
       <c r="P23" s="57" t="n"/>
       <c r="Q23" s="57" t="n"/>
       <c r="R23" s="57" t="n"/>
@@ -4782,21 +4827,21 @@
       <c r="U23" s="57" t="n"/>
       <c r="V23" s="57" t="n"/>
       <c r="W23" s="57">
-        <f>SUM(K23:U23)</f>
+        <f>SUM(K44:U44)</f>
         <v/>
       </c>
       <c r="X23" s="57" t="n"/>
       <c r="Y23" s="57" t="n"/>
       <c r="Z23" s="59" t="n"/>
       <c r="AA23" s="57">
-        <f>SUM(X23:Z23)</f>
+        <f>SUM(X44:Z44)</f>
         <v/>
       </c>
       <c r="AB23" s="57">
-        <f>+W23+AA23</f>
+        <f>+W44+AA44</f>
         <v/>
       </c>
-      <c r="AC23" s="56" t="n"/>
+      <c r="AC23" s="63" t="n"/>
       <c r="AD23" s="149" t="n"/>
       <c r="AE23" s="119" t="n"/>
       <c r="AF23" s="119" t="n"/>
@@ -5010,10 +5055,10 @@
       <c r="I24" s="57" t="n"/>
       <c r="J24" s="125" t="n"/>
       <c r="K24" s="126" t="n"/>
-      <c r="L24" s="126" t="n"/>
+      <c r="L24" s="59" t="n"/>
       <c r="M24" s="60" t="n"/>
       <c r="N24" s="57" t="n"/>
-      <c r="O24" s="126" t="n"/>
+      <c r="O24" s="59" t="n"/>
       <c r="P24" s="57" t="n"/>
       <c r="Q24" s="57" t="n"/>
       <c r="R24" s="57" t="n"/>
@@ -5022,21 +5067,21 @@
       <c r="U24" s="57" t="n"/>
       <c r="V24" s="57" t="n"/>
       <c r="W24" s="57">
-        <f>SUM(K24:U24)</f>
+        <f>SUM(K45:U45)</f>
         <v/>
       </c>
       <c r="X24" s="57" t="n"/>
       <c r="Y24" s="57" t="n"/>
       <c r="Z24" s="59" t="n"/>
       <c r="AA24" s="57">
-        <f>SUM(X24:Z24)</f>
+        <f>SUM(X45:Z45)</f>
         <v/>
       </c>
       <c r="AB24" s="57">
-        <f>+W24+AA24</f>
+        <f>+W45+AA45</f>
         <v/>
       </c>
-      <c r="AC24" s="56" t="n"/>
+      <c r="AC24" s="63" t="n"/>
       <c r="AD24" s="149" t="n"/>
       <c r="AE24" s="119" t="n"/>
       <c r="AF24" s="119" t="n"/>
@@ -5250,10 +5295,10 @@
       <c r="I25" s="57" t="n"/>
       <c r="J25" s="125" t="n"/>
       <c r="K25" s="126" t="n"/>
-      <c r="L25" s="126" t="n"/>
+      <c r="L25" s="59" t="n"/>
       <c r="M25" s="60" t="n"/>
       <c r="N25" s="57" t="n"/>
-      <c r="O25" s="126" t="n"/>
+      <c r="O25" s="59" t="n"/>
       <c r="P25" s="57" t="n"/>
       <c r="Q25" s="57" t="n"/>
       <c r="R25" s="57" t="n"/>
@@ -5262,21 +5307,27 @@
       <c r="U25" s="57" t="n"/>
       <c r="V25" s="57" t="n"/>
       <c r="W25" s="57">
-        <f>SUM(K25:U25)</f>
+        <f>SUM(K46:U46)</f>
         <v/>
       </c>
       <c r="X25" s="57" t="n"/>
-      <c r="Y25" s="57" t="n"/>
+      <c r="Y25" s="57" t="n">
+        <v>20000</v>
+      </c>
       <c r="Z25" s="59" t="n"/>
       <c r="AA25" s="57">
-        <f>SUM(X25:Z25)</f>
+        <f>SUM(X46:Z46)</f>
         <v/>
       </c>
       <c r="AB25" s="57">
-        <f>+W25+AA25</f>
+        <f>+W46+AA46</f>
         <v/>
       </c>
-      <c r="AC25" s="56" t="n"/>
+      <c r="AC25" s="63" t="inlineStr">
+        <is>
+          <t>0318082</t>
+        </is>
+      </c>
       <c r="AD25" s="149" t="n"/>
       <c r="AE25" s="119" t="n"/>
       <c r="AF25" s="119" t="n"/>
@@ -5490,10 +5541,10 @@
       <c r="I26" s="57" t="n"/>
       <c r="J26" s="125" t="n"/>
       <c r="K26" s="126" t="n"/>
-      <c r="L26" s="126" t="n"/>
+      <c r="L26" s="59" t="n"/>
       <c r="M26" s="60" t="n"/>
       <c r="N26" s="57" t="n"/>
-      <c r="O26" s="126" t="n"/>
+      <c r="O26" s="59" t="n"/>
       <c r="P26" s="57" t="n"/>
       <c r="Q26" s="57" t="n"/>
       <c r="R26" s="57" t="n"/>
@@ -5502,21 +5553,27 @@
       <c r="U26" s="57" t="n"/>
       <c r="V26" s="57" t="n"/>
       <c r="W26" s="57">
-        <f>SUM(K26:U26)</f>
+        <f>SUM(K47:U47)</f>
         <v/>
       </c>
       <c r="X26" s="57" t="n"/>
-      <c r="Y26" s="57" t="n"/>
+      <c r="Y26" s="57" t="n">
+        <v>20000</v>
+      </c>
       <c r="Z26" s="59" t="n"/>
       <c r="AA26" s="57">
-        <f>SUM(X26:Z26)</f>
+        <f>SUM(X47:Z47)</f>
         <v/>
       </c>
       <c r="AB26" s="57">
-        <f>+W26+AA26</f>
+        <f>+W47+AA47</f>
         <v/>
       </c>
-      <c r="AC26" s="56" t="n"/>
+      <c r="AC26" s="63" t="inlineStr">
+        <is>
+          <t>0318092</t>
+        </is>
+      </c>
       <c r="AD26" s="149" t="n"/>
       <c r="AE26" s="119" t="n"/>
       <c r="AF26" s="119" t="n"/>
@@ -5733,7 +5790,7 @@
       <c r="L27" s="59" t="n"/>
       <c r="M27" s="60" t="n"/>
       <c r="N27" s="57" t="n"/>
-      <c r="O27" s="126" t="n"/>
+      <c r="O27" s="59" t="n"/>
       <c r="P27" s="57" t="n"/>
       <c r="Q27" s="57" t="n"/>
       <c r="R27" s="57" t="n"/>
@@ -5742,21 +5799,27 @@
       <c r="U27" s="57" t="n"/>
       <c r="V27" s="57" t="n"/>
       <c r="W27" s="57">
-        <f>SUM(K27:U27)</f>
+        <f>SUM(K48:U48)</f>
         <v/>
       </c>
       <c r="X27" s="57" t="n"/>
-      <c r="Y27" s="57" t="n"/>
+      <c r="Y27" s="57" t="n">
+        <v>20000</v>
+      </c>
       <c r="Z27" s="59" t="n"/>
       <c r="AA27" s="57">
-        <f>SUM(X27:Z27)</f>
+        <f>SUM(X48:Z48)</f>
         <v/>
       </c>
       <c r="AB27" s="57">
-        <f>+W27+AA27</f>
+        <f>+W48+AA48</f>
         <v/>
       </c>
-      <c r="AC27" s="56" t="n"/>
+      <c r="AC27" s="63" t="inlineStr">
+        <is>
+          <t>0318086</t>
+        </is>
+      </c>
       <c r="AD27" s="149" t="n"/>
       <c r="AE27" s="119" t="n"/>
       <c r="AF27" s="119" t="n"/>
@@ -5959,45 +6022,51 @@
       <c r="HU27" s="119" t="n"/>
     </row>
     <row r="28" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A28" s="58" t="n"/>
-      <c r="B28" s="121" t="n"/>
-      <c r="C28" s="122" t="n"/>
-      <c r="D28" s="123" t="n"/>
-      <c r="E28" s="124" t="n"/>
-      <c r="F28" s="55" t="n"/>
-      <c r="G28" s="125" t="n"/>
-      <c r="H28" s="56" t="n"/>
-      <c r="I28" s="57" t="n"/>
-      <c r="J28" s="125" t="n"/>
-      <c r="K28" s="126" t="n"/>
-      <c r="L28" s="59" t="n"/>
-      <c r="M28" s="60" t="n"/>
-      <c r="N28" s="57" t="n"/>
-      <c r="O28" s="59" t="n"/>
-      <c r="P28" s="57" t="n"/>
-      <c r="Q28" s="57" t="n"/>
-      <c r="R28" s="57" t="n"/>
-      <c r="S28" s="57" t="n"/>
-      <c r="T28" s="57" t="n"/>
-      <c r="U28" s="57" t="n"/>
-      <c r="V28" s="57" t="n"/>
-      <c r="W28" s="57">
-        <f>SUM(K28:U28)</f>
+      <c r="A28" s="129" t="n"/>
+      <c r="B28" s="130" t="n"/>
+      <c r="C28" s="131" t="n"/>
+      <c r="D28" s="132" t="n"/>
+      <c r="E28" s="133" t="n"/>
+      <c r="F28" s="134" t="n"/>
+      <c r="G28" s="135" t="n"/>
+      <c r="H28" s="136" t="n"/>
+      <c r="I28" s="137" t="n"/>
+      <c r="J28" s="135" t="n"/>
+      <c r="K28" s="138" t="n"/>
+      <c r="L28" s="139" t="n"/>
+      <c r="M28" s="140" t="n"/>
+      <c r="N28" s="137" t="n"/>
+      <c r="O28" s="139" t="n"/>
+      <c r="P28" s="137" t="n"/>
+      <c r="Q28" s="137" t="n"/>
+      <c r="R28" s="137" t="n"/>
+      <c r="S28" s="137" t="n"/>
+      <c r="T28" s="137" t="n"/>
+      <c r="U28" s="137" t="n"/>
+      <c r="V28" s="137" t="n"/>
+      <c r="W28" s="137">
+        <f>SUM(K49:U49)</f>
         <v/>
       </c>
-      <c r="X28" s="57" t="n"/>
-      <c r="Y28" s="57" t="n"/>
-      <c r="Z28" s="59" t="n"/>
-      <c r="AA28" s="57">
-        <f>SUM(X28:Z28)</f>
+      <c r="X28" s="137" t="n"/>
+      <c r="Y28" s="137" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Z28" s="139" t="n"/>
+      <c r="AA28" s="137">
+        <f>SUM(X49:Z49)</f>
         <v/>
       </c>
-      <c r="AB28" s="57">
-        <f>+W28+AA28</f>
+      <c r="AB28" s="137">
+        <f>+W49+AA49</f>
         <v/>
       </c>
-      <c r="AC28" s="56" t="n"/>
-      <c r="AD28" s="149" t="n"/>
+      <c r="AC28" s="128" t="inlineStr">
+        <is>
+          <t>0318084</t>
+        </is>
+      </c>
+      <c r="AD28" s="150" t="n"/>
       <c r="AE28" s="119" t="n"/>
       <c r="AF28" s="119" t="n"/>
       <c r="AG28" s="119" t="n"/>
@@ -6199,5753 +6268,748 @@
       <c r="HU28" s="119" t="n"/>
     </row>
     <row r="29" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A29" s="58" t="n"/>
-      <c r="B29" s="121" t="n"/>
-      <c r="C29" s="122" t="n"/>
-      <c r="D29" s="123" t="n"/>
-      <c r="E29" s="124" t="n"/>
-      <c r="F29" s="55" t="n"/>
-      <c r="G29" s="125" t="n"/>
-      <c r="H29" s="56" t="n"/>
-      <c r="I29" s="57" t="n"/>
-      <c r="J29" s="125" t="n"/>
-      <c r="K29" s="126" t="n"/>
-      <c r="L29" s="59" t="n"/>
-      <c r="M29" s="60" t="n"/>
-      <c r="N29" s="57" t="n"/>
-      <c r="O29" s="59" t="n"/>
-      <c r="P29" s="57" t="n"/>
-      <c r="Q29" s="57" t="n"/>
-      <c r="R29" s="57" t="n"/>
-      <c r="S29" s="57" t="n"/>
-      <c r="T29" s="57" t="n"/>
-      <c r="U29" s="57" t="n"/>
-      <c r="V29" s="57" t="n"/>
-      <c r="W29" s="57">
-        <f>SUM(K29:U29)</f>
-        <v/>
-      </c>
-      <c r="X29" s="57" t="n"/>
-      <c r="Y29" s="57" t="n"/>
-      <c r="Z29" s="59" t="n"/>
-      <c r="AA29" s="57">
-        <f>SUM(X29:Z29)</f>
-        <v/>
-      </c>
-      <c r="AB29" s="57">
-        <f>+W29+AA29</f>
-        <v/>
-      </c>
-      <c r="AC29" s="56" t="n"/>
-      <c r="AD29" s="149" t="n"/>
-      <c r="AE29" s="119" t="n"/>
-      <c r="AF29" s="119" t="n"/>
-      <c r="AG29" s="119" t="n"/>
-      <c r="AH29" s="119" t="n"/>
-      <c r="AI29" s="119" t="n"/>
-      <c r="AJ29" s="119" t="n"/>
-      <c r="AK29" s="119" t="n"/>
-      <c r="AL29" s="119" t="n"/>
-      <c r="AM29" s="119" t="n"/>
-      <c r="AN29" s="119" t="n"/>
-      <c r="AO29" s="119" t="n"/>
-      <c r="AP29" s="119" t="n"/>
-      <c r="AQ29" s="119" t="n"/>
-      <c r="AR29" s="119" t="n"/>
-      <c r="AS29" s="119" t="n"/>
-      <c r="AT29" s="119" t="n"/>
-      <c r="AU29" s="119" t="n"/>
-      <c r="AV29" s="119" t="n"/>
-      <c r="AW29" s="119" t="n"/>
-      <c r="AX29" s="119" t="n"/>
-      <c r="AY29" s="119" t="n"/>
-      <c r="AZ29" s="119" t="n"/>
-      <c r="BA29" s="119" t="n"/>
-      <c r="BB29" s="119" t="n"/>
-      <c r="BC29" s="119" t="n"/>
-      <c r="BD29" s="119" t="n"/>
-      <c r="BE29" s="119" t="n"/>
-      <c r="BF29" s="119" t="n"/>
-      <c r="BG29" s="119" t="n"/>
-      <c r="BH29" s="119" t="n"/>
-      <c r="BI29" s="119" t="n"/>
-      <c r="BJ29" s="119" t="n"/>
-      <c r="BK29" s="119" t="n"/>
-      <c r="BL29" s="119" t="n"/>
-      <c r="BM29" s="119" t="n"/>
-      <c r="BN29" s="119" t="n"/>
-      <c r="BO29" s="119" t="n"/>
-      <c r="BP29" s="119" t="n"/>
-      <c r="BQ29" s="119" t="n"/>
-      <c r="BR29" s="119" t="n"/>
-      <c r="BS29" s="119" t="n"/>
-      <c r="BT29" s="119" t="n"/>
-      <c r="BU29" s="119" t="n"/>
-      <c r="BV29" s="119" t="n"/>
-      <c r="BW29" s="119" t="n"/>
-      <c r="BX29" s="119" t="n"/>
-      <c r="BY29" s="119" t="n"/>
-      <c r="BZ29" s="119" t="n"/>
-      <c r="CA29" s="119" t="n"/>
-      <c r="CB29" s="119" t="n"/>
-      <c r="CC29" s="119" t="n"/>
-      <c r="CD29" s="119" t="n"/>
-      <c r="CE29" s="119" t="n"/>
-      <c r="CF29" s="119" t="n"/>
-      <c r="CG29" s="119" t="n"/>
-      <c r="CH29" s="119" t="n"/>
-      <c r="CI29" s="119" t="n"/>
-      <c r="CJ29" s="119" t="n"/>
-      <c r="CK29" s="119" t="n"/>
-      <c r="CL29" s="119" t="n"/>
-      <c r="CM29" s="119" t="n"/>
-      <c r="CN29" s="119" t="n"/>
-      <c r="CO29" s="119" t="n"/>
-      <c r="CP29" s="119" t="n"/>
-      <c r="CQ29" s="119" t="n"/>
-      <c r="CR29" s="119" t="n"/>
-      <c r="CS29" s="119" t="n"/>
-      <c r="CT29" s="119" t="n"/>
-      <c r="CU29" s="119" t="n"/>
-      <c r="CV29" s="119" t="n"/>
-      <c r="CW29" s="119" t="n"/>
-      <c r="CX29" s="119" t="n"/>
-      <c r="CY29" s="119" t="n"/>
-      <c r="CZ29" s="119" t="n"/>
-      <c r="DA29" s="119" t="n"/>
-      <c r="DB29" s="119" t="n"/>
-      <c r="DC29" s="119" t="n"/>
-      <c r="DD29" s="119" t="n"/>
-      <c r="DE29" s="119" t="n"/>
-      <c r="DF29" s="119" t="n"/>
-      <c r="DG29" s="119" t="n"/>
-      <c r="DH29" s="119" t="n"/>
-      <c r="DI29" s="119" t="n"/>
-      <c r="DJ29" s="119" t="n"/>
-      <c r="DK29" s="119" t="n"/>
-      <c r="DL29" s="119" t="n"/>
-      <c r="DM29" s="119" t="n"/>
-      <c r="DN29" s="119" t="n"/>
-      <c r="DO29" s="119" t="n"/>
-      <c r="DP29" s="119" t="n"/>
-      <c r="DQ29" s="119" t="n"/>
-      <c r="DR29" s="119" t="n"/>
-      <c r="DS29" s="119" t="n"/>
-      <c r="DT29" s="119" t="n"/>
-      <c r="DU29" s="119" t="n"/>
-      <c r="DV29" s="119" t="n"/>
-      <c r="DW29" s="119" t="n"/>
-      <c r="DX29" s="119" t="n"/>
-      <c r="DY29" s="119" t="n"/>
-      <c r="DZ29" s="119" t="n"/>
-      <c r="EA29" s="119" t="n"/>
-      <c r="EB29" s="119" t="n"/>
-      <c r="EC29" s="119" t="n"/>
-      <c r="ED29" s="119" t="n"/>
-      <c r="EE29" s="119" t="n"/>
-      <c r="EF29" s="119" t="n"/>
-      <c r="EG29" s="119" t="n"/>
-      <c r="EH29" s="119" t="n"/>
-      <c r="EI29" s="119" t="n"/>
-      <c r="EJ29" s="119" t="n"/>
-      <c r="EK29" s="119" t="n"/>
-      <c r="EL29" s="119" t="n"/>
-      <c r="EM29" s="119" t="n"/>
-      <c r="EN29" s="119" t="n"/>
-      <c r="EO29" s="119" t="n"/>
-      <c r="EP29" s="119" t="n"/>
-      <c r="EQ29" s="119" t="n"/>
-      <c r="ER29" s="119" t="n"/>
-      <c r="ES29" s="119" t="n"/>
-      <c r="ET29" s="119" t="n"/>
-      <c r="EU29" s="119" t="n"/>
-      <c r="EV29" s="119" t="n"/>
-      <c r="EW29" s="119" t="n"/>
-      <c r="EX29" s="119" t="n"/>
-      <c r="EY29" s="119" t="n"/>
-      <c r="EZ29" s="119" t="n"/>
-      <c r="FA29" s="119" t="n"/>
-      <c r="FB29" s="119" t="n"/>
-      <c r="FC29" s="119" t="n"/>
-      <c r="FD29" s="119" t="n"/>
-      <c r="FE29" s="119" t="n"/>
-      <c r="FF29" s="119" t="n"/>
-      <c r="FG29" s="119" t="n"/>
-      <c r="FH29" s="119" t="n"/>
-      <c r="FI29" s="119" t="n"/>
-      <c r="FJ29" s="119" t="n"/>
-      <c r="FK29" s="119" t="n"/>
-      <c r="FL29" s="119" t="n"/>
-      <c r="FM29" s="119" t="n"/>
-      <c r="FN29" s="119" t="n"/>
-      <c r="FO29" s="119" t="n"/>
-      <c r="FP29" s="119" t="n"/>
-      <c r="FQ29" s="119" t="n"/>
-      <c r="FR29" s="119" t="n"/>
-      <c r="FS29" s="119" t="n"/>
-      <c r="FT29" s="119" t="n"/>
-      <c r="FU29" s="119" t="n"/>
-      <c r="FV29" s="119" t="n"/>
-      <c r="FW29" s="119" t="n"/>
-      <c r="FX29" s="119" t="n"/>
-      <c r="FY29" s="119" t="n"/>
-      <c r="FZ29" s="119" t="n"/>
-      <c r="GA29" s="119" t="n"/>
-      <c r="GB29" s="119" t="n"/>
-      <c r="GC29" s="119" t="n"/>
-      <c r="GD29" s="119" t="n"/>
-      <c r="GE29" s="119" t="n"/>
-      <c r="GF29" s="119" t="n"/>
-      <c r="GG29" s="119" t="n"/>
-      <c r="GH29" s="119" t="n"/>
-      <c r="GI29" s="119" t="n"/>
-      <c r="GJ29" s="119" t="n"/>
-      <c r="GK29" s="119" t="n"/>
-      <c r="GL29" s="119" t="n"/>
-      <c r="GM29" s="119" t="n"/>
-      <c r="GN29" s="119" t="n"/>
-      <c r="GO29" s="119" t="n"/>
-      <c r="GP29" s="119" t="n"/>
-      <c r="GQ29" s="119" t="n"/>
-      <c r="GR29" s="119" t="n"/>
-      <c r="GS29" s="119" t="n"/>
-      <c r="GT29" s="119" t="n"/>
-      <c r="GU29" s="119" t="n"/>
-      <c r="GV29" s="119" t="n"/>
-      <c r="GW29" s="119" t="n"/>
-      <c r="GX29" s="119" t="n"/>
-      <c r="GY29" s="119" t="n"/>
-      <c r="GZ29" s="119" t="n"/>
-      <c r="HA29" s="119" t="n"/>
-      <c r="HB29" s="119" t="n"/>
-      <c r="HC29" s="119" t="n"/>
-      <c r="HD29" s="119" t="n"/>
-      <c r="HE29" s="119" t="n"/>
-      <c r="HF29" s="119" t="n"/>
-      <c r="HG29" s="119" t="n"/>
-      <c r="HH29" s="119" t="n"/>
-      <c r="HI29" s="119" t="n"/>
-      <c r="HJ29" s="119" t="n"/>
-      <c r="HK29" s="119" t="n"/>
-      <c r="HL29" s="119" t="n"/>
-      <c r="HM29" s="119" t="n"/>
-      <c r="HN29" s="119" t="n"/>
-      <c r="HO29" s="119" t="n"/>
-      <c r="HP29" s="119" t="n"/>
-      <c r="HQ29" s="119" t="n"/>
-      <c r="HR29" s="119" t="n"/>
-      <c r="HS29" s="119" t="n"/>
-      <c r="HT29" s="119" t="n"/>
-      <c r="HU29" s="119" t="n"/>
-    </row>
-    <row r="30" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A30" s="58" t="n"/>
-      <c r="B30" s="121" t="n"/>
-      <c r="C30" s="122" t="n"/>
-      <c r="D30" s="123" t="n"/>
-      <c r="E30" s="124" t="n"/>
-      <c r="F30" s="55" t="n"/>
-      <c r="G30" s="125" t="n"/>
-      <c r="H30" s="56" t="n"/>
-      <c r="I30" s="57" t="n"/>
-      <c r="J30" s="125" t="n"/>
-      <c r="K30" s="126" t="n"/>
-      <c r="L30" s="59" t="n"/>
-      <c r="M30" s="60" t="n"/>
-      <c r="N30" s="57" t="n"/>
-      <c r="O30" s="59" t="n"/>
-      <c r="P30" s="57" t="n"/>
-      <c r="Q30" s="57" t="n"/>
-      <c r="R30" s="57" t="n"/>
-      <c r="S30" s="57" t="n"/>
-      <c r="T30" s="57" t="n"/>
-      <c r="U30" s="57" t="n"/>
-      <c r="V30" s="57" t="n"/>
-      <c r="W30" s="57">
-        <f>SUM(K30:U30)</f>
-        <v/>
-      </c>
-      <c r="X30" s="57" t="n"/>
-      <c r="Y30" s="57" t="n"/>
-      <c r="Z30" s="59" t="n"/>
-      <c r="AA30" s="57">
-        <f>SUM(X30:Z30)</f>
-        <v/>
-      </c>
-      <c r="AB30" s="57">
-        <f>+W30+AA30</f>
-        <v/>
-      </c>
-      <c r="AC30" s="63" t="n"/>
-      <c r="AD30" s="149" t="n"/>
-      <c r="AE30" s="119" t="n"/>
-      <c r="AF30" s="119" t="n"/>
-      <c r="AG30" s="119" t="n"/>
-      <c r="AH30" s="119" t="n"/>
-      <c r="AI30" s="119" t="n"/>
-      <c r="AJ30" s="119" t="n"/>
-      <c r="AK30" s="119" t="n"/>
-      <c r="AL30" s="119" t="n"/>
-      <c r="AM30" s="119" t="n"/>
-      <c r="AN30" s="119" t="n"/>
-      <c r="AO30" s="119" t="n"/>
-      <c r="AP30" s="119" t="n"/>
-      <c r="AQ30" s="119" t="n"/>
-      <c r="AR30" s="119" t="n"/>
-      <c r="AS30" s="119" t="n"/>
-      <c r="AT30" s="119" t="n"/>
-      <c r="AU30" s="119" t="n"/>
-      <c r="AV30" s="119" t="n"/>
-      <c r="AW30" s="119" t="n"/>
-      <c r="AX30" s="119" t="n"/>
-      <c r="AY30" s="119" t="n"/>
-      <c r="AZ30" s="119" t="n"/>
-      <c r="BA30" s="119" t="n"/>
-      <c r="BB30" s="119" t="n"/>
-      <c r="BC30" s="119" t="n"/>
-      <c r="BD30" s="119" t="n"/>
-      <c r="BE30" s="119" t="n"/>
-      <c r="BF30" s="119" t="n"/>
-      <c r="BG30" s="119" t="n"/>
-      <c r="BH30" s="119" t="n"/>
-      <c r="BI30" s="119" t="n"/>
-      <c r="BJ30" s="119" t="n"/>
-      <c r="BK30" s="119" t="n"/>
-      <c r="BL30" s="119" t="n"/>
-      <c r="BM30" s="119" t="n"/>
-      <c r="BN30" s="119" t="n"/>
-      <c r="BO30" s="119" t="n"/>
-      <c r="BP30" s="119" t="n"/>
-      <c r="BQ30" s="119" t="n"/>
-      <c r="BR30" s="119" t="n"/>
-      <c r="BS30" s="119" t="n"/>
-      <c r="BT30" s="119" t="n"/>
-      <c r="BU30" s="119" t="n"/>
-      <c r="BV30" s="119" t="n"/>
-      <c r="BW30" s="119" t="n"/>
-      <c r="BX30" s="119" t="n"/>
-      <c r="BY30" s="119" t="n"/>
-      <c r="BZ30" s="119" t="n"/>
-      <c r="CA30" s="119" t="n"/>
-      <c r="CB30" s="119" t="n"/>
-      <c r="CC30" s="119" t="n"/>
-      <c r="CD30" s="119" t="n"/>
-      <c r="CE30" s="119" t="n"/>
-      <c r="CF30" s="119" t="n"/>
-      <c r="CG30" s="119" t="n"/>
-      <c r="CH30" s="119" t="n"/>
-      <c r="CI30" s="119" t="n"/>
-      <c r="CJ30" s="119" t="n"/>
-      <c r="CK30" s="119" t="n"/>
-      <c r="CL30" s="119" t="n"/>
-      <c r="CM30" s="119" t="n"/>
-      <c r="CN30" s="119" t="n"/>
-      <c r="CO30" s="119" t="n"/>
-      <c r="CP30" s="119" t="n"/>
-      <c r="CQ30" s="119" t="n"/>
-      <c r="CR30" s="119" t="n"/>
-      <c r="CS30" s="119" t="n"/>
-      <c r="CT30" s="119" t="n"/>
-      <c r="CU30" s="119" t="n"/>
-      <c r="CV30" s="119" t="n"/>
-      <c r="CW30" s="119" t="n"/>
-      <c r="CX30" s="119" t="n"/>
-      <c r="CY30" s="119" t="n"/>
-      <c r="CZ30" s="119" t="n"/>
-      <c r="DA30" s="119" t="n"/>
-      <c r="DB30" s="119" t="n"/>
-      <c r="DC30" s="119" t="n"/>
-      <c r="DD30" s="119" t="n"/>
-      <c r="DE30" s="119" t="n"/>
-      <c r="DF30" s="119" t="n"/>
-      <c r="DG30" s="119" t="n"/>
-      <c r="DH30" s="119" t="n"/>
-      <c r="DI30" s="119" t="n"/>
-      <c r="DJ30" s="119" t="n"/>
-      <c r="DK30" s="119" t="n"/>
-      <c r="DL30" s="119" t="n"/>
-      <c r="DM30" s="119" t="n"/>
-      <c r="DN30" s="119" t="n"/>
-      <c r="DO30" s="119" t="n"/>
-      <c r="DP30" s="119" t="n"/>
-      <c r="DQ30" s="119" t="n"/>
-      <c r="DR30" s="119" t="n"/>
-      <c r="DS30" s="119" t="n"/>
-      <c r="DT30" s="119" t="n"/>
-      <c r="DU30" s="119" t="n"/>
-      <c r="DV30" s="119" t="n"/>
-      <c r="DW30" s="119" t="n"/>
-      <c r="DX30" s="119" t="n"/>
-      <c r="DY30" s="119" t="n"/>
-      <c r="DZ30" s="119" t="n"/>
-      <c r="EA30" s="119" t="n"/>
-      <c r="EB30" s="119" t="n"/>
-      <c r="EC30" s="119" t="n"/>
-      <c r="ED30" s="119" t="n"/>
-      <c r="EE30" s="119" t="n"/>
-      <c r="EF30" s="119" t="n"/>
-      <c r="EG30" s="119" t="n"/>
-      <c r="EH30" s="119" t="n"/>
-      <c r="EI30" s="119" t="n"/>
-      <c r="EJ30" s="119" t="n"/>
-      <c r="EK30" s="119" t="n"/>
-      <c r="EL30" s="119" t="n"/>
-      <c r="EM30" s="119" t="n"/>
-      <c r="EN30" s="119" t="n"/>
-      <c r="EO30" s="119" t="n"/>
-      <c r="EP30" s="119" t="n"/>
-      <c r="EQ30" s="119" t="n"/>
-      <c r="ER30" s="119" t="n"/>
-      <c r="ES30" s="119" t="n"/>
-      <c r="ET30" s="119" t="n"/>
-      <c r="EU30" s="119" t="n"/>
-      <c r="EV30" s="119" t="n"/>
-      <c r="EW30" s="119" t="n"/>
-      <c r="EX30" s="119" t="n"/>
-      <c r="EY30" s="119" t="n"/>
-      <c r="EZ30" s="119" t="n"/>
-      <c r="FA30" s="119" t="n"/>
-      <c r="FB30" s="119" t="n"/>
-      <c r="FC30" s="119" t="n"/>
-      <c r="FD30" s="119" t="n"/>
-      <c r="FE30" s="119" t="n"/>
-      <c r="FF30" s="119" t="n"/>
-      <c r="FG30" s="119" t="n"/>
-      <c r="FH30" s="119" t="n"/>
-      <c r="FI30" s="119" t="n"/>
-      <c r="FJ30" s="119" t="n"/>
-      <c r="FK30" s="119" t="n"/>
-      <c r="FL30" s="119" t="n"/>
-      <c r="FM30" s="119" t="n"/>
-      <c r="FN30" s="119" t="n"/>
-      <c r="FO30" s="119" t="n"/>
-      <c r="FP30" s="119" t="n"/>
-      <c r="FQ30" s="119" t="n"/>
-      <c r="FR30" s="119" t="n"/>
-      <c r="FS30" s="119" t="n"/>
-      <c r="FT30" s="119" t="n"/>
-      <c r="FU30" s="119" t="n"/>
-      <c r="FV30" s="119" t="n"/>
-      <c r="FW30" s="119" t="n"/>
-      <c r="FX30" s="119" t="n"/>
-      <c r="FY30" s="119" t="n"/>
-      <c r="FZ30" s="119" t="n"/>
-      <c r="GA30" s="119" t="n"/>
-      <c r="GB30" s="119" t="n"/>
-      <c r="GC30" s="119" t="n"/>
-      <c r="GD30" s="119" t="n"/>
-      <c r="GE30" s="119" t="n"/>
-      <c r="GF30" s="119" t="n"/>
-      <c r="GG30" s="119" t="n"/>
-      <c r="GH30" s="119" t="n"/>
-      <c r="GI30" s="119" t="n"/>
-      <c r="GJ30" s="119" t="n"/>
-      <c r="GK30" s="119" t="n"/>
-      <c r="GL30" s="119" t="n"/>
-      <c r="GM30" s="119" t="n"/>
-      <c r="GN30" s="119" t="n"/>
-      <c r="GO30" s="119" t="n"/>
-      <c r="GP30" s="119" t="n"/>
-      <c r="GQ30" s="119" t="n"/>
-      <c r="GR30" s="119" t="n"/>
-      <c r="GS30" s="119" t="n"/>
-      <c r="GT30" s="119" t="n"/>
-      <c r="GU30" s="119" t="n"/>
-      <c r="GV30" s="119" t="n"/>
-      <c r="GW30" s="119" t="n"/>
-      <c r="GX30" s="119" t="n"/>
-      <c r="GY30" s="119" t="n"/>
-      <c r="GZ30" s="119" t="n"/>
-      <c r="HA30" s="119" t="n"/>
-      <c r="HB30" s="119" t="n"/>
-      <c r="HC30" s="119" t="n"/>
-      <c r="HD30" s="119" t="n"/>
-      <c r="HE30" s="119" t="n"/>
-      <c r="HF30" s="119" t="n"/>
-      <c r="HG30" s="119" t="n"/>
-      <c r="HH30" s="119" t="n"/>
-      <c r="HI30" s="119" t="n"/>
-      <c r="HJ30" s="119" t="n"/>
-      <c r="HK30" s="119" t="n"/>
-      <c r="HL30" s="119" t="n"/>
-      <c r="HM30" s="119" t="n"/>
-      <c r="HN30" s="119" t="n"/>
-      <c r="HO30" s="119" t="n"/>
-      <c r="HP30" s="119" t="n"/>
-      <c r="HQ30" s="119" t="n"/>
-      <c r="HR30" s="119" t="n"/>
-      <c r="HS30" s="119" t="n"/>
-      <c r="HT30" s="119" t="n"/>
-      <c r="HU30" s="119" t="n"/>
-    </row>
-    <row r="31" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A31" s="58" t="n"/>
-      <c r="B31" s="121" t="n"/>
-      <c r="C31" s="122" t="n"/>
-      <c r="D31" s="123" t="n"/>
-      <c r="E31" s="124" t="n"/>
-      <c r="F31" s="55" t="n"/>
-      <c r="G31" s="125" t="n"/>
-      <c r="H31" s="56" t="n"/>
-      <c r="I31" s="57" t="n"/>
-      <c r="J31" s="125" t="n"/>
-      <c r="K31" s="126" t="n"/>
-      <c r="L31" s="59" t="n"/>
-      <c r="M31" s="60" t="n"/>
-      <c r="N31" s="57" t="n"/>
-      <c r="O31" s="126" t="n"/>
-      <c r="P31" s="57" t="n"/>
-      <c r="Q31" s="57" t="n"/>
-      <c r="R31" s="57" t="n"/>
-      <c r="S31" s="57" t="n"/>
-      <c r="T31" s="57" t="n"/>
-      <c r="U31" s="57" t="n"/>
-      <c r="V31" s="57" t="n"/>
-      <c r="W31" s="57">
-        <f>SUM(K31:U31)</f>
-        <v/>
-      </c>
-      <c r="X31" s="57" t="n"/>
-      <c r="Y31" s="57" t="n"/>
-      <c r="Z31" s="59" t="n"/>
-      <c r="AA31" s="57">
-        <f>SUM(X31:Z31)</f>
-        <v/>
-      </c>
-      <c r="AB31" s="57">
-        <f>+W31+AA31</f>
-        <v/>
-      </c>
-      <c r="AC31" s="63" t="n"/>
-      <c r="AD31" s="149" t="n"/>
-      <c r="AE31" s="119" t="n"/>
-      <c r="AF31" s="119" t="n"/>
-      <c r="AG31" s="119" t="n"/>
-      <c r="AH31" s="119" t="n"/>
-      <c r="AI31" s="119" t="n"/>
-      <c r="AJ31" s="119" t="n"/>
-      <c r="AK31" s="119" t="n"/>
-      <c r="AL31" s="119" t="n"/>
-      <c r="AM31" s="119" t="n"/>
-      <c r="AN31" s="119" t="n"/>
-      <c r="AO31" s="119" t="n"/>
-      <c r="AP31" s="119" t="n"/>
-      <c r="AQ31" s="119" t="n"/>
-      <c r="AR31" s="119" t="n"/>
-      <c r="AS31" s="119" t="n"/>
-      <c r="AT31" s="119" t="n"/>
-      <c r="AU31" s="119" t="n"/>
-      <c r="AV31" s="119" t="n"/>
-      <c r="AW31" s="119" t="n"/>
-      <c r="AX31" s="119" t="n"/>
-      <c r="AY31" s="119" t="n"/>
-      <c r="AZ31" s="119" t="n"/>
-      <c r="BA31" s="119" t="n"/>
-      <c r="BB31" s="119" t="n"/>
-      <c r="BC31" s="119" t="n"/>
-      <c r="BD31" s="119" t="n"/>
-      <c r="BE31" s="119" t="n"/>
-      <c r="BF31" s="119" t="n"/>
-      <c r="BG31" s="119" t="n"/>
-      <c r="BH31" s="119" t="n"/>
-      <c r="BI31" s="119" t="n"/>
-      <c r="BJ31" s="119" t="n"/>
-      <c r="BK31" s="119" t="n"/>
-      <c r="BL31" s="119" t="n"/>
-      <c r="BM31" s="119" t="n"/>
-      <c r="BN31" s="119" t="n"/>
-      <c r="BO31" s="119" t="n"/>
-      <c r="BP31" s="119" t="n"/>
-      <c r="BQ31" s="119" t="n"/>
-      <c r="BR31" s="119" t="n"/>
-      <c r="BS31" s="119" t="n"/>
-      <c r="BT31" s="119" t="n"/>
-      <c r="BU31" s="119" t="n"/>
-      <c r="BV31" s="119" t="n"/>
-      <c r="BW31" s="119" t="n"/>
-      <c r="BX31" s="119" t="n"/>
-      <c r="BY31" s="119" t="n"/>
-      <c r="BZ31" s="119" t="n"/>
-      <c r="CA31" s="119" t="n"/>
-      <c r="CB31" s="119" t="n"/>
-      <c r="CC31" s="119" t="n"/>
-      <c r="CD31" s="119" t="n"/>
-      <c r="CE31" s="119" t="n"/>
-      <c r="CF31" s="119" t="n"/>
-      <c r="CG31" s="119" t="n"/>
-      <c r="CH31" s="119" t="n"/>
-      <c r="CI31" s="119" t="n"/>
-      <c r="CJ31" s="119" t="n"/>
-      <c r="CK31" s="119" t="n"/>
-      <c r="CL31" s="119" t="n"/>
-      <c r="CM31" s="119" t="n"/>
-      <c r="CN31" s="119" t="n"/>
-      <c r="CO31" s="119" t="n"/>
-      <c r="CP31" s="119" t="n"/>
-      <c r="CQ31" s="119" t="n"/>
-      <c r="CR31" s="119" t="n"/>
-      <c r="CS31" s="119" t="n"/>
-      <c r="CT31" s="119" t="n"/>
-      <c r="CU31" s="119" t="n"/>
-      <c r="CV31" s="119" t="n"/>
-      <c r="CW31" s="119" t="n"/>
-      <c r="CX31" s="119" t="n"/>
-      <c r="CY31" s="119" t="n"/>
-      <c r="CZ31" s="119" t="n"/>
-      <c r="DA31" s="119" t="n"/>
-      <c r="DB31" s="119" t="n"/>
-      <c r="DC31" s="119" t="n"/>
-      <c r="DD31" s="119" t="n"/>
-      <c r="DE31" s="119" t="n"/>
-      <c r="DF31" s="119" t="n"/>
-      <c r="DG31" s="119" t="n"/>
-      <c r="DH31" s="119" t="n"/>
-      <c r="DI31" s="119" t="n"/>
-      <c r="DJ31" s="119" t="n"/>
-      <c r="DK31" s="119" t="n"/>
-      <c r="DL31" s="119" t="n"/>
-      <c r="DM31" s="119" t="n"/>
-      <c r="DN31" s="119" t="n"/>
-      <c r="DO31" s="119" t="n"/>
-      <c r="DP31" s="119" t="n"/>
-      <c r="DQ31" s="119" t="n"/>
-      <c r="DR31" s="119" t="n"/>
-      <c r="DS31" s="119" t="n"/>
-      <c r="DT31" s="119" t="n"/>
-      <c r="DU31" s="119" t="n"/>
-      <c r="DV31" s="119" t="n"/>
-      <c r="DW31" s="119" t="n"/>
-      <c r="DX31" s="119" t="n"/>
-      <c r="DY31" s="119" t="n"/>
-      <c r="DZ31" s="119" t="n"/>
-      <c r="EA31" s="119" t="n"/>
-      <c r="EB31" s="119" t="n"/>
-      <c r="EC31" s="119" t="n"/>
-      <c r="ED31" s="119" t="n"/>
-      <c r="EE31" s="119" t="n"/>
-      <c r="EF31" s="119" t="n"/>
-      <c r="EG31" s="119" t="n"/>
-      <c r="EH31" s="119" t="n"/>
-      <c r="EI31" s="119" t="n"/>
-      <c r="EJ31" s="119" t="n"/>
-      <c r="EK31" s="119" t="n"/>
-      <c r="EL31" s="119" t="n"/>
-      <c r="EM31" s="119" t="n"/>
-      <c r="EN31" s="119" t="n"/>
-      <c r="EO31" s="119" t="n"/>
-      <c r="EP31" s="119" t="n"/>
-      <c r="EQ31" s="119" t="n"/>
-      <c r="ER31" s="119" t="n"/>
-      <c r="ES31" s="119" t="n"/>
-      <c r="ET31" s="119" t="n"/>
-      <c r="EU31" s="119" t="n"/>
-      <c r="EV31" s="119" t="n"/>
-      <c r="EW31" s="119" t="n"/>
-      <c r="EX31" s="119" t="n"/>
-      <c r="EY31" s="119" t="n"/>
-      <c r="EZ31" s="119" t="n"/>
-      <c r="FA31" s="119" t="n"/>
-      <c r="FB31" s="119" t="n"/>
-      <c r="FC31" s="119" t="n"/>
-      <c r="FD31" s="119" t="n"/>
-      <c r="FE31" s="119" t="n"/>
-      <c r="FF31" s="119" t="n"/>
-      <c r="FG31" s="119" t="n"/>
-      <c r="FH31" s="119" t="n"/>
-      <c r="FI31" s="119" t="n"/>
-      <c r="FJ31" s="119" t="n"/>
-      <c r="FK31" s="119" t="n"/>
-      <c r="FL31" s="119" t="n"/>
-      <c r="FM31" s="119" t="n"/>
-      <c r="FN31" s="119" t="n"/>
-      <c r="FO31" s="119" t="n"/>
-      <c r="FP31" s="119" t="n"/>
-      <c r="FQ31" s="119" t="n"/>
-      <c r="FR31" s="119" t="n"/>
-      <c r="FS31" s="119" t="n"/>
-      <c r="FT31" s="119" t="n"/>
-      <c r="FU31" s="119" t="n"/>
-      <c r="FV31" s="119" t="n"/>
-      <c r="FW31" s="119" t="n"/>
-      <c r="FX31" s="119" t="n"/>
-      <c r="FY31" s="119" t="n"/>
-      <c r="FZ31" s="119" t="n"/>
-      <c r="GA31" s="119" t="n"/>
-      <c r="GB31" s="119" t="n"/>
-      <c r="GC31" s="119" t="n"/>
-      <c r="GD31" s="119" t="n"/>
-      <c r="GE31" s="119" t="n"/>
-      <c r="GF31" s="119" t="n"/>
-      <c r="GG31" s="119" t="n"/>
-      <c r="GH31" s="119" t="n"/>
-      <c r="GI31" s="119" t="n"/>
-      <c r="GJ31" s="119" t="n"/>
-      <c r="GK31" s="119" t="n"/>
-      <c r="GL31" s="119" t="n"/>
-      <c r="GM31" s="119" t="n"/>
-      <c r="GN31" s="119" t="n"/>
-      <c r="GO31" s="119" t="n"/>
-      <c r="GP31" s="119" t="n"/>
-      <c r="GQ31" s="119" t="n"/>
-      <c r="GR31" s="119" t="n"/>
-      <c r="GS31" s="119" t="n"/>
-      <c r="GT31" s="119" t="n"/>
-      <c r="GU31" s="119" t="n"/>
-      <c r="GV31" s="119" t="n"/>
-      <c r="GW31" s="119" t="n"/>
-      <c r="GX31" s="119" t="n"/>
-      <c r="GY31" s="119" t="n"/>
-      <c r="GZ31" s="119" t="n"/>
-      <c r="HA31" s="119" t="n"/>
-      <c r="HB31" s="119" t="n"/>
-      <c r="HC31" s="119" t="n"/>
-      <c r="HD31" s="119" t="n"/>
-      <c r="HE31" s="119" t="n"/>
-      <c r="HF31" s="119" t="n"/>
-      <c r="HG31" s="119" t="n"/>
-      <c r="HH31" s="119" t="n"/>
-      <c r="HI31" s="119" t="n"/>
-      <c r="HJ31" s="119" t="n"/>
-      <c r="HK31" s="119" t="n"/>
-      <c r="HL31" s="119" t="n"/>
-      <c r="HM31" s="119" t="n"/>
-      <c r="HN31" s="119" t="n"/>
-      <c r="HO31" s="119" t="n"/>
-      <c r="HP31" s="119" t="n"/>
-      <c r="HQ31" s="119" t="n"/>
-      <c r="HR31" s="119" t="n"/>
-      <c r="HS31" s="119" t="n"/>
-      <c r="HT31" s="119" t="n"/>
-      <c r="HU31" s="119" t="n"/>
-    </row>
-    <row r="32" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A32" s="58" t="n"/>
-      <c r="B32" s="121" t="n"/>
-      <c r="C32" s="122" t="n"/>
-      <c r="D32" s="123" t="n"/>
-      <c r="E32" s="124" t="n"/>
-      <c r="F32" s="55" t="n"/>
-      <c r="G32" s="125" t="n"/>
-      <c r="H32" s="56" t="n"/>
-      <c r="I32" s="57" t="n"/>
-      <c r="J32" s="125" t="n"/>
-      <c r="K32" s="126" t="n"/>
-      <c r="L32" s="59" t="n"/>
-      <c r="M32" s="60" t="n"/>
-      <c r="N32" s="57" t="n"/>
-      <c r="O32" s="59" t="n"/>
-      <c r="P32" s="57" t="n"/>
-      <c r="Q32" s="57" t="n"/>
-      <c r="R32" s="57" t="n"/>
-      <c r="S32" s="57" t="n"/>
-      <c r="T32" s="57" t="n"/>
-      <c r="U32" s="57" t="n"/>
-      <c r="V32" s="57" t="n"/>
-      <c r="W32" s="57">
-        <f>SUM(K32:U32)</f>
-        <v/>
-      </c>
-      <c r="X32" s="57" t="n"/>
-      <c r="Y32" s="57" t="n"/>
-      <c r="Z32" s="59" t="n"/>
-      <c r="AA32" s="57">
-        <f>SUM(X32:Z32)</f>
-        <v/>
-      </c>
-      <c r="AB32" s="57">
-        <f>+W32+AA32</f>
-        <v/>
-      </c>
-      <c r="AC32" s="63" t="n"/>
-      <c r="AD32" s="149" t="n"/>
-      <c r="AE32" s="119" t="n"/>
-      <c r="AF32" s="119" t="n"/>
-      <c r="AG32" s="119" t="n"/>
-      <c r="AH32" s="119" t="n"/>
-      <c r="AI32" s="119" t="n"/>
-      <c r="AJ32" s="119" t="n"/>
-      <c r="AK32" s="119" t="n"/>
-      <c r="AL32" s="119" t="n"/>
-      <c r="AM32" s="119" t="n"/>
-      <c r="AN32" s="119" t="n"/>
-      <c r="AO32" s="119" t="n"/>
-      <c r="AP32" s="119" t="n"/>
-      <c r="AQ32" s="119" t="n"/>
-      <c r="AR32" s="119" t="n"/>
-      <c r="AS32" s="119" t="n"/>
-      <c r="AT32" s="119" t="n"/>
-      <c r="AU32" s="119" t="n"/>
-      <c r="AV32" s="119" t="n"/>
-      <c r="AW32" s="119" t="n"/>
-      <c r="AX32" s="119" t="n"/>
-      <c r="AY32" s="119" t="n"/>
-      <c r="AZ32" s="119" t="n"/>
-      <c r="BA32" s="119" t="n"/>
-      <c r="BB32" s="119" t="n"/>
-      <c r="BC32" s="119" t="n"/>
-      <c r="BD32" s="119" t="n"/>
-      <c r="BE32" s="119" t="n"/>
-      <c r="BF32" s="119" t="n"/>
-      <c r="BG32" s="119" t="n"/>
-      <c r="BH32" s="119" t="n"/>
-      <c r="BI32" s="119" t="n"/>
-      <c r="BJ32" s="119" t="n"/>
-      <c r="BK32" s="119" t="n"/>
-      <c r="BL32" s="119" t="n"/>
-      <c r="BM32" s="119" t="n"/>
-      <c r="BN32" s="119" t="n"/>
-      <c r="BO32" s="119" t="n"/>
-      <c r="BP32" s="119" t="n"/>
-      <c r="BQ32" s="119" t="n"/>
-      <c r="BR32" s="119" t="n"/>
-      <c r="BS32" s="119" t="n"/>
-      <c r="BT32" s="119" t="n"/>
-      <c r="BU32" s="119" t="n"/>
-      <c r="BV32" s="119" t="n"/>
-      <c r="BW32" s="119" t="n"/>
-      <c r="BX32" s="119" t="n"/>
-      <c r="BY32" s="119" t="n"/>
-      <c r="BZ32" s="119" t="n"/>
-      <c r="CA32" s="119" t="n"/>
-      <c r="CB32" s="119" t="n"/>
-      <c r="CC32" s="119" t="n"/>
-      <c r="CD32" s="119" t="n"/>
-      <c r="CE32" s="119" t="n"/>
-      <c r="CF32" s="119" t="n"/>
-      <c r="CG32" s="119" t="n"/>
-      <c r="CH32" s="119" t="n"/>
-      <c r="CI32" s="119" t="n"/>
-      <c r="CJ32" s="119" t="n"/>
-      <c r="CK32" s="119" t="n"/>
-      <c r="CL32" s="119" t="n"/>
-      <c r="CM32" s="119" t="n"/>
-      <c r="CN32" s="119" t="n"/>
-      <c r="CO32" s="119" t="n"/>
-      <c r="CP32" s="119" t="n"/>
-      <c r="CQ32" s="119" t="n"/>
-      <c r="CR32" s="119" t="n"/>
-      <c r="CS32" s="119" t="n"/>
-      <c r="CT32" s="119" t="n"/>
-      <c r="CU32" s="119" t="n"/>
-      <c r="CV32" s="119" t="n"/>
-      <c r="CW32" s="119" t="n"/>
-      <c r="CX32" s="119" t="n"/>
-      <c r="CY32" s="119" t="n"/>
-      <c r="CZ32" s="119" t="n"/>
-      <c r="DA32" s="119" t="n"/>
-      <c r="DB32" s="119" t="n"/>
-      <c r="DC32" s="119" t="n"/>
-      <c r="DD32" s="119" t="n"/>
-      <c r="DE32" s="119" t="n"/>
-      <c r="DF32" s="119" t="n"/>
-      <c r="DG32" s="119" t="n"/>
-      <c r="DH32" s="119" t="n"/>
-      <c r="DI32" s="119" t="n"/>
-      <c r="DJ32" s="119" t="n"/>
-      <c r="DK32" s="119" t="n"/>
-      <c r="DL32" s="119" t="n"/>
-      <c r="DM32" s="119" t="n"/>
-      <c r="DN32" s="119" t="n"/>
-      <c r="DO32" s="119" t="n"/>
-      <c r="DP32" s="119" t="n"/>
-      <c r="DQ32" s="119" t="n"/>
-      <c r="DR32" s="119" t="n"/>
-      <c r="DS32" s="119" t="n"/>
-      <c r="DT32" s="119" t="n"/>
-      <c r="DU32" s="119" t="n"/>
-      <c r="DV32" s="119" t="n"/>
-      <c r="DW32" s="119" t="n"/>
-      <c r="DX32" s="119" t="n"/>
-      <c r="DY32" s="119" t="n"/>
-      <c r="DZ32" s="119" t="n"/>
-      <c r="EA32" s="119" t="n"/>
-      <c r="EB32" s="119" t="n"/>
-      <c r="EC32" s="119" t="n"/>
-      <c r="ED32" s="119" t="n"/>
-      <c r="EE32" s="119" t="n"/>
-      <c r="EF32" s="119" t="n"/>
-      <c r="EG32" s="119" t="n"/>
-      <c r="EH32" s="119" t="n"/>
-      <c r="EI32" s="119" t="n"/>
-      <c r="EJ32" s="119" t="n"/>
-      <c r="EK32" s="119" t="n"/>
-      <c r="EL32" s="119" t="n"/>
-      <c r="EM32" s="119" t="n"/>
-      <c r="EN32" s="119" t="n"/>
-      <c r="EO32" s="119" t="n"/>
-      <c r="EP32" s="119" t="n"/>
-      <c r="EQ32" s="119" t="n"/>
-      <c r="ER32" s="119" t="n"/>
-      <c r="ES32" s="119" t="n"/>
-      <c r="ET32" s="119" t="n"/>
-      <c r="EU32" s="119" t="n"/>
-      <c r="EV32" s="119" t="n"/>
-      <c r="EW32" s="119" t="n"/>
-      <c r="EX32" s="119" t="n"/>
-      <c r="EY32" s="119" t="n"/>
-      <c r="EZ32" s="119" t="n"/>
-      <c r="FA32" s="119" t="n"/>
-      <c r="FB32" s="119" t="n"/>
-      <c r="FC32" s="119" t="n"/>
-      <c r="FD32" s="119" t="n"/>
-      <c r="FE32" s="119" t="n"/>
-      <c r="FF32" s="119" t="n"/>
-      <c r="FG32" s="119" t="n"/>
-      <c r="FH32" s="119" t="n"/>
-      <c r="FI32" s="119" t="n"/>
-      <c r="FJ32" s="119" t="n"/>
-      <c r="FK32" s="119" t="n"/>
-      <c r="FL32" s="119" t="n"/>
-      <c r="FM32" s="119" t="n"/>
-      <c r="FN32" s="119" t="n"/>
-      <c r="FO32" s="119" t="n"/>
-      <c r="FP32" s="119" t="n"/>
-      <c r="FQ32" s="119" t="n"/>
-      <c r="FR32" s="119" t="n"/>
-      <c r="FS32" s="119" t="n"/>
-      <c r="FT32" s="119" t="n"/>
-      <c r="FU32" s="119" t="n"/>
-      <c r="FV32" s="119" t="n"/>
-      <c r="FW32" s="119" t="n"/>
-      <c r="FX32" s="119" t="n"/>
-      <c r="FY32" s="119" t="n"/>
-      <c r="FZ32" s="119" t="n"/>
-      <c r="GA32" s="119" t="n"/>
-      <c r="GB32" s="119" t="n"/>
-      <c r="GC32" s="119" t="n"/>
-      <c r="GD32" s="119" t="n"/>
-      <c r="GE32" s="119" t="n"/>
-      <c r="GF32" s="119" t="n"/>
-      <c r="GG32" s="119" t="n"/>
-      <c r="GH32" s="119" t="n"/>
-      <c r="GI32" s="119" t="n"/>
-      <c r="GJ32" s="119" t="n"/>
-      <c r="GK32" s="119" t="n"/>
-      <c r="GL32" s="119" t="n"/>
-      <c r="GM32" s="119" t="n"/>
-      <c r="GN32" s="119" t="n"/>
-      <c r="GO32" s="119" t="n"/>
-      <c r="GP32" s="119" t="n"/>
-      <c r="GQ32" s="119" t="n"/>
-      <c r="GR32" s="119" t="n"/>
-      <c r="GS32" s="119" t="n"/>
-      <c r="GT32" s="119" t="n"/>
-      <c r="GU32" s="119" t="n"/>
-      <c r="GV32" s="119" t="n"/>
-      <c r="GW32" s="119" t="n"/>
-      <c r="GX32" s="119" t="n"/>
-      <c r="GY32" s="119" t="n"/>
-      <c r="GZ32" s="119" t="n"/>
-      <c r="HA32" s="119" t="n"/>
-      <c r="HB32" s="119" t="n"/>
-      <c r="HC32" s="119" t="n"/>
-      <c r="HD32" s="119" t="n"/>
-      <c r="HE32" s="119" t="n"/>
-      <c r="HF32" s="119" t="n"/>
-      <c r="HG32" s="119" t="n"/>
-      <c r="HH32" s="119" t="n"/>
-      <c r="HI32" s="119" t="n"/>
-      <c r="HJ32" s="119" t="n"/>
-      <c r="HK32" s="119" t="n"/>
-      <c r="HL32" s="119" t="n"/>
-      <c r="HM32" s="119" t="n"/>
-      <c r="HN32" s="119" t="n"/>
-      <c r="HO32" s="119" t="n"/>
-      <c r="HP32" s="119" t="n"/>
-      <c r="HQ32" s="119" t="n"/>
-      <c r="HR32" s="119" t="n"/>
-      <c r="HS32" s="119" t="n"/>
-      <c r="HT32" s="119" t="n"/>
-      <c r="HU32" s="119" t="n"/>
-    </row>
-    <row r="33" ht="52" customFormat="1" customHeight="1" s="120" thickBot="1">
-      <c r="A33" s="129" t="n"/>
-      <c r="B33" s="130" t="n"/>
-      <c r="C33" s="131" t="n"/>
-      <c r="D33" s="132" t="n"/>
-      <c r="E33" s="133" t="n"/>
-      <c r="F33" s="134" t="n"/>
-      <c r="G33" s="135" t="n"/>
-      <c r="H33" s="136" t="n"/>
-      <c r="I33" s="137" t="n"/>
-      <c r="J33" s="135" t="n"/>
-      <c r="K33" s="138" t="n"/>
-      <c r="L33" s="139" t="n"/>
-      <c r="M33" s="140" t="n"/>
-      <c r="N33" s="137" t="n"/>
-      <c r="O33" s="139" t="n"/>
-      <c r="P33" s="137" t="n"/>
-      <c r="Q33" s="137" t="n"/>
-      <c r="R33" s="137" t="n"/>
-      <c r="S33" s="137" t="n"/>
-      <c r="T33" s="137" t="n"/>
-      <c r="U33" s="137" t="n"/>
-      <c r="V33" s="137" t="n"/>
-      <c r="W33" s="137">
-        <f>SUM(K33:U33)</f>
-        <v/>
-      </c>
-      <c r="X33" s="137" t="n"/>
-      <c r="Y33" s="137" t="n"/>
-      <c r="Z33" s="139" t="n"/>
-      <c r="AA33" s="137">
-        <f>SUM(X33:Z33)</f>
-        <v/>
-      </c>
-      <c r="AB33" s="137">
-        <f>+W33+AA33</f>
-        <v/>
-      </c>
-      <c r="AC33" s="128" t="n"/>
-      <c r="AD33" s="150" t="n"/>
-      <c r="AE33" s="119" t="n"/>
-      <c r="AF33" s="119" t="n"/>
-      <c r="AG33" s="119" t="n"/>
-      <c r="AH33" s="119" t="n"/>
-      <c r="AI33" s="119" t="n"/>
-      <c r="AJ33" s="119" t="n"/>
-      <c r="AK33" s="119" t="n"/>
-      <c r="AL33" s="119" t="n"/>
-      <c r="AM33" s="119" t="n"/>
-      <c r="AN33" s="119" t="n"/>
-      <c r="AO33" s="119" t="n"/>
-      <c r="AP33" s="119" t="n"/>
-      <c r="AQ33" s="119" t="n"/>
-      <c r="AR33" s="119" t="n"/>
-      <c r="AS33" s="119" t="n"/>
-      <c r="AT33" s="119" t="n"/>
-      <c r="AU33" s="119" t="n"/>
-      <c r="AV33" s="119" t="n"/>
-      <c r="AW33" s="119" t="n"/>
-      <c r="AX33" s="119" t="n"/>
-      <c r="AY33" s="119" t="n"/>
-      <c r="AZ33" s="119" t="n"/>
-      <c r="BA33" s="119" t="n"/>
-      <c r="BB33" s="119" t="n"/>
-      <c r="BC33" s="119" t="n"/>
-      <c r="BD33" s="119" t="n"/>
-      <c r="BE33" s="119" t="n"/>
-      <c r="BF33" s="119" t="n"/>
-      <c r="BG33" s="119" t="n"/>
-      <c r="BH33" s="119" t="n"/>
-      <c r="BI33" s="119" t="n"/>
-      <c r="BJ33" s="119" t="n"/>
-      <c r="BK33" s="119" t="n"/>
-      <c r="BL33" s="119" t="n"/>
-      <c r="BM33" s="119" t="n"/>
-      <c r="BN33" s="119" t="n"/>
-      <c r="BO33" s="119" t="n"/>
-      <c r="BP33" s="119" t="n"/>
-      <c r="BQ33" s="119" t="n"/>
-      <c r="BR33" s="119" t="n"/>
-      <c r="BS33" s="119" t="n"/>
-      <c r="BT33" s="119" t="n"/>
-      <c r="BU33" s="119" t="n"/>
-      <c r="BV33" s="119" t="n"/>
-      <c r="BW33" s="119" t="n"/>
-      <c r="BX33" s="119" t="n"/>
-      <c r="BY33" s="119" t="n"/>
-      <c r="BZ33" s="119" t="n"/>
-      <c r="CA33" s="119" t="n"/>
-      <c r="CB33" s="119" t="n"/>
-      <c r="CC33" s="119" t="n"/>
-      <c r="CD33" s="119" t="n"/>
-      <c r="CE33" s="119" t="n"/>
-      <c r="CF33" s="119" t="n"/>
-      <c r="CG33" s="119" t="n"/>
-      <c r="CH33" s="119" t="n"/>
-      <c r="CI33" s="119" t="n"/>
-      <c r="CJ33" s="119" t="n"/>
-      <c r="CK33" s="119" t="n"/>
-      <c r="CL33" s="119" t="n"/>
-      <c r="CM33" s="119" t="n"/>
-      <c r="CN33" s="119" t="n"/>
-      <c r="CO33" s="119" t="n"/>
-      <c r="CP33" s="119" t="n"/>
-      <c r="CQ33" s="119" t="n"/>
-      <c r="CR33" s="119" t="n"/>
-      <c r="CS33" s="119" t="n"/>
-      <c r="CT33" s="119" t="n"/>
-      <c r="CU33" s="119" t="n"/>
-      <c r="CV33" s="119" t="n"/>
-      <c r="CW33" s="119" t="n"/>
-      <c r="CX33" s="119" t="n"/>
-      <c r="CY33" s="119" t="n"/>
-      <c r="CZ33" s="119" t="n"/>
-      <c r="DA33" s="119" t="n"/>
-      <c r="DB33" s="119" t="n"/>
-      <c r="DC33" s="119" t="n"/>
-      <c r="DD33" s="119" t="n"/>
-      <c r="DE33" s="119" t="n"/>
-      <c r="DF33" s="119" t="n"/>
-      <c r="DG33" s="119" t="n"/>
-      <c r="DH33" s="119" t="n"/>
-      <c r="DI33" s="119" t="n"/>
-      <c r="DJ33" s="119" t="n"/>
-      <c r="DK33" s="119" t="n"/>
-      <c r="DL33" s="119" t="n"/>
-      <c r="DM33" s="119" t="n"/>
-      <c r="DN33" s="119" t="n"/>
-      <c r="DO33" s="119" t="n"/>
-      <c r="DP33" s="119" t="n"/>
-      <c r="DQ33" s="119" t="n"/>
-      <c r="DR33" s="119" t="n"/>
-      <c r="DS33" s="119" t="n"/>
-      <c r="DT33" s="119" t="n"/>
-      <c r="DU33" s="119" t="n"/>
-      <c r="DV33" s="119" t="n"/>
-      <c r="DW33" s="119" t="n"/>
-      <c r="DX33" s="119" t="n"/>
-      <c r="DY33" s="119" t="n"/>
-      <c r="DZ33" s="119" t="n"/>
-      <c r="EA33" s="119" t="n"/>
-      <c r="EB33" s="119" t="n"/>
-      <c r="EC33" s="119" t="n"/>
-      <c r="ED33" s="119" t="n"/>
-      <c r="EE33" s="119" t="n"/>
-      <c r="EF33" s="119" t="n"/>
-      <c r="EG33" s="119" t="n"/>
-      <c r="EH33" s="119" t="n"/>
-      <c r="EI33" s="119" t="n"/>
-      <c r="EJ33" s="119" t="n"/>
-      <c r="EK33" s="119" t="n"/>
-      <c r="EL33" s="119" t="n"/>
-      <c r="EM33" s="119" t="n"/>
-      <c r="EN33" s="119" t="n"/>
-      <c r="EO33" s="119" t="n"/>
-      <c r="EP33" s="119" t="n"/>
-      <c r="EQ33" s="119" t="n"/>
-      <c r="ER33" s="119" t="n"/>
-      <c r="ES33" s="119" t="n"/>
-      <c r="ET33" s="119" t="n"/>
-      <c r="EU33" s="119" t="n"/>
-      <c r="EV33" s="119" t="n"/>
-      <c r="EW33" s="119" t="n"/>
-      <c r="EX33" s="119" t="n"/>
-      <c r="EY33" s="119" t="n"/>
-      <c r="EZ33" s="119" t="n"/>
-      <c r="FA33" s="119" t="n"/>
-      <c r="FB33" s="119" t="n"/>
-      <c r="FC33" s="119" t="n"/>
-      <c r="FD33" s="119" t="n"/>
-      <c r="FE33" s="119" t="n"/>
-      <c r="FF33" s="119" t="n"/>
-      <c r="FG33" s="119" t="n"/>
-      <c r="FH33" s="119" t="n"/>
-      <c r="FI33" s="119" t="n"/>
-      <c r="FJ33" s="119" t="n"/>
-      <c r="FK33" s="119" t="n"/>
-      <c r="FL33" s="119" t="n"/>
-      <c r="FM33" s="119" t="n"/>
-      <c r="FN33" s="119" t="n"/>
-      <c r="FO33" s="119" t="n"/>
-      <c r="FP33" s="119" t="n"/>
-      <c r="FQ33" s="119" t="n"/>
-      <c r="FR33" s="119" t="n"/>
-      <c r="FS33" s="119" t="n"/>
-      <c r="FT33" s="119" t="n"/>
-      <c r="FU33" s="119" t="n"/>
-      <c r="FV33" s="119" t="n"/>
-      <c r="FW33" s="119" t="n"/>
-      <c r="FX33" s="119" t="n"/>
-      <c r="FY33" s="119" t="n"/>
-      <c r="FZ33" s="119" t="n"/>
-      <c r="GA33" s="119" t="n"/>
-      <c r="GB33" s="119" t="n"/>
-      <c r="GC33" s="119" t="n"/>
-      <c r="GD33" s="119" t="n"/>
-      <c r="GE33" s="119" t="n"/>
-      <c r="GF33" s="119" t="n"/>
-      <c r="GG33" s="119" t="n"/>
-      <c r="GH33" s="119" t="n"/>
-      <c r="GI33" s="119" t="n"/>
-      <c r="GJ33" s="119" t="n"/>
-      <c r="GK33" s="119" t="n"/>
-      <c r="GL33" s="119" t="n"/>
-      <c r="GM33" s="119" t="n"/>
-      <c r="GN33" s="119" t="n"/>
-      <c r="GO33" s="119" t="n"/>
-      <c r="GP33" s="119" t="n"/>
-      <c r="GQ33" s="119" t="n"/>
-      <c r="GR33" s="119" t="n"/>
-      <c r="GS33" s="119" t="n"/>
-      <c r="GT33" s="119" t="n"/>
-      <c r="GU33" s="119" t="n"/>
-      <c r="GV33" s="119" t="n"/>
-      <c r="GW33" s="119" t="n"/>
-      <c r="GX33" s="119" t="n"/>
-      <c r="GY33" s="119" t="n"/>
-      <c r="GZ33" s="119" t="n"/>
-      <c r="HA33" s="119" t="n"/>
-      <c r="HB33" s="119" t="n"/>
-      <c r="HC33" s="119" t="n"/>
-      <c r="HD33" s="119" t="n"/>
-      <c r="HE33" s="119" t="n"/>
-      <c r="HF33" s="119" t="n"/>
-      <c r="HG33" s="119" t="n"/>
-      <c r="HH33" s="119" t="n"/>
-      <c r="HI33" s="119" t="n"/>
-      <c r="HJ33" s="119" t="n"/>
-      <c r="HK33" s="119" t="n"/>
-      <c r="HL33" s="119" t="n"/>
-      <c r="HM33" s="119" t="n"/>
-      <c r="HN33" s="119" t="n"/>
-      <c r="HO33" s="119" t="n"/>
-      <c r="HP33" s="119" t="n"/>
-      <c r="HQ33" s="119" t="n"/>
-      <c r="HR33" s="119" t="n"/>
-      <c r="HS33" s="119" t="n"/>
-      <c r="HT33" s="119" t="n"/>
-      <c r="HU33" s="119" t="n"/>
-    </row>
-    <row r="34" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A34" s="70" t="n"/>
-      <c r="B34" s="111" t="n"/>
-      <c r="C34" s="112" t="n"/>
-      <c r="D34" s="113" t="n"/>
-      <c r="E34" s="114" t="n"/>
-      <c r="F34" s="71" t="n"/>
-      <c r="G34" s="115" t="n"/>
-      <c r="H34" s="72" t="n"/>
-      <c r="I34" s="73" t="n"/>
-      <c r="J34" s="115" t="n"/>
-      <c r="K34" s="116" t="n"/>
-      <c r="L34" s="117" t="n"/>
-      <c r="M34" s="118" t="n"/>
-      <c r="N34" s="73" t="n"/>
-      <c r="O34" s="117" t="n"/>
-      <c r="P34" s="73" t="n"/>
-      <c r="Q34" s="73" t="n"/>
-      <c r="R34" s="73" t="n"/>
-      <c r="S34" s="73" t="n"/>
-      <c r="T34" s="73" t="n"/>
-      <c r="U34" s="73" t="n"/>
-      <c r="V34" s="73" t="n"/>
-      <c r="W34" s="73">
-        <f>SUM(K34:U34)</f>
-        <v/>
-      </c>
-      <c r="X34" s="73" t="n"/>
-      <c r="Y34" s="73" t="n"/>
-      <c r="Z34" s="117" t="n"/>
-      <c r="AA34" s="73">
-        <f>SUM(X34:Z34)</f>
-        <v/>
-      </c>
-      <c r="AB34" s="73">
-        <f>+W34+AA34</f>
-        <v/>
-      </c>
-      <c r="AC34" s="141" t="n"/>
-      <c r="AD34" s="148" t="inlineStr">
-        <is>
-          <t>00000210</t>
-        </is>
-      </c>
-      <c r="AE34" s="119" t="n"/>
-      <c r="AF34" s="119" t="n"/>
-      <c r="AG34" s="119" t="n"/>
-      <c r="AH34" s="119" t="n"/>
-      <c r="AI34" s="119" t="n"/>
-      <c r="AJ34" s="119" t="n"/>
-      <c r="AK34" s="119" t="n"/>
-      <c r="AL34" s="119" t="n"/>
-      <c r="AM34" s="119" t="n"/>
-      <c r="AN34" s="119" t="n"/>
-      <c r="AO34" s="119" t="n"/>
-      <c r="AP34" s="119" t="n"/>
-      <c r="AQ34" s="119" t="n"/>
-      <c r="AR34" s="119" t="n"/>
-      <c r="AS34" s="119" t="n"/>
-      <c r="AT34" s="119" t="n"/>
-      <c r="AU34" s="119" t="n"/>
-      <c r="AV34" s="119" t="n"/>
-      <c r="AW34" s="119" t="n"/>
-      <c r="AX34" s="119" t="n"/>
-      <c r="AY34" s="119" t="n"/>
-      <c r="AZ34" s="119" t="n"/>
-      <c r="BA34" s="119" t="n"/>
-      <c r="BB34" s="119" t="n"/>
-      <c r="BC34" s="119" t="n"/>
-      <c r="BD34" s="119" t="n"/>
-      <c r="BE34" s="119" t="n"/>
-      <c r="BF34" s="119" t="n"/>
-      <c r="BG34" s="119" t="n"/>
-      <c r="BH34" s="119" t="n"/>
-      <c r="BI34" s="119" t="n"/>
-      <c r="BJ34" s="119" t="n"/>
-      <c r="BK34" s="119" t="n"/>
-      <c r="BL34" s="119" t="n"/>
-      <c r="BM34" s="119" t="n"/>
-      <c r="BN34" s="119" t="n"/>
-      <c r="BO34" s="119" t="n"/>
-      <c r="BP34" s="119" t="n"/>
-      <c r="BQ34" s="119" t="n"/>
-      <c r="BR34" s="119" t="n"/>
-      <c r="BS34" s="119" t="n"/>
-      <c r="BT34" s="119" t="n"/>
-      <c r="BU34" s="119" t="n"/>
-      <c r="BV34" s="119" t="n"/>
-      <c r="BW34" s="119" t="n"/>
-      <c r="BX34" s="119" t="n"/>
-      <c r="BY34" s="119" t="n"/>
-      <c r="BZ34" s="119" t="n"/>
-      <c r="CA34" s="119" t="n"/>
-      <c r="CB34" s="119" t="n"/>
-      <c r="CC34" s="119" t="n"/>
-      <c r="CD34" s="119" t="n"/>
-      <c r="CE34" s="119" t="n"/>
-      <c r="CF34" s="119" t="n"/>
-      <c r="CG34" s="119" t="n"/>
-      <c r="CH34" s="119" t="n"/>
-      <c r="CI34" s="119" t="n"/>
-      <c r="CJ34" s="119" t="n"/>
-      <c r="CK34" s="119" t="n"/>
-      <c r="CL34" s="119" t="n"/>
-      <c r="CM34" s="119" t="n"/>
-      <c r="CN34" s="119" t="n"/>
-      <c r="CO34" s="119" t="n"/>
-      <c r="CP34" s="119" t="n"/>
-      <c r="CQ34" s="119" t="n"/>
-      <c r="CR34" s="119" t="n"/>
-      <c r="CS34" s="119" t="n"/>
-      <c r="CT34" s="119" t="n"/>
-      <c r="CU34" s="119" t="n"/>
-      <c r="CV34" s="119" t="n"/>
-      <c r="CW34" s="119" t="n"/>
-      <c r="CX34" s="119" t="n"/>
-      <c r="CY34" s="119" t="n"/>
-      <c r="CZ34" s="119" t="n"/>
-      <c r="DA34" s="119" t="n"/>
-      <c r="DB34" s="119" t="n"/>
-      <c r="DC34" s="119" t="n"/>
-      <c r="DD34" s="119" t="n"/>
-      <c r="DE34" s="119" t="n"/>
-      <c r="DF34" s="119" t="n"/>
-      <c r="DG34" s="119" t="n"/>
-      <c r="DH34" s="119" t="n"/>
-      <c r="DI34" s="119" t="n"/>
-      <c r="DJ34" s="119" t="n"/>
-      <c r="DK34" s="119" t="n"/>
-      <c r="DL34" s="119" t="n"/>
-      <c r="DM34" s="119" t="n"/>
-      <c r="DN34" s="119" t="n"/>
-      <c r="DO34" s="119" t="n"/>
-      <c r="DP34" s="119" t="n"/>
-      <c r="DQ34" s="119" t="n"/>
-      <c r="DR34" s="119" t="n"/>
-      <c r="DS34" s="119" t="n"/>
-      <c r="DT34" s="119" t="n"/>
-      <c r="DU34" s="119" t="n"/>
-      <c r="DV34" s="119" t="n"/>
-      <c r="DW34" s="119" t="n"/>
-      <c r="DX34" s="119" t="n"/>
-      <c r="DY34" s="119" t="n"/>
-      <c r="DZ34" s="119" t="n"/>
-      <c r="EA34" s="119" t="n"/>
-      <c r="EB34" s="119" t="n"/>
-      <c r="EC34" s="119" t="n"/>
-      <c r="ED34" s="119" t="n"/>
-      <c r="EE34" s="119" t="n"/>
-      <c r="EF34" s="119" t="n"/>
-      <c r="EG34" s="119" t="n"/>
-      <c r="EH34" s="119" t="n"/>
-      <c r="EI34" s="119" t="n"/>
-      <c r="EJ34" s="119" t="n"/>
-      <c r="EK34" s="119" t="n"/>
-      <c r="EL34" s="119" t="n"/>
-      <c r="EM34" s="119" t="n"/>
-      <c r="EN34" s="119" t="n"/>
-      <c r="EO34" s="119" t="n"/>
-      <c r="EP34" s="119" t="n"/>
-      <c r="EQ34" s="119" t="n"/>
-      <c r="ER34" s="119" t="n"/>
-      <c r="ES34" s="119" t="n"/>
-      <c r="ET34" s="119" t="n"/>
-      <c r="EU34" s="119" t="n"/>
-      <c r="EV34" s="119" t="n"/>
-      <c r="EW34" s="119" t="n"/>
-      <c r="EX34" s="119" t="n"/>
-      <c r="EY34" s="119" t="n"/>
-      <c r="EZ34" s="119" t="n"/>
-      <c r="FA34" s="119" t="n"/>
-      <c r="FB34" s="119" t="n"/>
-      <c r="FC34" s="119" t="n"/>
-      <c r="FD34" s="119" t="n"/>
-      <c r="FE34" s="119" t="n"/>
-      <c r="FF34" s="119" t="n"/>
-      <c r="FG34" s="119" t="n"/>
-      <c r="FH34" s="119" t="n"/>
-      <c r="FI34" s="119" t="n"/>
-      <c r="FJ34" s="119" t="n"/>
-      <c r="FK34" s="119" t="n"/>
-      <c r="FL34" s="119" t="n"/>
-      <c r="FM34" s="119" t="n"/>
-      <c r="FN34" s="119" t="n"/>
-      <c r="FO34" s="119" t="n"/>
-      <c r="FP34" s="119" t="n"/>
-      <c r="FQ34" s="119" t="n"/>
-      <c r="FR34" s="119" t="n"/>
-      <c r="FS34" s="119" t="n"/>
-      <c r="FT34" s="119" t="n"/>
-      <c r="FU34" s="119" t="n"/>
-      <c r="FV34" s="119" t="n"/>
-      <c r="FW34" s="119" t="n"/>
-      <c r="FX34" s="119" t="n"/>
-      <c r="FY34" s="119" t="n"/>
-      <c r="FZ34" s="119" t="n"/>
-      <c r="GA34" s="119" t="n"/>
-      <c r="GB34" s="119" t="n"/>
-      <c r="GC34" s="119" t="n"/>
-      <c r="GD34" s="119" t="n"/>
-      <c r="GE34" s="119" t="n"/>
-      <c r="GF34" s="119" t="n"/>
-      <c r="GG34" s="119" t="n"/>
-      <c r="GH34" s="119" t="n"/>
-      <c r="GI34" s="119" t="n"/>
-      <c r="GJ34" s="119" t="n"/>
-      <c r="GK34" s="119" t="n"/>
-      <c r="GL34" s="119" t="n"/>
-      <c r="GM34" s="119" t="n"/>
-      <c r="GN34" s="119" t="n"/>
-      <c r="GO34" s="119" t="n"/>
-      <c r="GP34" s="119" t="n"/>
-      <c r="GQ34" s="119" t="n"/>
-      <c r="GR34" s="119" t="n"/>
-      <c r="GS34" s="119" t="n"/>
-      <c r="GT34" s="119" t="n"/>
-      <c r="GU34" s="119" t="n"/>
-      <c r="GV34" s="119" t="n"/>
-      <c r="GW34" s="119" t="n"/>
-      <c r="GX34" s="119" t="n"/>
-      <c r="GY34" s="119" t="n"/>
-      <c r="GZ34" s="119" t="n"/>
-      <c r="HA34" s="119" t="n"/>
-      <c r="HB34" s="119" t="n"/>
-      <c r="HC34" s="119" t="n"/>
-      <c r="HD34" s="119" t="n"/>
-      <c r="HE34" s="119" t="n"/>
-      <c r="HF34" s="119" t="n"/>
-      <c r="HG34" s="119" t="n"/>
-      <c r="HH34" s="119" t="n"/>
-      <c r="HI34" s="119" t="n"/>
-      <c r="HJ34" s="119" t="n"/>
-      <c r="HK34" s="119" t="n"/>
-      <c r="HL34" s="119" t="n"/>
-      <c r="HM34" s="119" t="n"/>
-      <c r="HN34" s="119" t="n"/>
-      <c r="HO34" s="119" t="n"/>
-      <c r="HP34" s="119" t="n"/>
-      <c r="HQ34" s="119" t="n"/>
-      <c r="HR34" s="119" t="n"/>
-      <c r="HS34" s="119" t="n"/>
-      <c r="HT34" s="119" t="n"/>
-      <c r="HU34" s="119" t="n"/>
-    </row>
-    <row r="35" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A35" s="58" t="n"/>
-      <c r="B35" s="121" t="n"/>
-      <c r="C35" s="122" t="n"/>
-      <c r="D35" s="123" t="n"/>
-      <c r="E35" s="124" t="n"/>
-      <c r="F35" s="55" t="n"/>
-      <c r="G35" s="125" t="n"/>
-      <c r="H35" s="56" t="n"/>
-      <c r="I35" s="57" t="n"/>
-      <c r="J35" s="125" t="n"/>
-      <c r="K35" s="126" t="n"/>
-      <c r="L35" s="59" t="n"/>
-      <c r="M35" s="60" t="n"/>
-      <c r="N35" s="57" t="n"/>
-      <c r="O35" s="59" t="n"/>
-      <c r="P35" s="57" t="n"/>
-      <c r="Q35" s="57" t="n"/>
-      <c r="R35" s="57" t="n"/>
-      <c r="S35" s="57" t="n"/>
-      <c r="T35" s="57" t="n"/>
-      <c r="U35" s="57" t="n"/>
-      <c r="V35" s="57" t="n"/>
-      <c r="W35" s="57">
-        <f>SUM(K35:U35)</f>
-        <v/>
-      </c>
-      <c r="X35" s="57" t="n"/>
-      <c r="Y35" s="57" t="n"/>
-      <c r="Z35" s="59" t="n"/>
-      <c r="AA35" s="57">
-        <f>SUM(X35:Z35)</f>
-        <v/>
-      </c>
-      <c r="AB35" s="57">
-        <f>+W35+AA35</f>
-        <v/>
-      </c>
-      <c r="AC35" s="63" t="n"/>
-      <c r="AD35" s="149" t="n"/>
-      <c r="AE35" s="119" t="n"/>
-      <c r="AF35" s="119" t="n"/>
-      <c r="AG35" s="119" t="n"/>
-      <c r="AH35" s="119" t="n"/>
-      <c r="AI35" s="119" t="n"/>
-      <c r="AJ35" s="119" t="n"/>
-      <c r="AK35" s="119" t="n"/>
-      <c r="AL35" s="119" t="n"/>
-      <c r="AM35" s="119" t="n"/>
-      <c r="AN35" s="119" t="n"/>
-      <c r="AO35" s="119" t="n"/>
-      <c r="AP35" s="119" t="n"/>
-      <c r="AQ35" s="119" t="n"/>
-      <c r="AR35" s="119" t="n"/>
-      <c r="AS35" s="119" t="n"/>
-      <c r="AT35" s="119" t="n"/>
-      <c r="AU35" s="119" t="n"/>
-      <c r="AV35" s="119" t="n"/>
-      <c r="AW35" s="119" t="n"/>
-      <c r="AX35" s="119" t="n"/>
-      <c r="AY35" s="119" t="n"/>
-      <c r="AZ35" s="119" t="n"/>
-      <c r="BA35" s="119" t="n"/>
-      <c r="BB35" s="119" t="n"/>
-      <c r="BC35" s="119" t="n"/>
-      <c r="BD35" s="119" t="n"/>
-      <c r="BE35" s="119" t="n"/>
-      <c r="BF35" s="119" t="n"/>
-      <c r="BG35" s="119" t="n"/>
-      <c r="BH35" s="119" t="n"/>
-      <c r="BI35" s="119" t="n"/>
-      <c r="BJ35" s="119" t="n"/>
-      <c r="BK35" s="119" t="n"/>
-      <c r="BL35" s="119" t="n"/>
-      <c r="BM35" s="119" t="n"/>
-      <c r="BN35" s="119" t="n"/>
-      <c r="BO35" s="119" t="n"/>
-      <c r="BP35" s="119" t="n"/>
-      <c r="BQ35" s="119" t="n"/>
-      <c r="BR35" s="119" t="n"/>
-      <c r="BS35" s="119" t="n"/>
-      <c r="BT35" s="119" t="n"/>
-      <c r="BU35" s="119" t="n"/>
-      <c r="BV35" s="119" t="n"/>
-      <c r="BW35" s="119" t="n"/>
-      <c r="BX35" s="119" t="n"/>
-      <c r="BY35" s="119" t="n"/>
-      <c r="BZ35" s="119" t="n"/>
-      <c r="CA35" s="119" t="n"/>
-      <c r="CB35" s="119" t="n"/>
-      <c r="CC35" s="119" t="n"/>
-      <c r="CD35" s="119" t="n"/>
-      <c r="CE35" s="119" t="n"/>
-      <c r="CF35" s="119" t="n"/>
-      <c r="CG35" s="119" t="n"/>
-      <c r="CH35" s="119" t="n"/>
-      <c r="CI35" s="119" t="n"/>
-      <c r="CJ35" s="119" t="n"/>
-      <c r="CK35" s="119" t="n"/>
-      <c r="CL35" s="119" t="n"/>
-      <c r="CM35" s="119" t="n"/>
-      <c r="CN35" s="119" t="n"/>
-      <c r="CO35" s="119" t="n"/>
-      <c r="CP35" s="119" t="n"/>
-      <c r="CQ35" s="119" t="n"/>
-      <c r="CR35" s="119" t="n"/>
-      <c r="CS35" s="119" t="n"/>
-      <c r="CT35" s="119" t="n"/>
-      <c r="CU35" s="119" t="n"/>
-      <c r="CV35" s="119" t="n"/>
-      <c r="CW35" s="119" t="n"/>
-      <c r="CX35" s="119" t="n"/>
-      <c r="CY35" s="119" t="n"/>
-      <c r="CZ35" s="119" t="n"/>
-      <c r="DA35" s="119" t="n"/>
-      <c r="DB35" s="119" t="n"/>
-      <c r="DC35" s="119" t="n"/>
-      <c r="DD35" s="119" t="n"/>
-      <c r="DE35" s="119" t="n"/>
-      <c r="DF35" s="119" t="n"/>
-      <c r="DG35" s="119" t="n"/>
-      <c r="DH35" s="119" t="n"/>
-      <c r="DI35" s="119" t="n"/>
-      <c r="DJ35" s="119" t="n"/>
-      <c r="DK35" s="119" t="n"/>
-      <c r="DL35" s="119" t="n"/>
-      <c r="DM35" s="119" t="n"/>
-      <c r="DN35" s="119" t="n"/>
-      <c r="DO35" s="119" t="n"/>
-      <c r="DP35" s="119" t="n"/>
-      <c r="DQ35" s="119" t="n"/>
-      <c r="DR35" s="119" t="n"/>
-      <c r="DS35" s="119" t="n"/>
-      <c r="DT35" s="119" t="n"/>
-      <c r="DU35" s="119" t="n"/>
-      <c r="DV35" s="119" t="n"/>
-      <c r="DW35" s="119" t="n"/>
-      <c r="DX35" s="119" t="n"/>
-      <c r="DY35" s="119" t="n"/>
-      <c r="DZ35" s="119" t="n"/>
-      <c r="EA35" s="119" t="n"/>
-      <c r="EB35" s="119" t="n"/>
-      <c r="EC35" s="119" t="n"/>
-      <c r="ED35" s="119" t="n"/>
-      <c r="EE35" s="119" t="n"/>
-      <c r="EF35" s="119" t="n"/>
-      <c r="EG35" s="119" t="n"/>
-      <c r="EH35" s="119" t="n"/>
-      <c r="EI35" s="119" t="n"/>
-      <c r="EJ35" s="119" t="n"/>
-      <c r="EK35" s="119" t="n"/>
-      <c r="EL35" s="119" t="n"/>
-      <c r="EM35" s="119" t="n"/>
-      <c r="EN35" s="119" t="n"/>
-      <c r="EO35" s="119" t="n"/>
-      <c r="EP35" s="119" t="n"/>
-      <c r="EQ35" s="119" t="n"/>
-      <c r="ER35" s="119" t="n"/>
-      <c r="ES35" s="119" t="n"/>
-      <c r="ET35" s="119" t="n"/>
-      <c r="EU35" s="119" t="n"/>
-      <c r="EV35" s="119" t="n"/>
-      <c r="EW35" s="119" t="n"/>
-      <c r="EX35" s="119" t="n"/>
-      <c r="EY35" s="119" t="n"/>
-      <c r="EZ35" s="119" t="n"/>
-      <c r="FA35" s="119" t="n"/>
-      <c r="FB35" s="119" t="n"/>
-      <c r="FC35" s="119" t="n"/>
-      <c r="FD35" s="119" t="n"/>
-      <c r="FE35" s="119" t="n"/>
-      <c r="FF35" s="119" t="n"/>
-      <c r="FG35" s="119" t="n"/>
-      <c r="FH35" s="119" t="n"/>
-      <c r="FI35" s="119" t="n"/>
-      <c r="FJ35" s="119" t="n"/>
-      <c r="FK35" s="119" t="n"/>
-      <c r="FL35" s="119" t="n"/>
-      <c r="FM35" s="119" t="n"/>
-      <c r="FN35" s="119" t="n"/>
-      <c r="FO35" s="119" t="n"/>
-      <c r="FP35" s="119" t="n"/>
-      <c r="FQ35" s="119" t="n"/>
-      <c r="FR35" s="119" t="n"/>
-      <c r="FS35" s="119" t="n"/>
-      <c r="FT35" s="119" t="n"/>
-      <c r="FU35" s="119" t="n"/>
-      <c r="FV35" s="119" t="n"/>
-      <c r="FW35" s="119" t="n"/>
-      <c r="FX35" s="119" t="n"/>
-      <c r="FY35" s="119" t="n"/>
-      <c r="FZ35" s="119" t="n"/>
-      <c r="GA35" s="119" t="n"/>
-      <c r="GB35" s="119" t="n"/>
-      <c r="GC35" s="119" t="n"/>
-      <c r="GD35" s="119" t="n"/>
-      <c r="GE35" s="119" t="n"/>
-      <c r="GF35" s="119" t="n"/>
-      <c r="GG35" s="119" t="n"/>
-      <c r="GH35" s="119" t="n"/>
-      <c r="GI35" s="119" t="n"/>
-      <c r="GJ35" s="119" t="n"/>
-      <c r="GK35" s="119" t="n"/>
-      <c r="GL35" s="119" t="n"/>
-      <c r="GM35" s="119" t="n"/>
-      <c r="GN35" s="119" t="n"/>
-      <c r="GO35" s="119" t="n"/>
-      <c r="GP35" s="119" t="n"/>
-      <c r="GQ35" s="119" t="n"/>
-      <c r="GR35" s="119" t="n"/>
-      <c r="GS35" s="119" t="n"/>
-      <c r="GT35" s="119" t="n"/>
-      <c r="GU35" s="119" t="n"/>
-      <c r="GV35" s="119" t="n"/>
-      <c r="GW35" s="119" t="n"/>
-      <c r="GX35" s="119" t="n"/>
-      <c r="GY35" s="119" t="n"/>
-      <c r="GZ35" s="119" t="n"/>
-      <c r="HA35" s="119" t="n"/>
-      <c r="HB35" s="119" t="n"/>
-      <c r="HC35" s="119" t="n"/>
-      <c r="HD35" s="119" t="n"/>
-      <c r="HE35" s="119" t="n"/>
-      <c r="HF35" s="119" t="n"/>
-      <c r="HG35" s="119" t="n"/>
-      <c r="HH35" s="119" t="n"/>
-      <c r="HI35" s="119" t="n"/>
-      <c r="HJ35" s="119" t="n"/>
-      <c r="HK35" s="119" t="n"/>
-      <c r="HL35" s="119" t="n"/>
-      <c r="HM35" s="119" t="n"/>
-      <c r="HN35" s="119" t="n"/>
-      <c r="HO35" s="119" t="n"/>
-      <c r="HP35" s="119" t="n"/>
-      <c r="HQ35" s="119" t="n"/>
-      <c r="HR35" s="119" t="n"/>
-      <c r="HS35" s="119" t="n"/>
-      <c r="HT35" s="119" t="n"/>
-      <c r="HU35" s="119" t="n"/>
-    </row>
-    <row r="36" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A36" s="58" t="n"/>
-      <c r="B36" s="121" t="n"/>
-      <c r="C36" s="122" t="n"/>
-      <c r="D36" s="123" t="n"/>
-      <c r="E36" s="124" t="n"/>
-      <c r="F36" s="55" t="n"/>
-      <c r="G36" s="125" t="n"/>
-      <c r="H36" s="56" t="n"/>
-      <c r="I36" s="57" t="n"/>
-      <c r="J36" s="125" t="n"/>
-      <c r="K36" s="126" t="n"/>
-      <c r="L36" s="59" t="n"/>
-      <c r="M36" s="60" t="n"/>
-      <c r="N36" s="57" t="n"/>
-      <c r="O36" s="59" t="n"/>
-      <c r="P36" s="57" t="n"/>
-      <c r="Q36" s="57" t="n"/>
-      <c r="R36" s="57" t="n"/>
-      <c r="S36" s="57" t="n"/>
-      <c r="T36" s="57" t="n"/>
-      <c r="U36" s="57" t="n"/>
-      <c r="V36" s="57" t="n"/>
-      <c r="W36" s="57">
-        <f>SUM(K36:U36)</f>
-        <v/>
-      </c>
-      <c r="X36" s="57" t="n"/>
-      <c r="Y36" s="57" t="n"/>
-      <c r="Z36" s="59" t="n"/>
-      <c r="AA36" s="57">
-        <f>SUM(X36:Z36)</f>
-        <v/>
-      </c>
-      <c r="AB36" s="57">
-        <f>+W36+AA36</f>
-        <v/>
-      </c>
-      <c r="AC36" s="56" t="n"/>
-      <c r="AD36" s="149" t="n"/>
-      <c r="AE36" s="119" t="n"/>
-      <c r="AF36" s="119" t="n"/>
-      <c r="AG36" s="119" t="n"/>
-      <c r="AH36" s="119" t="n"/>
-      <c r="AI36" s="119" t="n"/>
-      <c r="AJ36" s="119" t="n"/>
-      <c r="AK36" s="119" t="n"/>
-      <c r="AL36" s="119" t="n"/>
-      <c r="AM36" s="119" t="n"/>
-      <c r="AN36" s="119" t="n"/>
-      <c r="AO36" s="119" t="n"/>
-      <c r="AP36" s="119" t="n"/>
-      <c r="AQ36" s="119" t="n"/>
-      <c r="AR36" s="119" t="n"/>
-      <c r="AS36" s="119" t="n"/>
-      <c r="AT36" s="119" t="n"/>
-      <c r="AU36" s="119" t="n"/>
-      <c r="AV36" s="119" t="n"/>
-      <c r="AW36" s="119" t="n"/>
-      <c r="AX36" s="119" t="n"/>
-      <c r="AY36" s="119" t="n"/>
-      <c r="AZ36" s="119" t="n"/>
-      <c r="BA36" s="119" t="n"/>
-      <c r="BB36" s="119" t="n"/>
-      <c r="BC36" s="119" t="n"/>
-      <c r="BD36" s="119" t="n"/>
-      <c r="BE36" s="119" t="n"/>
-      <c r="BF36" s="119" t="n"/>
-      <c r="BG36" s="119" t="n"/>
-      <c r="BH36" s="119" t="n"/>
-      <c r="BI36" s="119" t="n"/>
-      <c r="BJ36" s="119" t="n"/>
-      <c r="BK36" s="119" t="n"/>
-      <c r="BL36" s="119" t="n"/>
-      <c r="BM36" s="119" t="n"/>
-      <c r="BN36" s="119" t="n"/>
-      <c r="BO36" s="119" t="n"/>
-      <c r="BP36" s="119" t="n"/>
-      <c r="BQ36" s="119" t="n"/>
-      <c r="BR36" s="119" t="n"/>
-      <c r="BS36" s="119" t="n"/>
-      <c r="BT36" s="119" t="n"/>
-      <c r="BU36" s="119" t="n"/>
-      <c r="BV36" s="119" t="n"/>
-      <c r="BW36" s="119" t="n"/>
-      <c r="BX36" s="119" t="n"/>
-      <c r="BY36" s="119" t="n"/>
-      <c r="BZ36" s="119" t="n"/>
-      <c r="CA36" s="119" t="n"/>
-      <c r="CB36" s="119" t="n"/>
-      <c r="CC36" s="119" t="n"/>
-      <c r="CD36" s="119" t="n"/>
-      <c r="CE36" s="119" t="n"/>
-      <c r="CF36" s="119" t="n"/>
-      <c r="CG36" s="119" t="n"/>
-      <c r="CH36" s="119" t="n"/>
-      <c r="CI36" s="119" t="n"/>
-      <c r="CJ36" s="119" t="n"/>
-      <c r="CK36" s="119" t="n"/>
-      <c r="CL36" s="119" t="n"/>
-      <c r="CM36" s="119" t="n"/>
-      <c r="CN36" s="119" t="n"/>
-      <c r="CO36" s="119" t="n"/>
-      <c r="CP36" s="119" t="n"/>
-      <c r="CQ36" s="119" t="n"/>
-      <c r="CR36" s="119" t="n"/>
-      <c r="CS36" s="119" t="n"/>
-      <c r="CT36" s="119" t="n"/>
-      <c r="CU36" s="119" t="n"/>
-      <c r="CV36" s="119" t="n"/>
-      <c r="CW36" s="119" t="n"/>
-      <c r="CX36" s="119" t="n"/>
-      <c r="CY36" s="119" t="n"/>
-      <c r="CZ36" s="119" t="n"/>
-      <c r="DA36" s="119" t="n"/>
-      <c r="DB36" s="119" t="n"/>
-      <c r="DC36" s="119" t="n"/>
-      <c r="DD36" s="119" t="n"/>
-      <c r="DE36" s="119" t="n"/>
-      <c r="DF36" s="119" t="n"/>
-      <c r="DG36" s="119" t="n"/>
-      <c r="DH36" s="119" t="n"/>
-      <c r="DI36" s="119" t="n"/>
-      <c r="DJ36" s="119" t="n"/>
-      <c r="DK36" s="119" t="n"/>
-      <c r="DL36" s="119" t="n"/>
-      <c r="DM36" s="119" t="n"/>
-      <c r="DN36" s="119" t="n"/>
-      <c r="DO36" s="119" t="n"/>
-      <c r="DP36" s="119" t="n"/>
-      <c r="DQ36" s="119" t="n"/>
-      <c r="DR36" s="119" t="n"/>
-      <c r="DS36" s="119" t="n"/>
-      <c r="DT36" s="119" t="n"/>
-      <c r="DU36" s="119" t="n"/>
-      <c r="DV36" s="119" t="n"/>
-      <c r="DW36" s="119" t="n"/>
-      <c r="DX36" s="119" t="n"/>
-      <c r="DY36" s="119" t="n"/>
-      <c r="DZ36" s="119" t="n"/>
-      <c r="EA36" s="119" t="n"/>
-      <c r="EB36" s="119" t="n"/>
-      <c r="EC36" s="119" t="n"/>
-      <c r="ED36" s="119" t="n"/>
-      <c r="EE36" s="119" t="n"/>
-      <c r="EF36" s="119" t="n"/>
-      <c r="EG36" s="119" t="n"/>
-      <c r="EH36" s="119" t="n"/>
-      <c r="EI36" s="119" t="n"/>
-      <c r="EJ36" s="119" t="n"/>
-      <c r="EK36" s="119" t="n"/>
-      <c r="EL36" s="119" t="n"/>
-      <c r="EM36" s="119" t="n"/>
-      <c r="EN36" s="119" t="n"/>
-      <c r="EO36" s="119" t="n"/>
-      <c r="EP36" s="119" t="n"/>
-      <c r="EQ36" s="119" t="n"/>
-      <c r="ER36" s="119" t="n"/>
-      <c r="ES36" s="119" t="n"/>
-      <c r="ET36" s="119" t="n"/>
-      <c r="EU36" s="119" t="n"/>
-      <c r="EV36" s="119" t="n"/>
-      <c r="EW36" s="119" t="n"/>
-      <c r="EX36" s="119" t="n"/>
-      <c r="EY36" s="119" t="n"/>
-      <c r="EZ36" s="119" t="n"/>
-      <c r="FA36" s="119" t="n"/>
-      <c r="FB36" s="119" t="n"/>
-      <c r="FC36" s="119" t="n"/>
-      <c r="FD36" s="119" t="n"/>
-      <c r="FE36" s="119" t="n"/>
-      <c r="FF36" s="119" t="n"/>
-      <c r="FG36" s="119" t="n"/>
-      <c r="FH36" s="119" t="n"/>
-      <c r="FI36" s="119" t="n"/>
-      <c r="FJ36" s="119" t="n"/>
-      <c r="FK36" s="119" t="n"/>
-      <c r="FL36" s="119" t="n"/>
-      <c r="FM36" s="119" t="n"/>
-      <c r="FN36" s="119" t="n"/>
-      <c r="FO36" s="119" t="n"/>
-      <c r="FP36" s="119" t="n"/>
-      <c r="FQ36" s="119" t="n"/>
-      <c r="FR36" s="119" t="n"/>
-      <c r="FS36" s="119" t="n"/>
-      <c r="FT36" s="119" t="n"/>
-      <c r="FU36" s="119" t="n"/>
-      <c r="FV36" s="119" t="n"/>
-      <c r="FW36" s="119" t="n"/>
-      <c r="FX36" s="119" t="n"/>
-      <c r="FY36" s="119" t="n"/>
-      <c r="FZ36" s="119" t="n"/>
-      <c r="GA36" s="119" t="n"/>
-      <c r="GB36" s="119" t="n"/>
-      <c r="GC36" s="119" t="n"/>
-      <c r="GD36" s="119" t="n"/>
-      <c r="GE36" s="119" t="n"/>
-      <c r="GF36" s="119" t="n"/>
-      <c r="GG36" s="119" t="n"/>
-      <c r="GH36" s="119" t="n"/>
-      <c r="GI36" s="119" t="n"/>
-      <c r="GJ36" s="119" t="n"/>
-      <c r="GK36" s="119" t="n"/>
-      <c r="GL36" s="119" t="n"/>
-      <c r="GM36" s="119" t="n"/>
-      <c r="GN36" s="119" t="n"/>
-      <c r="GO36" s="119" t="n"/>
-      <c r="GP36" s="119" t="n"/>
-      <c r="GQ36" s="119" t="n"/>
-      <c r="GR36" s="119" t="n"/>
-      <c r="GS36" s="119" t="n"/>
-      <c r="GT36" s="119" t="n"/>
-      <c r="GU36" s="119" t="n"/>
-      <c r="GV36" s="119" t="n"/>
-      <c r="GW36" s="119" t="n"/>
-      <c r="GX36" s="119" t="n"/>
-      <c r="GY36" s="119" t="n"/>
-      <c r="GZ36" s="119" t="n"/>
-      <c r="HA36" s="119" t="n"/>
-      <c r="HB36" s="119" t="n"/>
-      <c r="HC36" s="119" t="n"/>
-      <c r="HD36" s="119" t="n"/>
-      <c r="HE36" s="119" t="n"/>
-      <c r="HF36" s="119" t="n"/>
-      <c r="HG36" s="119" t="n"/>
-      <c r="HH36" s="119" t="n"/>
-      <c r="HI36" s="119" t="n"/>
-      <c r="HJ36" s="119" t="n"/>
-      <c r="HK36" s="119" t="n"/>
-      <c r="HL36" s="119" t="n"/>
-      <c r="HM36" s="119" t="n"/>
-      <c r="HN36" s="119" t="n"/>
-      <c r="HO36" s="119" t="n"/>
-      <c r="HP36" s="119" t="n"/>
-      <c r="HQ36" s="119" t="n"/>
-      <c r="HR36" s="119" t="n"/>
-      <c r="HS36" s="119" t="n"/>
-      <c r="HT36" s="119" t="n"/>
-      <c r="HU36" s="119" t="n"/>
-    </row>
-    <row r="37" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A37" s="58" t="n"/>
-      <c r="B37" s="121" t="n"/>
-      <c r="C37" s="122" t="n"/>
-      <c r="D37" s="123" t="n"/>
-      <c r="E37" s="124" t="n"/>
-      <c r="F37" s="55" t="n"/>
-      <c r="G37" s="125" t="n"/>
-      <c r="H37" s="56" t="n"/>
-      <c r="I37" s="57" t="n"/>
-      <c r="J37" s="125" t="n"/>
-      <c r="K37" s="126" t="n"/>
-      <c r="L37" s="59" t="n"/>
-      <c r="M37" s="60" t="n"/>
-      <c r="N37" s="57" t="n"/>
-      <c r="O37" s="59" t="n"/>
-      <c r="P37" s="57" t="n"/>
-      <c r="Q37" s="57" t="n"/>
-      <c r="R37" s="57" t="n"/>
-      <c r="S37" s="57" t="n"/>
-      <c r="T37" s="57" t="n"/>
-      <c r="U37" s="57" t="n"/>
-      <c r="V37" s="57" t="n"/>
-      <c r="W37" s="57">
-        <f>SUM(K37:U37)</f>
-        <v/>
-      </c>
-      <c r="X37" s="57" t="n"/>
-      <c r="Y37" s="57" t="n"/>
-      <c r="Z37" s="59" t="n"/>
-      <c r="AA37" s="57">
-        <f>SUM(X37:Z37)</f>
-        <v/>
-      </c>
-      <c r="AB37" s="57">
-        <f>+W37+AA37</f>
-        <v/>
-      </c>
-      <c r="AC37" s="63" t="n"/>
-      <c r="AD37" s="149" t="n"/>
-      <c r="AE37" s="119" t="n"/>
-      <c r="AF37" s="119" t="n"/>
-      <c r="AG37" s="119" t="n"/>
-      <c r="AH37" s="119" t="n"/>
-      <c r="AI37" s="119" t="n"/>
-      <c r="AJ37" s="119" t="n"/>
-      <c r="AK37" s="119" t="n"/>
-      <c r="AL37" s="119" t="n"/>
-      <c r="AM37" s="119" t="n"/>
-      <c r="AN37" s="119" t="n"/>
-      <c r="AO37" s="119" t="n"/>
-      <c r="AP37" s="119" t="n"/>
-      <c r="AQ37" s="119" t="n"/>
-      <c r="AR37" s="119" t="n"/>
-      <c r="AS37" s="119" t="n"/>
-      <c r="AT37" s="119" t="n"/>
-      <c r="AU37" s="119" t="n"/>
-      <c r="AV37" s="119" t="n"/>
-      <c r="AW37" s="119" t="n"/>
-      <c r="AX37" s="119" t="n"/>
-      <c r="AY37" s="119" t="n"/>
-      <c r="AZ37" s="119" t="n"/>
-      <c r="BA37" s="119" t="n"/>
-      <c r="BB37" s="119" t="n"/>
-      <c r="BC37" s="119" t="n"/>
-      <c r="BD37" s="119" t="n"/>
-      <c r="BE37" s="119" t="n"/>
-      <c r="BF37" s="119" t="n"/>
-      <c r="BG37" s="119" t="n"/>
-      <c r="BH37" s="119" t="n"/>
-      <c r="BI37" s="119" t="n"/>
-      <c r="BJ37" s="119" t="n"/>
-      <c r="BK37" s="119" t="n"/>
-      <c r="BL37" s="119" t="n"/>
-      <c r="BM37" s="119" t="n"/>
-      <c r="BN37" s="119" t="n"/>
-      <c r="BO37" s="119" t="n"/>
-      <c r="BP37" s="119" t="n"/>
-      <c r="BQ37" s="119" t="n"/>
-      <c r="BR37" s="119" t="n"/>
-      <c r="BS37" s="119" t="n"/>
-      <c r="BT37" s="119" t="n"/>
-      <c r="BU37" s="119" t="n"/>
-      <c r="BV37" s="119" t="n"/>
-      <c r="BW37" s="119" t="n"/>
-      <c r="BX37" s="119" t="n"/>
-      <c r="BY37" s="119" t="n"/>
-      <c r="BZ37" s="119" t="n"/>
-      <c r="CA37" s="119" t="n"/>
-      <c r="CB37" s="119" t="n"/>
-      <c r="CC37" s="119" t="n"/>
-      <c r="CD37" s="119" t="n"/>
-      <c r="CE37" s="119" t="n"/>
-      <c r="CF37" s="119" t="n"/>
-      <c r="CG37" s="119" t="n"/>
-      <c r="CH37" s="119" t="n"/>
-      <c r="CI37" s="119" t="n"/>
-      <c r="CJ37" s="119" t="n"/>
-      <c r="CK37" s="119" t="n"/>
-      <c r="CL37" s="119" t="n"/>
-      <c r="CM37" s="119" t="n"/>
-      <c r="CN37" s="119" t="n"/>
-      <c r="CO37" s="119" t="n"/>
-      <c r="CP37" s="119" t="n"/>
-      <c r="CQ37" s="119" t="n"/>
-      <c r="CR37" s="119" t="n"/>
-      <c r="CS37" s="119" t="n"/>
-      <c r="CT37" s="119" t="n"/>
-      <c r="CU37" s="119" t="n"/>
-      <c r="CV37" s="119" t="n"/>
-      <c r="CW37" s="119" t="n"/>
-      <c r="CX37" s="119" t="n"/>
-      <c r="CY37" s="119" t="n"/>
-      <c r="CZ37" s="119" t="n"/>
-      <c r="DA37" s="119" t="n"/>
-      <c r="DB37" s="119" t="n"/>
-      <c r="DC37" s="119" t="n"/>
-      <c r="DD37" s="119" t="n"/>
-      <c r="DE37" s="119" t="n"/>
-      <c r="DF37" s="119" t="n"/>
-      <c r="DG37" s="119" t="n"/>
-      <c r="DH37" s="119" t="n"/>
-      <c r="DI37" s="119" t="n"/>
-      <c r="DJ37" s="119" t="n"/>
-      <c r="DK37" s="119" t="n"/>
-      <c r="DL37" s="119" t="n"/>
-      <c r="DM37" s="119" t="n"/>
-      <c r="DN37" s="119" t="n"/>
-      <c r="DO37" s="119" t="n"/>
-      <c r="DP37" s="119" t="n"/>
-      <c r="DQ37" s="119" t="n"/>
-      <c r="DR37" s="119" t="n"/>
-      <c r="DS37" s="119" t="n"/>
-      <c r="DT37" s="119" t="n"/>
-      <c r="DU37" s="119" t="n"/>
-      <c r="DV37" s="119" t="n"/>
-      <c r="DW37" s="119" t="n"/>
-      <c r="DX37" s="119" t="n"/>
-      <c r="DY37" s="119" t="n"/>
-      <c r="DZ37" s="119" t="n"/>
-      <c r="EA37" s="119" t="n"/>
-      <c r="EB37" s="119" t="n"/>
-      <c r="EC37" s="119" t="n"/>
-      <c r="ED37" s="119" t="n"/>
-      <c r="EE37" s="119" t="n"/>
-      <c r="EF37" s="119" t="n"/>
-      <c r="EG37" s="119" t="n"/>
-      <c r="EH37" s="119" t="n"/>
-      <c r="EI37" s="119" t="n"/>
-      <c r="EJ37" s="119" t="n"/>
-      <c r="EK37" s="119" t="n"/>
-      <c r="EL37" s="119" t="n"/>
-      <c r="EM37" s="119" t="n"/>
-      <c r="EN37" s="119" t="n"/>
-      <c r="EO37" s="119" t="n"/>
-      <c r="EP37" s="119" t="n"/>
-      <c r="EQ37" s="119" t="n"/>
-      <c r="ER37" s="119" t="n"/>
-      <c r="ES37" s="119" t="n"/>
-      <c r="ET37" s="119" t="n"/>
-      <c r="EU37" s="119" t="n"/>
-      <c r="EV37" s="119" t="n"/>
-      <c r="EW37" s="119" t="n"/>
-      <c r="EX37" s="119" t="n"/>
-      <c r="EY37" s="119" t="n"/>
-      <c r="EZ37" s="119" t="n"/>
-      <c r="FA37" s="119" t="n"/>
-      <c r="FB37" s="119" t="n"/>
-      <c r="FC37" s="119" t="n"/>
-      <c r="FD37" s="119" t="n"/>
-      <c r="FE37" s="119" t="n"/>
-      <c r="FF37" s="119" t="n"/>
-      <c r="FG37" s="119" t="n"/>
-      <c r="FH37" s="119" t="n"/>
-      <c r="FI37" s="119" t="n"/>
-      <c r="FJ37" s="119" t="n"/>
-      <c r="FK37" s="119" t="n"/>
-      <c r="FL37" s="119" t="n"/>
-      <c r="FM37" s="119" t="n"/>
-      <c r="FN37" s="119" t="n"/>
-      <c r="FO37" s="119" t="n"/>
-      <c r="FP37" s="119" t="n"/>
-      <c r="FQ37" s="119" t="n"/>
-      <c r="FR37" s="119" t="n"/>
-      <c r="FS37" s="119" t="n"/>
-      <c r="FT37" s="119" t="n"/>
-      <c r="FU37" s="119" t="n"/>
-      <c r="FV37" s="119" t="n"/>
-      <c r="FW37" s="119" t="n"/>
-      <c r="FX37" s="119" t="n"/>
-      <c r="FY37" s="119" t="n"/>
-      <c r="FZ37" s="119" t="n"/>
-      <c r="GA37" s="119" t="n"/>
-      <c r="GB37" s="119" t="n"/>
-      <c r="GC37" s="119" t="n"/>
-      <c r="GD37" s="119" t="n"/>
-      <c r="GE37" s="119" t="n"/>
-      <c r="GF37" s="119" t="n"/>
-      <c r="GG37" s="119" t="n"/>
-      <c r="GH37" s="119" t="n"/>
-      <c r="GI37" s="119" t="n"/>
-      <c r="GJ37" s="119" t="n"/>
-      <c r="GK37" s="119" t="n"/>
-      <c r="GL37" s="119" t="n"/>
-      <c r="GM37" s="119" t="n"/>
-      <c r="GN37" s="119" t="n"/>
-      <c r="GO37" s="119" t="n"/>
-      <c r="GP37" s="119" t="n"/>
-      <c r="GQ37" s="119" t="n"/>
-      <c r="GR37" s="119" t="n"/>
-      <c r="GS37" s="119" t="n"/>
-      <c r="GT37" s="119" t="n"/>
-      <c r="GU37" s="119" t="n"/>
-      <c r="GV37" s="119" t="n"/>
-      <c r="GW37" s="119" t="n"/>
-      <c r="GX37" s="119" t="n"/>
-      <c r="GY37" s="119" t="n"/>
-      <c r="GZ37" s="119" t="n"/>
-      <c r="HA37" s="119" t="n"/>
-      <c r="HB37" s="119" t="n"/>
-      <c r="HC37" s="119" t="n"/>
-      <c r="HD37" s="119" t="n"/>
-      <c r="HE37" s="119" t="n"/>
-      <c r="HF37" s="119" t="n"/>
-      <c r="HG37" s="119" t="n"/>
-      <c r="HH37" s="119" t="n"/>
-      <c r="HI37" s="119" t="n"/>
-      <c r="HJ37" s="119" t="n"/>
-      <c r="HK37" s="119" t="n"/>
-      <c r="HL37" s="119" t="n"/>
-      <c r="HM37" s="119" t="n"/>
-      <c r="HN37" s="119" t="n"/>
-      <c r="HO37" s="119" t="n"/>
-      <c r="HP37" s="119" t="n"/>
-      <c r="HQ37" s="119" t="n"/>
-      <c r="HR37" s="119" t="n"/>
-      <c r="HS37" s="119" t="n"/>
-      <c r="HT37" s="119" t="n"/>
-      <c r="HU37" s="119" t="n"/>
-    </row>
-    <row r="38" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A38" s="58" t="n"/>
-      <c r="B38" s="121" t="n"/>
-      <c r="C38" s="122" t="n"/>
-      <c r="D38" s="123" t="n"/>
-      <c r="E38" s="124" t="n"/>
-      <c r="F38" s="55" t="n"/>
-      <c r="G38" s="125" t="n"/>
-      <c r="H38" s="56" t="n"/>
-      <c r="I38" s="57" t="n"/>
-      <c r="J38" s="125" t="n"/>
-      <c r="K38" s="126" t="n"/>
-      <c r="L38" s="59" t="n"/>
-      <c r="M38" s="60" t="n"/>
-      <c r="N38" s="57" t="n"/>
-      <c r="O38" s="59" t="n"/>
-      <c r="P38" s="57" t="n"/>
-      <c r="Q38" s="57" t="n"/>
-      <c r="R38" s="57" t="n"/>
-      <c r="S38" s="57" t="n"/>
-      <c r="T38" s="57" t="n"/>
-      <c r="U38" s="57" t="n"/>
-      <c r="V38" s="57" t="n"/>
-      <c r="W38" s="57">
-        <f>SUM(K38:U38)</f>
-        <v/>
-      </c>
-      <c r="X38" s="57" t="n"/>
-      <c r="Y38" s="57" t="n"/>
-      <c r="Z38" s="59" t="n"/>
-      <c r="AA38" s="57">
-        <f>SUM(X38:Z38)</f>
-        <v/>
-      </c>
-      <c r="AB38" s="57">
-        <f>+W38+AA38</f>
-        <v/>
-      </c>
-      <c r="AC38" s="63" t="n"/>
-      <c r="AD38" s="149" t="n"/>
-      <c r="AE38" s="119" t="n"/>
-      <c r="AF38" s="119" t="n"/>
-      <c r="AG38" s="119" t="n"/>
-      <c r="AH38" s="119" t="n"/>
-      <c r="AI38" s="119" t="n"/>
-      <c r="AJ38" s="119" t="n"/>
-      <c r="AK38" s="119" t="n"/>
-      <c r="AL38" s="119" t="n"/>
-      <c r="AM38" s="119" t="n"/>
-      <c r="AN38" s="119" t="n"/>
-      <c r="AO38" s="119" t="n"/>
-      <c r="AP38" s="119" t="n"/>
-      <c r="AQ38" s="119" t="n"/>
-      <c r="AR38" s="119" t="n"/>
-      <c r="AS38" s="119" t="n"/>
-      <c r="AT38" s="119" t="n"/>
-      <c r="AU38" s="119" t="n"/>
-      <c r="AV38" s="119" t="n"/>
-      <c r="AW38" s="119" t="n"/>
-      <c r="AX38" s="119" t="n"/>
-      <c r="AY38" s="119" t="n"/>
-      <c r="AZ38" s="119" t="n"/>
-      <c r="BA38" s="119" t="n"/>
-      <c r="BB38" s="119" t="n"/>
-      <c r="BC38" s="119" t="n"/>
-      <c r="BD38" s="119" t="n"/>
-      <c r="BE38" s="119" t="n"/>
-      <c r="BF38" s="119" t="n"/>
-      <c r="BG38" s="119" t="n"/>
-      <c r="BH38" s="119" t="n"/>
-      <c r="BI38" s="119" t="n"/>
-      <c r="BJ38" s="119" t="n"/>
-      <c r="BK38" s="119" t="n"/>
-      <c r="BL38" s="119" t="n"/>
-      <c r="BM38" s="119" t="n"/>
-      <c r="BN38" s="119" t="n"/>
-      <c r="BO38" s="119" t="n"/>
-      <c r="BP38" s="119" t="n"/>
-      <c r="BQ38" s="119" t="n"/>
-      <c r="BR38" s="119" t="n"/>
-      <c r="BS38" s="119" t="n"/>
-      <c r="BT38" s="119" t="n"/>
-      <c r="BU38" s="119" t="n"/>
-      <c r="BV38" s="119" t="n"/>
-      <c r="BW38" s="119" t="n"/>
-      <c r="BX38" s="119" t="n"/>
-      <c r="BY38" s="119" t="n"/>
-      <c r="BZ38" s="119" t="n"/>
-      <c r="CA38" s="119" t="n"/>
-      <c r="CB38" s="119" t="n"/>
-      <c r="CC38" s="119" t="n"/>
-      <c r="CD38" s="119" t="n"/>
-      <c r="CE38" s="119" t="n"/>
-      <c r="CF38" s="119" t="n"/>
-      <c r="CG38" s="119" t="n"/>
-      <c r="CH38" s="119" t="n"/>
-      <c r="CI38" s="119" t="n"/>
-      <c r="CJ38" s="119" t="n"/>
-      <c r="CK38" s="119" t="n"/>
-      <c r="CL38" s="119" t="n"/>
-      <c r="CM38" s="119" t="n"/>
-      <c r="CN38" s="119" t="n"/>
-      <c r="CO38" s="119" t="n"/>
-      <c r="CP38" s="119" t="n"/>
-      <c r="CQ38" s="119" t="n"/>
-      <c r="CR38" s="119" t="n"/>
-      <c r="CS38" s="119" t="n"/>
-      <c r="CT38" s="119" t="n"/>
-      <c r="CU38" s="119" t="n"/>
-      <c r="CV38" s="119" t="n"/>
-      <c r="CW38" s="119" t="n"/>
-      <c r="CX38" s="119" t="n"/>
-      <c r="CY38" s="119" t="n"/>
-      <c r="CZ38" s="119" t="n"/>
-      <c r="DA38" s="119" t="n"/>
-      <c r="DB38" s="119" t="n"/>
-      <c r="DC38" s="119" t="n"/>
-      <c r="DD38" s="119" t="n"/>
-      <c r="DE38" s="119" t="n"/>
-      <c r="DF38" s="119" t="n"/>
-      <c r="DG38" s="119" t="n"/>
-      <c r="DH38" s="119" t="n"/>
-      <c r="DI38" s="119" t="n"/>
-      <c r="DJ38" s="119" t="n"/>
-      <c r="DK38" s="119" t="n"/>
-      <c r="DL38" s="119" t="n"/>
-      <c r="DM38" s="119" t="n"/>
-      <c r="DN38" s="119" t="n"/>
-      <c r="DO38" s="119" t="n"/>
-      <c r="DP38" s="119" t="n"/>
-      <c r="DQ38" s="119" t="n"/>
-      <c r="DR38" s="119" t="n"/>
-      <c r="DS38" s="119" t="n"/>
-      <c r="DT38" s="119" t="n"/>
-      <c r="DU38" s="119" t="n"/>
-      <c r="DV38" s="119" t="n"/>
-      <c r="DW38" s="119" t="n"/>
-      <c r="DX38" s="119" t="n"/>
-      <c r="DY38" s="119" t="n"/>
-      <c r="DZ38" s="119" t="n"/>
-      <c r="EA38" s="119" t="n"/>
-      <c r="EB38" s="119" t="n"/>
-      <c r="EC38" s="119" t="n"/>
-      <c r="ED38" s="119" t="n"/>
-      <c r="EE38" s="119" t="n"/>
-      <c r="EF38" s="119" t="n"/>
-      <c r="EG38" s="119" t="n"/>
-      <c r="EH38" s="119" t="n"/>
-      <c r="EI38" s="119" t="n"/>
-      <c r="EJ38" s="119" t="n"/>
-      <c r="EK38" s="119" t="n"/>
-      <c r="EL38" s="119" t="n"/>
-      <c r="EM38" s="119" t="n"/>
-      <c r="EN38" s="119" t="n"/>
-      <c r="EO38" s="119" t="n"/>
-      <c r="EP38" s="119" t="n"/>
-      <c r="EQ38" s="119" t="n"/>
-      <c r="ER38" s="119" t="n"/>
-      <c r="ES38" s="119" t="n"/>
-      <c r="ET38" s="119" t="n"/>
-      <c r="EU38" s="119" t="n"/>
-      <c r="EV38" s="119" t="n"/>
-      <c r="EW38" s="119" t="n"/>
-      <c r="EX38" s="119" t="n"/>
-      <c r="EY38" s="119" t="n"/>
-      <c r="EZ38" s="119" t="n"/>
-      <c r="FA38" s="119" t="n"/>
-      <c r="FB38" s="119" t="n"/>
-      <c r="FC38" s="119" t="n"/>
-      <c r="FD38" s="119" t="n"/>
-      <c r="FE38" s="119" t="n"/>
-      <c r="FF38" s="119" t="n"/>
-      <c r="FG38" s="119" t="n"/>
-      <c r="FH38" s="119" t="n"/>
-      <c r="FI38" s="119" t="n"/>
-      <c r="FJ38" s="119" t="n"/>
-      <c r="FK38" s="119" t="n"/>
-      <c r="FL38" s="119" t="n"/>
-      <c r="FM38" s="119" t="n"/>
-      <c r="FN38" s="119" t="n"/>
-      <c r="FO38" s="119" t="n"/>
-      <c r="FP38" s="119" t="n"/>
-      <c r="FQ38" s="119" t="n"/>
-      <c r="FR38" s="119" t="n"/>
-      <c r="FS38" s="119" t="n"/>
-      <c r="FT38" s="119" t="n"/>
-      <c r="FU38" s="119" t="n"/>
-      <c r="FV38" s="119" t="n"/>
-      <c r="FW38" s="119" t="n"/>
-      <c r="FX38" s="119" t="n"/>
-      <c r="FY38" s="119" t="n"/>
-      <c r="FZ38" s="119" t="n"/>
-      <c r="GA38" s="119" t="n"/>
-      <c r="GB38" s="119" t="n"/>
-      <c r="GC38" s="119" t="n"/>
-      <c r="GD38" s="119" t="n"/>
-      <c r="GE38" s="119" t="n"/>
-      <c r="GF38" s="119" t="n"/>
-      <c r="GG38" s="119" t="n"/>
-      <c r="GH38" s="119" t="n"/>
-      <c r="GI38" s="119" t="n"/>
-      <c r="GJ38" s="119" t="n"/>
-      <c r="GK38" s="119" t="n"/>
-      <c r="GL38" s="119" t="n"/>
-      <c r="GM38" s="119" t="n"/>
-      <c r="GN38" s="119" t="n"/>
-      <c r="GO38" s="119" t="n"/>
-      <c r="GP38" s="119" t="n"/>
-      <c r="GQ38" s="119" t="n"/>
-      <c r="GR38" s="119" t="n"/>
-      <c r="GS38" s="119" t="n"/>
-      <c r="GT38" s="119" t="n"/>
-      <c r="GU38" s="119" t="n"/>
-      <c r="GV38" s="119" t="n"/>
-      <c r="GW38" s="119" t="n"/>
-      <c r="GX38" s="119" t="n"/>
-      <c r="GY38" s="119" t="n"/>
-      <c r="GZ38" s="119" t="n"/>
-      <c r="HA38" s="119" t="n"/>
-      <c r="HB38" s="119" t="n"/>
-      <c r="HC38" s="119" t="n"/>
-      <c r="HD38" s="119" t="n"/>
-      <c r="HE38" s="119" t="n"/>
-      <c r="HF38" s="119" t="n"/>
-      <c r="HG38" s="119" t="n"/>
-      <c r="HH38" s="119" t="n"/>
-      <c r="HI38" s="119" t="n"/>
-      <c r="HJ38" s="119" t="n"/>
-      <c r="HK38" s="119" t="n"/>
-      <c r="HL38" s="119" t="n"/>
-      <c r="HM38" s="119" t="n"/>
-      <c r="HN38" s="119" t="n"/>
-      <c r="HO38" s="119" t="n"/>
-      <c r="HP38" s="119" t="n"/>
-      <c r="HQ38" s="119" t="n"/>
-      <c r="HR38" s="119" t="n"/>
-      <c r="HS38" s="119" t="n"/>
-      <c r="HT38" s="119" t="n"/>
-      <c r="HU38" s="119" t="n"/>
-    </row>
-    <row r="39" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A39" s="58" t="n"/>
-      <c r="B39" s="121" t="n"/>
-      <c r="C39" s="122" t="n"/>
-      <c r="D39" s="123" t="n"/>
-      <c r="E39" s="124" t="n"/>
-      <c r="F39" s="55" t="n"/>
-      <c r="G39" s="125" t="n"/>
-      <c r="H39" s="56" t="n"/>
-      <c r="I39" s="57" t="n"/>
-      <c r="J39" s="125" t="n"/>
-      <c r="K39" s="126" t="n"/>
-      <c r="L39" s="59" t="n"/>
-      <c r="M39" s="60" t="n"/>
-      <c r="N39" s="57" t="n"/>
-      <c r="O39" s="59" t="n"/>
-      <c r="P39" s="57" t="n"/>
-      <c r="Q39" s="57" t="n"/>
-      <c r="R39" s="57" t="n"/>
-      <c r="S39" s="57" t="n"/>
-      <c r="T39" s="57" t="n"/>
-      <c r="U39" s="57" t="n"/>
-      <c r="V39" s="57" t="n"/>
-      <c r="W39" s="57">
-        <f>SUM(K39:U39)</f>
-        <v/>
-      </c>
-      <c r="X39" s="57" t="n"/>
-      <c r="Y39" s="57" t="n"/>
-      <c r="Z39" s="59" t="n"/>
-      <c r="AA39" s="57">
-        <f>SUM(X39:Z39)</f>
-        <v/>
-      </c>
-      <c r="AB39" s="57">
-        <f>+W39+AA39</f>
-        <v/>
-      </c>
-      <c r="AC39" s="63" t="n"/>
-      <c r="AD39" s="149" t="n"/>
-      <c r="AE39" s="119" t="n"/>
-      <c r="AF39" s="119" t="n"/>
-      <c r="AG39" s="119" t="n"/>
-      <c r="AH39" s="119" t="n"/>
-      <c r="AI39" s="119" t="n"/>
-      <c r="AJ39" s="119" t="n"/>
-      <c r="AK39" s="119" t="n"/>
-      <c r="AL39" s="119" t="n"/>
-      <c r="AM39" s="119" t="n"/>
-      <c r="AN39" s="119" t="n"/>
-      <c r="AO39" s="119" t="n"/>
-      <c r="AP39" s="119" t="n"/>
-      <c r="AQ39" s="119" t="n"/>
-      <c r="AR39" s="119" t="n"/>
-      <c r="AS39" s="119" t="n"/>
-      <c r="AT39" s="119" t="n"/>
-      <c r="AU39" s="119" t="n"/>
-      <c r="AV39" s="119" t="n"/>
-      <c r="AW39" s="119" t="n"/>
-      <c r="AX39" s="119" t="n"/>
-      <c r="AY39" s="119" t="n"/>
-      <c r="AZ39" s="119" t="n"/>
-      <c r="BA39" s="119" t="n"/>
-      <c r="BB39" s="119" t="n"/>
-      <c r="BC39" s="119" t="n"/>
-      <c r="BD39" s="119" t="n"/>
-      <c r="BE39" s="119" t="n"/>
-      <c r="BF39" s="119" t="n"/>
-      <c r="BG39" s="119" t="n"/>
-      <c r="BH39" s="119" t="n"/>
-      <c r="BI39" s="119" t="n"/>
-      <c r="BJ39" s="119" t="n"/>
-      <c r="BK39" s="119" t="n"/>
-      <c r="BL39" s="119" t="n"/>
-      <c r="BM39" s="119" t="n"/>
-      <c r="BN39" s="119" t="n"/>
-      <c r="BO39" s="119" t="n"/>
-      <c r="BP39" s="119" t="n"/>
-      <c r="BQ39" s="119" t="n"/>
-      <c r="BR39" s="119" t="n"/>
-      <c r="BS39" s="119" t="n"/>
-      <c r="BT39" s="119" t="n"/>
-      <c r="BU39" s="119" t="n"/>
-      <c r="BV39" s="119" t="n"/>
-      <c r="BW39" s="119" t="n"/>
-      <c r="BX39" s="119" t="n"/>
-      <c r="BY39" s="119" t="n"/>
-      <c r="BZ39" s="119" t="n"/>
-      <c r="CA39" s="119" t="n"/>
-      <c r="CB39" s="119" t="n"/>
-      <c r="CC39" s="119" t="n"/>
-      <c r="CD39" s="119" t="n"/>
-      <c r="CE39" s="119" t="n"/>
-      <c r="CF39" s="119" t="n"/>
-      <c r="CG39" s="119" t="n"/>
-      <c r="CH39" s="119" t="n"/>
-      <c r="CI39" s="119" t="n"/>
-      <c r="CJ39" s="119" t="n"/>
-      <c r="CK39" s="119" t="n"/>
-      <c r="CL39" s="119" t="n"/>
-      <c r="CM39" s="119" t="n"/>
-      <c r="CN39" s="119" t="n"/>
-      <c r="CO39" s="119" t="n"/>
-      <c r="CP39" s="119" t="n"/>
-      <c r="CQ39" s="119" t="n"/>
-      <c r="CR39" s="119" t="n"/>
-      <c r="CS39" s="119" t="n"/>
-      <c r="CT39" s="119" t="n"/>
-      <c r="CU39" s="119" t="n"/>
-      <c r="CV39" s="119" t="n"/>
-      <c r="CW39" s="119" t="n"/>
-      <c r="CX39" s="119" t="n"/>
-      <c r="CY39" s="119" t="n"/>
-      <c r="CZ39" s="119" t="n"/>
-      <c r="DA39" s="119" t="n"/>
-      <c r="DB39" s="119" t="n"/>
-      <c r="DC39" s="119" t="n"/>
-      <c r="DD39" s="119" t="n"/>
-      <c r="DE39" s="119" t="n"/>
-      <c r="DF39" s="119" t="n"/>
-      <c r="DG39" s="119" t="n"/>
-      <c r="DH39" s="119" t="n"/>
-      <c r="DI39" s="119" t="n"/>
-      <c r="DJ39" s="119" t="n"/>
-      <c r="DK39" s="119" t="n"/>
-      <c r="DL39" s="119" t="n"/>
-      <c r="DM39" s="119" t="n"/>
-      <c r="DN39" s="119" t="n"/>
-      <c r="DO39" s="119" t="n"/>
-      <c r="DP39" s="119" t="n"/>
-      <c r="DQ39" s="119" t="n"/>
-      <c r="DR39" s="119" t="n"/>
-      <c r="DS39" s="119" t="n"/>
-      <c r="DT39" s="119" t="n"/>
-      <c r="DU39" s="119" t="n"/>
-      <c r="DV39" s="119" t="n"/>
-      <c r="DW39" s="119" t="n"/>
-      <c r="DX39" s="119" t="n"/>
-      <c r="DY39" s="119" t="n"/>
-      <c r="DZ39" s="119" t="n"/>
-      <c r="EA39" s="119" t="n"/>
-      <c r="EB39" s="119" t="n"/>
-      <c r="EC39" s="119" t="n"/>
-      <c r="ED39" s="119" t="n"/>
-      <c r="EE39" s="119" t="n"/>
-      <c r="EF39" s="119" t="n"/>
-      <c r="EG39" s="119" t="n"/>
-      <c r="EH39" s="119" t="n"/>
-      <c r="EI39" s="119" t="n"/>
-      <c r="EJ39" s="119" t="n"/>
-      <c r="EK39" s="119" t="n"/>
-      <c r="EL39" s="119" t="n"/>
-      <c r="EM39" s="119" t="n"/>
-      <c r="EN39" s="119" t="n"/>
-      <c r="EO39" s="119" t="n"/>
-      <c r="EP39" s="119" t="n"/>
-      <c r="EQ39" s="119" t="n"/>
-      <c r="ER39" s="119" t="n"/>
-      <c r="ES39" s="119" t="n"/>
-      <c r="ET39" s="119" t="n"/>
-      <c r="EU39" s="119" t="n"/>
-      <c r="EV39" s="119" t="n"/>
-      <c r="EW39" s="119" t="n"/>
-      <c r="EX39" s="119" t="n"/>
-      <c r="EY39" s="119" t="n"/>
-      <c r="EZ39" s="119" t="n"/>
-      <c r="FA39" s="119" t="n"/>
-      <c r="FB39" s="119" t="n"/>
-      <c r="FC39" s="119" t="n"/>
-      <c r="FD39" s="119" t="n"/>
-      <c r="FE39" s="119" t="n"/>
-      <c r="FF39" s="119" t="n"/>
-      <c r="FG39" s="119" t="n"/>
-      <c r="FH39" s="119" t="n"/>
-      <c r="FI39" s="119" t="n"/>
-      <c r="FJ39" s="119" t="n"/>
-      <c r="FK39" s="119" t="n"/>
-      <c r="FL39" s="119" t="n"/>
-      <c r="FM39" s="119" t="n"/>
-      <c r="FN39" s="119" t="n"/>
-      <c r="FO39" s="119" t="n"/>
-      <c r="FP39" s="119" t="n"/>
-      <c r="FQ39" s="119" t="n"/>
-      <c r="FR39" s="119" t="n"/>
-      <c r="FS39" s="119" t="n"/>
-      <c r="FT39" s="119" t="n"/>
-      <c r="FU39" s="119" t="n"/>
-      <c r="FV39" s="119" t="n"/>
-      <c r="FW39" s="119" t="n"/>
-      <c r="FX39" s="119" t="n"/>
-      <c r="FY39" s="119" t="n"/>
-      <c r="FZ39" s="119" t="n"/>
-      <c r="GA39" s="119" t="n"/>
-      <c r="GB39" s="119" t="n"/>
-      <c r="GC39" s="119" t="n"/>
-      <c r="GD39" s="119" t="n"/>
-      <c r="GE39" s="119" t="n"/>
-      <c r="GF39" s="119" t="n"/>
-      <c r="GG39" s="119" t="n"/>
-      <c r="GH39" s="119" t="n"/>
-      <c r="GI39" s="119" t="n"/>
-      <c r="GJ39" s="119" t="n"/>
-      <c r="GK39" s="119" t="n"/>
-      <c r="GL39" s="119" t="n"/>
-      <c r="GM39" s="119" t="n"/>
-      <c r="GN39" s="119" t="n"/>
-      <c r="GO39" s="119" t="n"/>
-      <c r="GP39" s="119" t="n"/>
-      <c r="GQ39" s="119" t="n"/>
-      <c r="GR39" s="119" t="n"/>
-      <c r="GS39" s="119" t="n"/>
-      <c r="GT39" s="119" t="n"/>
-      <c r="GU39" s="119" t="n"/>
-      <c r="GV39" s="119" t="n"/>
-      <c r="GW39" s="119" t="n"/>
-      <c r="GX39" s="119" t="n"/>
-      <c r="GY39" s="119" t="n"/>
-      <c r="GZ39" s="119" t="n"/>
-      <c r="HA39" s="119" t="n"/>
-      <c r="HB39" s="119" t="n"/>
-      <c r="HC39" s="119" t="n"/>
-      <c r="HD39" s="119" t="n"/>
-      <c r="HE39" s="119" t="n"/>
-      <c r="HF39" s="119" t="n"/>
-      <c r="HG39" s="119" t="n"/>
-      <c r="HH39" s="119" t="n"/>
-      <c r="HI39" s="119" t="n"/>
-      <c r="HJ39" s="119" t="n"/>
-      <c r="HK39" s="119" t="n"/>
-      <c r="HL39" s="119" t="n"/>
-      <c r="HM39" s="119" t="n"/>
-      <c r="HN39" s="119" t="n"/>
-      <c r="HO39" s="119" t="n"/>
-      <c r="HP39" s="119" t="n"/>
-      <c r="HQ39" s="119" t="n"/>
-      <c r="HR39" s="119" t="n"/>
-      <c r="HS39" s="119" t="n"/>
-      <c r="HT39" s="119" t="n"/>
-      <c r="HU39" s="119" t="n"/>
-    </row>
-    <row r="40" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A40" s="58" t="n"/>
-      <c r="B40" s="121" t="n"/>
-      <c r="C40" s="122" t="n"/>
-      <c r="D40" s="123" t="n"/>
-      <c r="E40" s="124" t="n"/>
-      <c r="F40" s="55" t="n"/>
-      <c r="G40" s="125" t="n"/>
-      <c r="H40" s="56" t="n"/>
-      <c r="I40" s="57" t="n"/>
-      <c r="J40" s="125" t="n"/>
-      <c r="K40" s="126" t="n"/>
-      <c r="L40" s="59" t="n"/>
-      <c r="M40" s="60" t="n"/>
-      <c r="N40" s="57" t="n"/>
-      <c r="O40" s="59" t="n"/>
-      <c r="P40" s="57" t="n"/>
-      <c r="Q40" s="57" t="n"/>
-      <c r="R40" s="57" t="n"/>
-      <c r="S40" s="57" t="n"/>
-      <c r="T40" s="57" t="n"/>
-      <c r="U40" s="57" t="n"/>
-      <c r="V40" s="57" t="n"/>
-      <c r="W40" s="57">
-        <f>SUM(K40:U40)</f>
-        <v/>
-      </c>
-      <c r="X40" s="57" t="n"/>
-      <c r="Y40" s="57" t="n"/>
-      <c r="Z40" s="59" t="n"/>
-      <c r="AA40" s="57">
-        <f>SUM(X40:Z40)</f>
-        <v/>
-      </c>
-      <c r="AB40" s="57">
-        <f>+W40+AA40</f>
-        <v/>
-      </c>
-      <c r="AC40" s="63" t="n"/>
-      <c r="AD40" s="149" t="n"/>
-      <c r="AE40" s="119" t="n"/>
-      <c r="AF40" s="119" t="n"/>
-      <c r="AG40" s="119" t="n"/>
-      <c r="AH40" s="119" t="n"/>
-      <c r="AI40" s="119" t="n"/>
-      <c r="AJ40" s="119" t="n"/>
-      <c r="AK40" s="119" t="n"/>
-      <c r="AL40" s="119" t="n"/>
-      <c r="AM40" s="119" t="n"/>
-      <c r="AN40" s="119" t="n"/>
-      <c r="AO40" s="119" t="n"/>
-      <c r="AP40" s="119" t="n"/>
-      <c r="AQ40" s="119" t="n"/>
-      <c r="AR40" s="119" t="n"/>
-      <c r="AS40" s="119" t="n"/>
-      <c r="AT40" s="119" t="n"/>
-      <c r="AU40" s="119" t="n"/>
-      <c r="AV40" s="119" t="n"/>
-      <c r="AW40" s="119" t="n"/>
-      <c r="AX40" s="119" t="n"/>
-      <c r="AY40" s="119" t="n"/>
-      <c r="AZ40" s="119" t="n"/>
-      <c r="BA40" s="119" t="n"/>
-      <c r="BB40" s="119" t="n"/>
-      <c r="BC40" s="119" t="n"/>
-      <c r="BD40" s="119" t="n"/>
-      <c r="BE40" s="119" t="n"/>
-      <c r="BF40" s="119" t="n"/>
-      <c r="BG40" s="119" t="n"/>
-      <c r="BH40" s="119" t="n"/>
-      <c r="BI40" s="119" t="n"/>
-      <c r="BJ40" s="119" t="n"/>
-      <c r="BK40" s="119" t="n"/>
-      <c r="BL40" s="119" t="n"/>
-      <c r="BM40" s="119" t="n"/>
-      <c r="BN40" s="119" t="n"/>
-      <c r="BO40" s="119" t="n"/>
-      <c r="BP40" s="119" t="n"/>
-      <c r="BQ40" s="119" t="n"/>
-      <c r="BR40" s="119" t="n"/>
-      <c r="BS40" s="119" t="n"/>
-      <c r="BT40" s="119" t="n"/>
-      <c r="BU40" s="119" t="n"/>
-      <c r="BV40" s="119" t="n"/>
-      <c r="BW40" s="119" t="n"/>
-      <c r="BX40" s="119" t="n"/>
-      <c r="BY40" s="119" t="n"/>
-      <c r="BZ40" s="119" t="n"/>
-      <c r="CA40" s="119" t="n"/>
-      <c r="CB40" s="119" t="n"/>
-      <c r="CC40" s="119" t="n"/>
-      <c r="CD40" s="119" t="n"/>
-      <c r="CE40" s="119" t="n"/>
-      <c r="CF40" s="119" t="n"/>
-      <c r="CG40" s="119" t="n"/>
-      <c r="CH40" s="119" t="n"/>
-      <c r="CI40" s="119" t="n"/>
-      <c r="CJ40" s="119" t="n"/>
-      <c r="CK40" s="119" t="n"/>
-      <c r="CL40" s="119" t="n"/>
-      <c r="CM40" s="119" t="n"/>
-      <c r="CN40" s="119" t="n"/>
-      <c r="CO40" s="119" t="n"/>
-      <c r="CP40" s="119" t="n"/>
-      <c r="CQ40" s="119" t="n"/>
-      <c r="CR40" s="119" t="n"/>
-      <c r="CS40" s="119" t="n"/>
-      <c r="CT40" s="119" t="n"/>
-      <c r="CU40" s="119" t="n"/>
-      <c r="CV40" s="119" t="n"/>
-      <c r="CW40" s="119" t="n"/>
-      <c r="CX40" s="119" t="n"/>
-      <c r="CY40" s="119" t="n"/>
-      <c r="CZ40" s="119" t="n"/>
-      <c r="DA40" s="119" t="n"/>
-      <c r="DB40" s="119" t="n"/>
-      <c r="DC40" s="119" t="n"/>
-      <c r="DD40" s="119" t="n"/>
-      <c r="DE40" s="119" t="n"/>
-      <c r="DF40" s="119" t="n"/>
-      <c r="DG40" s="119" t="n"/>
-      <c r="DH40" s="119" t="n"/>
-      <c r="DI40" s="119" t="n"/>
-      <c r="DJ40" s="119" t="n"/>
-      <c r="DK40" s="119" t="n"/>
-      <c r="DL40" s="119" t="n"/>
-      <c r="DM40" s="119" t="n"/>
-      <c r="DN40" s="119" t="n"/>
-      <c r="DO40" s="119" t="n"/>
-      <c r="DP40" s="119" t="n"/>
-      <c r="DQ40" s="119" t="n"/>
-      <c r="DR40" s="119" t="n"/>
-      <c r="DS40" s="119" t="n"/>
-      <c r="DT40" s="119" t="n"/>
-      <c r="DU40" s="119" t="n"/>
-      <c r="DV40" s="119" t="n"/>
-      <c r="DW40" s="119" t="n"/>
-      <c r="DX40" s="119" t="n"/>
-      <c r="DY40" s="119" t="n"/>
-      <c r="DZ40" s="119" t="n"/>
-      <c r="EA40" s="119" t="n"/>
-      <c r="EB40" s="119" t="n"/>
-      <c r="EC40" s="119" t="n"/>
-      <c r="ED40" s="119" t="n"/>
-      <c r="EE40" s="119" t="n"/>
-      <c r="EF40" s="119" t="n"/>
-      <c r="EG40" s="119" t="n"/>
-      <c r="EH40" s="119" t="n"/>
-      <c r="EI40" s="119" t="n"/>
-      <c r="EJ40" s="119" t="n"/>
-      <c r="EK40" s="119" t="n"/>
-      <c r="EL40" s="119" t="n"/>
-      <c r="EM40" s="119" t="n"/>
-      <c r="EN40" s="119" t="n"/>
-      <c r="EO40" s="119" t="n"/>
-      <c r="EP40" s="119" t="n"/>
-      <c r="EQ40" s="119" t="n"/>
-      <c r="ER40" s="119" t="n"/>
-      <c r="ES40" s="119" t="n"/>
-      <c r="ET40" s="119" t="n"/>
-      <c r="EU40" s="119" t="n"/>
-      <c r="EV40" s="119" t="n"/>
-      <c r="EW40" s="119" t="n"/>
-      <c r="EX40" s="119" t="n"/>
-      <c r="EY40" s="119" t="n"/>
-      <c r="EZ40" s="119" t="n"/>
-      <c r="FA40" s="119" t="n"/>
-      <c r="FB40" s="119" t="n"/>
-      <c r="FC40" s="119" t="n"/>
-      <c r="FD40" s="119" t="n"/>
-      <c r="FE40" s="119" t="n"/>
-      <c r="FF40" s="119" t="n"/>
-      <c r="FG40" s="119" t="n"/>
-      <c r="FH40" s="119" t="n"/>
-      <c r="FI40" s="119" t="n"/>
-      <c r="FJ40" s="119" t="n"/>
-      <c r="FK40" s="119" t="n"/>
-      <c r="FL40" s="119" t="n"/>
-      <c r="FM40" s="119" t="n"/>
-      <c r="FN40" s="119" t="n"/>
-      <c r="FO40" s="119" t="n"/>
-      <c r="FP40" s="119" t="n"/>
-      <c r="FQ40" s="119" t="n"/>
-      <c r="FR40" s="119" t="n"/>
-      <c r="FS40" s="119" t="n"/>
-      <c r="FT40" s="119" t="n"/>
-      <c r="FU40" s="119" t="n"/>
-      <c r="FV40" s="119" t="n"/>
-      <c r="FW40" s="119" t="n"/>
-      <c r="FX40" s="119" t="n"/>
-      <c r="FY40" s="119" t="n"/>
-      <c r="FZ40" s="119" t="n"/>
-      <c r="GA40" s="119" t="n"/>
-      <c r="GB40" s="119" t="n"/>
-      <c r="GC40" s="119" t="n"/>
-      <c r="GD40" s="119" t="n"/>
-      <c r="GE40" s="119" t="n"/>
-      <c r="GF40" s="119" t="n"/>
-      <c r="GG40" s="119" t="n"/>
-      <c r="GH40" s="119" t="n"/>
-      <c r="GI40" s="119" t="n"/>
-      <c r="GJ40" s="119" t="n"/>
-      <c r="GK40" s="119" t="n"/>
-      <c r="GL40" s="119" t="n"/>
-      <c r="GM40" s="119" t="n"/>
-      <c r="GN40" s="119" t="n"/>
-      <c r="GO40" s="119" t="n"/>
-      <c r="GP40" s="119" t="n"/>
-      <c r="GQ40" s="119" t="n"/>
-      <c r="GR40" s="119" t="n"/>
-      <c r="GS40" s="119" t="n"/>
-      <c r="GT40" s="119" t="n"/>
-      <c r="GU40" s="119" t="n"/>
-      <c r="GV40" s="119" t="n"/>
-      <c r="GW40" s="119" t="n"/>
-      <c r="GX40" s="119" t="n"/>
-      <c r="GY40" s="119" t="n"/>
-      <c r="GZ40" s="119" t="n"/>
-      <c r="HA40" s="119" t="n"/>
-      <c r="HB40" s="119" t="n"/>
-      <c r="HC40" s="119" t="n"/>
-      <c r="HD40" s="119" t="n"/>
-      <c r="HE40" s="119" t="n"/>
-      <c r="HF40" s="119" t="n"/>
-      <c r="HG40" s="119" t="n"/>
-      <c r="HH40" s="119" t="n"/>
-      <c r="HI40" s="119" t="n"/>
-      <c r="HJ40" s="119" t="n"/>
-      <c r="HK40" s="119" t="n"/>
-      <c r="HL40" s="119" t="n"/>
-      <c r="HM40" s="119" t="n"/>
-      <c r="HN40" s="119" t="n"/>
-      <c r="HO40" s="119" t="n"/>
-      <c r="HP40" s="119" t="n"/>
-      <c r="HQ40" s="119" t="n"/>
-      <c r="HR40" s="119" t="n"/>
-      <c r="HS40" s="119" t="n"/>
-      <c r="HT40" s="119" t="n"/>
-      <c r="HU40" s="119" t="n"/>
-    </row>
-    <row r="41" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A41" s="58" t="n"/>
-      <c r="B41" s="121" t="n"/>
-      <c r="C41" s="122" t="n"/>
-      <c r="D41" s="123" t="n"/>
-      <c r="E41" s="124" t="n"/>
-      <c r="F41" s="55" t="n"/>
-      <c r="G41" s="125" t="n"/>
-      <c r="H41" s="56" t="n"/>
-      <c r="I41" s="57" t="n"/>
-      <c r="J41" s="125" t="n"/>
-      <c r="K41" s="126" t="n"/>
-      <c r="L41" s="59" t="n"/>
-      <c r="M41" s="60" t="n"/>
-      <c r="N41" s="57" t="n"/>
-      <c r="O41" s="59" t="n"/>
-      <c r="P41" s="57" t="n"/>
-      <c r="Q41" s="57" t="n"/>
-      <c r="R41" s="57" t="n"/>
-      <c r="S41" s="57" t="n"/>
-      <c r="T41" s="57" t="n"/>
-      <c r="U41" s="57" t="n"/>
-      <c r="V41" s="57" t="n"/>
-      <c r="W41" s="57">
-        <f>SUM(K41:U41)</f>
-        <v/>
-      </c>
-      <c r="X41" s="57" t="n"/>
-      <c r="Y41" s="57" t="n"/>
-      <c r="Z41" s="59" t="n"/>
-      <c r="AA41" s="57">
-        <f>SUM(X41:Z41)</f>
-        <v/>
-      </c>
-      <c r="AB41" s="57">
-        <f>+W41+AA41</f>
-        <v/>
-      </c>
-      <c r="AC41" s="63" t="n"/>
-      <c r="AD41" s="149" t="n"/>
-      <c r="AE41" s="119" t="n"/>
-      <c r="AF41" s="119" t="n"/>
-      <c r="AG41" s="119" t="n"/>
-      <c r="AH41" s="119" t="n"/>
-      <c r="AI41" s="119" t="n"/>
-      <c r="AJ41" s="119" t="n"/>
-      <c r="AK41" s="119" t="n"/>
-      <c r="AL41" s="119" t="n"/>
-      <c r="AM41" s="119" t="n"/>
-      <c r="AN41" s="119" t="n"/>
-      <c r="AO41" s="119" t="n"/>
-      <c r="AP41" s="119" t="n"/>
-      <c r="AQ41" s="119" t="n"/>
-      <c r="AR41" s="119" t="n"/>
-      <c r="AS41" s="119" t="n"/>
-      <c r="AT41" s="119" t="n"/>
-      <c r="AU41" s="119" t="n"/>
-      <c r="AV41" s="119" t="n"/>
-      <c r="AW41" s="119" t="n"/>
-      <c r="AX41" s="119" t="n"/>
-      <c r="AY41" s="119" t="n"/>
-      <c r="AZ41" s="119" t="n"/>
-      <c r="BA41" s="119" t="n"/>
-      <c r="BB41" s="119" t="n"/>
-      <c r="BC41" s="119" t="n"/>
-      <c r="BD41" s="119" t="n"/>
-      <c r="BE41" s="119" t="n"/>
-      <c r="BF41" s="119" t="n"/>
-      <c r="BG41" s="119" t="n"/>
-      <c r="BH41" s="119" t="n"/>
-      <c r="BI41" s="119" t="n"/>
-      <c r="BJ41" s="119" t="n"/>
-      <c r="BK41" s="119" t="n"/>
-      <c r="BL41" s="119" t="n"/>
-      <c r="BM41" s="119" t="n"/>
-      <c r="BN41" s="119" t="n"/>
-      <c r="BO41" s="119" t="n"/>
-      <c r="BP41" s="119" t="n"/>
-      <c r="BQ41" s="119" t="n"/>
-      <c r="BR41" s="119" t="n"/>
-      <c r="BS41" s="119" t="n"/>
-      <c r="BT41" s="119" t="n"/>
-      <c r="BU41" s="119" t="n"/>
-      <c r="BV41" s="119" t="n"/>
-      <c r="BW41" s="119" t="n"/>
-      <c r="BX41" s="119" t="n"/>
-      <c r="BY41" s="119" t="n"/>
-      <c r="BZ41" s="119" t="n"/>
-      <c r="CA41" s="119" t="n"/>
-      <c r="CB41" s="119" t="n"/>
-      <c r="CC41" s="119" t="n"/>
-      <c r="CD41" s="119" t="n"/>
-      <c r="CE41" s="119" t="n"/>
-      <c r="CF41" s="119" t="n"/>
-      <c r="CG41" s="119" t="n"/>
-      <c r="CH41" s="119" t="n"/>
-      <c r="CI41" s="119" t="n"/>
-      <c r="CJ41" s="119" t="n"/>
-      <c r="CK41" s="119" t="n"/>
-      <c r="CL41" s="119" t="n"/>
-      <c r="CM41" s="119" t="n"/>
-      <c r="CN41" s="119" t="n"/>
-      <c r="CO41" s="119" t="n"/>
-      <c r="CP41" s="119" t="n"/>
-      <c r="CQ41" s="119" t="n"/>
-      <c r="CR41" s="119" t="n"/>
-      <c r="CS41" s="119" t="n"/>
-      <c r="CT41" s="119" t="n"/>
-      <c r="CU41" s="119" t="n"/>
-      <c r="CV41" s="119" t="n"/>
-      <c r="CW41" s="119" t="n"/>
-      <c r="CX41" s="119" t="n"/>
-      <c r="CY41" s="119" t="n"/>
-      <c r="CZ41" s="119" t="n"/>
-      <c r="DA41" s="119" t="n"/>
-      <c r="DB41" s="119" t="n"/>
-      <c r="DC41" s="119" t="n"/>
-      <c r="DD41" s="119" t="n"/>
-      <c r="DE41" s="119" t="n"/>
-      <c r="DF41" s="119" t="n"/>
-      <c r="DG41" s="119" t="n"/>
-      <c r="DH41" s="119" t="n"/>
-      <c r="DI41" s="119" t="n"/>
-      <c r="DJ41" s="119" t="n"/>
-      <c r="DK41" s="119" t="n"/>
-      <c r="DL41" s="119" t="n"/>
-      <c r="DM41" s="119" t="n"/>
-      <c r="DN41" s="119" t="n"/>
-      <c r="DO41" s="119" t="n"/>
-      <c r="DP41" s="119" t="n"/>
-      <c r="DQ41" s="119" t="n"/>
-      <c r="DR41" s="119" t="n"/>
-      <c r="DS41" s="119" t="n"/>
-      <c r="DT41" s="119" t="n"/>
-      <c r="DU41" s="119" t="n"/>
-      <c r="DV41" s="119" t="n"/>
-      <c r="DW41" s="119" t="n"/>
-      <c r="DX41" s="119" t="n"/>
-      <c r="DY41" s="119" t="n"/>
-      <c r="DZ41" s="119" t="n"/>
-      <c r="EA41" s="119" t="n"/>
-      <c r="EB41" s="119" t="n"/>
-      <c r="EC41" s="119" t="n"/>
-      <c r="ED41" s="119" t="n"/>
-      <c r="EE41" s="119" t="n"/>
-      <c r="EF41" s="119" t="n"/>
-      <c r="EG41" s="119" t="n"/>
-      <c r="EH41" s="119" t="n"/>
-      <c r="EI41" s="119" t="n"/>
-      <c r="EJ41" s="119" t="n"/>
-      <c r="EK41" s="119" t="n"/>
-      <c r="EL41" s="119" t="n"/>
-      <c r="EM41" s="119" t="n"/>
-      <c r="EN41" s="119" t="n"/>
-      <c r="EO41" s="119" t="n"/>
-      <c r="EP41" s="119" t="n"/>
-      <c r="EQ41" s="119" t="n"/>
-      <c r="ER41" s="119" t="n"/>
-      <c r="ES41" s="119" t="n"/>
-      <c r="ET41" s="119" t="n"/>
-      <c r="EU41" s="119" t="n"/>
-      <c r="EV41" s="119" t="n"/>
-      <c r="EW41" s="119" t="n"/>
-      <c r="EX41" s="119" t="n"/>
-      <c r="EY41" s="119" t="n"/>
-      <c r="EZ41" s="119" t="n"/>
-      <c r="FA41" s="119" t="n"/>
-      <c r="FB41" s="119" t="n"/>
-      <c r="FC41" s="119" t="n"/>
-      <c r="FD41" s="119" t="n"/>
-      <c r="FE41" s="119" t="n"/>
-      <c r="FF41" s="119" t="n"/>
-      <c r="FG41" s="119" t="n"/>
-      <c r="FH41" s="119" t="n"/>
-      <c r="FI41" s="119" t="n"/>
-      <c r="FJ41" s="119" t="n"/>
-      <c r="FK41" s="119" t="n"/>
-      <c r="FL41" s="119" t="n"/>
-      <c r="FM41" s="119" t="n"/>
-      <c r="FN41" s="119" t="n"/>
-      <c r="FO41" s="119" t="n"/>
-      <c r="FP41" s="119" t="n"/>
-      <c r="FQ41" s="119" t="n"/>
-      <c r="FR41" s="119" t="n"/>
-      <c r="FS41" s="119" t="n"/>
-      <c r="FT41" s="119" t="n"/>
-      <c r="FU41" s="119" t="n"/>
-      <c r="FV41" s="119" t="n"/>
-      <c r="FW41" s="119" t="n"/>
-      <c r="FX41" s="119" t="n"/>
-      <c r="FY41" s="119" t="n"/>
-      <c r="FZ41" s="119" t="n"/>
-      <c r="GA41" s="119" t="n"/>
-      <c r="GB41" s="119" t="n"/>
-      <c r="GC41" s="119" t="n"/>
-      <c r="GD41" s="119" t="n"/>
-      <c r="GE41" s="119" t="n"/>
-      <c r="GF41" s="119" t="n"/>
-      <c r="GG41" s="119" t="n"/>
-      <c r="GH41" s="119" t="n"/>
-      <c r="GI41" s="119" t="n"/>
-      <c r="GJ41" s="119" t="n"/>
-      <c r="GK41" s="119" t="n"/>
-      <c r="GL41" s="119" t="n"/>
-      <c r="GM41" s="119" t="n"/>
-      <c r="GN41" s="119" t="n"/>
-      <c r="GO41" s="119" t="n"/>
-      <c r="GP41" s="119" t="n"/>
-      <c r="GQ41" s="119" t="n"/>
-      <c r="GR41" s="119" t="n"/>
-      <c r="GS41" s="119" t="n"/>
-      <c r="GT41" s="119" t="n"/>
-      <c r="GU41" s="119" t="n"/>
-      <c r="GV41" s="119" t="n"/>
-      <c r="GW41" s="119" t="n"/>
-      <c r="GX41" s="119" t="n"/>
-      <c r="GY41" s="119" t="n"/>
-      <c r="GZ41" s="119" t="n"/>
-      <c r="HA41" s="119" t="n"/>
-      <c r="HB41" s="119" t="n"/>
-      <c r="HC41" s="119" t="n"/>
-      <c r="HD41" s="119" t="n"/>
-      <c r="HE41" s="119" t="n"/>
-      <c r="HF41" s="119" t="n"/>
-      <c r="HG41" s="119" t="n"/>
-      <c r="HH41" s="119" t="n"/>
-      <c r="HI41" s="119" t="n"/>
-      <c r="HJ41" s="119" t="n"/>
-      <c r="HK41" s="119" t="n"/>
-      <c r="HL41" s="119" t="n"/>
-      <c r="HM41" s="119" t="n"/>
-      <c r="HN41" s="119" t="n"/>
-      <c r="HO41" s="119" t="n"/>
-      <c r="HP41" s="119" t="n"/>
-      <c r="HQ41" s="119" t="n"/>
-      <c r="HR41" s="119" t="n"/>
-      <c r="HS41" s="119" t="n"/>
-      <c r="HT41" s="119" t="n"/>
-      <c r="HU41" s="119" t="n"/>
-    </row>
-    <row r="42" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A42" s="58" t="n"/>
-      <c r="B42" s="121" t="n"/>
-      <c r="C42" s="122" t="n"/>
-      <c r="D42" s="123" t="n"/>
-      <c r="E42" s="124" t="n"/>
-      <c r="F42" s="55" t="n"/>
-      <c r="G42" s="125" t="n"/>
-      <c r="H42" s="56" t="n"/>
-      <c r="I42" s="57" t="n"/>
-      <c r="J42" s="125" t="n"/>
-      <c r="K42" s="126" t="n"/>
-      <c r="L42" s="59" t="n"/>
-      <c r="M42" s="60" t="n"/>
-      <c r="N42" s="57" t="n"/>
-      <c r="O42" s="59" t="n"/>
-      <c r="P42" s="57" t="n"/>
-      <c r="Q42" s="57" t="n"/>
-      <c r="R42" s="57" t="n"/>
-      <c r="S42" s="57" t="n"/>
-      <c r="T42" s="57" t="n"/>
-      <c r="U42" s="57" t="n"/>
-      <c r="V42" s="57" t="n"/>
-      <c r="W42" s="57">
-        <f>SUM(K42:U42)</f>
-        <v/>
-      </c>
-      <c r="X42" s="57" t="n"/>
-      <c r="Y42" s="57" t="n"/>
-      <c r="Z42" s="59" t="n"/>
-      <c r="AA42" s="57">
-        <f>SUM(X42:Z42)</f>
-        <v/>
-      </c>
-      <c r="AB42" s="57">
-        <f>+W42+AA42</f>
-        <v/>
-      </c>
-      <c r="AC42" s="63" t="n"/>
-      <c r="AD42" s="149" t="n"/>
-      <c r="AE42" s="119" t="n"/>
-      <c r="AF42" s="119" t="n"/>
-      <c r="AG42" s="119" t="n"/>
-      <c r="AH42" s="119" t="n"/>
-      <c r="AI42" s="119" t="n"/>
-      <c r="AJ42" s="119" t="n"/>
-      <c r="AK42" s="119" t="n"/>
-      <c r="AL42" s="119" t="n"/>
-      <c r="AM42" s="119" t="n"/>
-      <c r="AN42" s="119" t="n"/>
-      <c r="AO42" s="119" t="n"/>
-      <c r="AP42" s="119" t="n"/>
-      <c r="AQ42" s="119" t="n"/>
-      <c r="AR42" s="119" t="n"/>
-      <c r="AS42" s="119" t="n"/>
-      <c r="AT42" s="119" t="n"/>
-      <c r="AU42" s="119" t="n"/>
-      <c r="AV42" s="119" t="n"/>
-      <c r="AW42" s="119" t="n"/>
-      <c r="AX42" s="119" t="n"/>
-      <c r="AY42" s="119" t="n"/>
-      <c r="AZ42" s="119" t="n"/>
-      <c r="BA42" s="119" t="n"/>
-      <c r="BB42" s="119" t="n"/>
-      <c r="BC42" s="119" t="n"/>
-      <c r="BD42" s="119" t="n"/>
-      <c r="BE42" s="119" t="n"/>
-      <c r="BF42" s="119" t="n"/>
-      <c r="BG42" s="119" t="n"/>
-      <c r="BH42" s="119" t="n"/>
-      <c r="BI42" s="119" t="n"/>
-      <c r="BJ42" s="119" t="n"/>
-      <c r="BK42" s="119" t="n"/>
-      <c r="BL42" s="119" t="n"/>
-      <c r="BM42" s="119" t="n"/>
-      <c r="BN42" s="119" t="n"/>
-      <c r="BO42" s="119" t="n"/>
-      <c r="BP42" s="119" t="n"/>
-      <c r="BQ42" s="119" t="n"/>
-      <c r="BR42" s="119" t="n"/>
-      <c r="BS42" s="119" t="n"/>
-      <c r="BT42" s="119" t="n"/>
-      <c r="BU42" s="119" t="n"/>
-      <c r="BV42" s="119" t="n"/>
-      <c r="BW42" s="119" t="n"/>
-      <c r="BX42" s="119" t="n"/>
-      <c r="BY42" s="119" t="n"/>
-      <c r="BZ42" s="119" t="n"/>
-      <c r="CA42" s="119" t="n"/>
-      <c r="CB42" s="119" t="n"/>
-      <c r="CC42" s="119" t="n"/>
-      <c r="CD42" s="119" t="n"/>
-      <c r="CE42" s="119" t="n"/>
-      <c r="CF42" s="119" t="n"/>
-      <c r="CG42" s="119" t="n"/>
-      <c r="CH42" s="119" t="n"/>
-      <c r="CI42" s="119" t="n"/>
-      <c r="CJ42" s="119" t="n"/>
-      <c r="CK42" s="119" t="n"/>
-      <c r="CL42" s="119" t="n"/>
-      <c r="CM42" s="119" t="n"/>
-      <c r="CN42" s="119" t="n"/>
-      <c r="CO42" s="119" t="n"/>
-      <c r="CP42" s="119" t="n"/>
-      <c r="CQ42" s="119" t="n"/>
-      <c r="CR42" s="119" t="n"/>
-      <c r="CS42" s="119" t="n"/>
-      <c r="CT42" s="119" t="n"/>
-      <c r="CU42" s="119" t="n"/>
-      <c r="CV42" s="119" t="n"/>
-      <c r="CW42" s="119" t="n"/>
-      <c r="CX42" s="119" t="n"/>
-      <c r="CY42" s="119" t="n"/>
-      <c r="CZ42" s="119" t="n"/>
-      <c r="DA42" s="119" t="n"/>
-      <c r="DB42" s="119" t="n"/>
-      <c r="DC42" s="119" t="n"/>
-      <c r="DD42" s="119" t="n"/>
-      <c r="DE42" s="119" t="n"/>
-      <c r="DF42" s="119" t="n"/>
-      <c r="DG42" s="119" t="n"/>
-      <c r="DH42" s="119" t="n"/>
-      <c r="DI42" s="119" t="n"/>
-      <c r="DJ42" s="119" t="n"/>
-      <c r="DK42" s="119" t="n"/>
-      <c r="DL42" s="119" t="n"/>
-      <c r="DM42" s="119" t="n"/>
-      <c r="DN42" s="119" t="n"/>
-      <c r="DO42" s="119" t="n"/>
-      <c r="DP42" s="119" t="n"/>
-      <c r="DQ42" s="119" t="n"/>
-      <c r="DR42" s="119" t="n"/>
-      <c r="DS42" s="119" t="n"/>
-      <c r="DT42" s="119" t="n"/>
-      <c r="DU42" s="119" t="n"/>
-      <c r="DV42" s="119" t="n"/>
-      <c r="DW42" s="119" t="n"/>
-      <c r="DX42" s="119" t="n"/>
-      <c r="DY42" s="119" t="n"/>
-      <c r="DZ42" s="119" t="n"/>
-      <c r="EA42" s="119" t="n"/>
-      <c r="EB42" s="119" t="n"/>
-      <c r="EC42" s="119" t="n"/>
-      <c r="ED42" s="119" t="n"/>
-      <c r="EE42" s="119" t="n"/>
-      <c r="EF42" s="119" t="n"/>
-      <c r="EG42" s="119" t="n"/>
-      <c r="EH42" s="119" t="n"/>
-      <c r="EI42" s="119" t="n"/>
-      <c r="EJ42" s="119" t="n"/>
-      <c r="EK42" s="119" t="n"/>
-      <c r="EL42" s="119" t="n"/>
-      <c r="EM42" s="119" t="n"/>
-      <c r="EN42" s="119" t="n"/>
-      <c r="EO42" s="119" t="n"/>
-      <c r="EP42" s="119" t="n"/>
-      <c r="EQ42" s="119" t="n"/>
-      <c r="ER42" s="119" t="n"/>
-      <c r="ES42" s="119" t="n"/>
-      <c r="ET42" s="119" t="n"/>
-      <c r="EU42" s="119" t="n"/>
-      <c r="EV42" s="119" t="n"/>
-      <c r="EW42" s="119" t="n"/>
-      <c r="EX42" s="119" t="n"/>
-      <c r="EY42" s="119" t="n"/>
-      <c r="EZ42" s="119" t="n"/>
-      <c r="FA42" s="119" t="n"/>
-      <c r="FB42" s="119" t="n"/>
-      <c r="FC42" s="119" t="n"/>
-      <c r="FD42" s="119" t="n"/>
-      <c r="FE42" s="119" t="n"/>
-      <c r="FF42" s="119" t="n"/>
-      <c r="FG42" s="119" t="n"/>
-      <c r="FH42" s="119" t="n"/>
-      <c r="FI42" s="119" t="n"/>
-      <c r="FJ42" s="119" t="n"/>
-      <c r="FK42" s="119" t="n"/>
-      <c r="FL42" s="119" t="n"/>
-      <c r="FM42" s="119" t="n"/>
-      <c r="FN42" s="119" t="n"/>
-      <c r="FO42" s="119" t="n"/>
-      <c r="FP42" s="119" t="n"/>
-      <c r="FQ42" s="119" t="n"/>
-      <c r="FR42" s="119" t="n"/>
-      <c r="FS42" s="119" t="n"/>
-      <c r="FT42" s="119" t="n"/>
-      <c r="FU42" s="119" t="n"/>
-      <c r="FV42" s="119" t="n"/>
-      <c r="FW42" s="119" t="n"/>
-      <c r="FX42" s="119" t="n"/>
-      <c r="FY42" s="119" t="n"/>
-      <c r="FZ42" s="119" t="n"/>
-      <c r="GA42" s="119" t="n"/>
-      <c r="GB42" s="119" t="n"/>
-      <c r="GC42" s="119" t="n"/>
-      <c r="GD42" s="119" t="n"/>
-      <c r="GE42" s="119" t="n"/>
-      <c r="GF42" s="119" t="n"/>
-      <c r="GG42" s="119" t="n"/>
-      <c r="GH42" s="119" t="n"/>
-      <c r="GI42" s="119" t="n"/>
-      <c r="GJ42" s="119" t="n"/>
-      <c r="GK42" s="119" t="n"/>
-      <c r="GL42" s="119" t="n"/>
-      <c r="GM42" s="119" t="n"/>
-      <c r="GN42" s="119" t="n"/>
-      <c r="GO42" s="119" t="n"/>
-      <c r="GP42" s="119" t="n"/>
-      <c r="GQ42" s="119" t="n"/>
-      <c r="GR42" s="119" t="n"/>
-      <c r="GS42" s="119" t="n"/>
-      <c r="GT42" s="119" t="n"/>
-      <c r="GU42" s="119" t="n"/>
-      <c r="GV42" s="119" t="n"/>
-      <c r="GW42" s="119" t="n"/>
-      <c r="GX42" s="119" t="n"/>
-      <c r="GY42" s="119" t="n"/>
-      <c r="GZ42" s="119" t="n"/>
-      <c r="HA42" s="119" t="n"/>
-      <c r="HB42" s="119" t="n"/>
-      <c r="HC42" s="119" t="n"/>
-      <c r="HD42" s="119" t="n"/>
-      <c r="HE42" s="119" t="n"/>
-      <c r="HF42" s="119" t="n"/>
-      <c r="HG42" s="119" t="n"/>
-      <c r="HH42" s="119" t="n"/>
-      <c r="HI42" s="119" t="n"/>
-      <c r="HJ42" s="119" t="n"/>
-      <c r="HK42" s="119" t="n"/>
-      <c r="HL42" s="119" t="n"/>
-      <c r="HM42" s="119" t="n"/>
-      <c r="HN42" s="119" t="n"/>
-      <c r="HO42" s="119" t="n"/>
-      <c r="HP42" s="119" t="n"/>
-      <c r="HQ42" s="119" t="n"/>
-      <c r="HR42" s="119" t="n"/>
-      <c r="HS42" s="119" t="n"/>
-      <c r="HT42" s="119" t="n"/>
-      <c r="HU42" s="119" t="n"/>
-    </row>
-    <row r="43" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A43" s="58" t="n"/>
-      <c r="B43" s="121" t="n"/>
-      <c r="C43" s="122" t="n"/>
-      <c r="D43" s="123" t="n"/>
-      <c r="E43" s="124" t="n"/>
-      <c r="F43" s="55" t="n"/>
-      <c r="G43" s="125" t="n"/>
-      <c r="H43" s="56" t="n"/>
-      <c r="I43" s="57" t="n"/>
-      <c r="J43" s="125" t="n"/>
-      <c r="K43" s="126" t="n"/>
-      <c r="L43" s="59" t="n"/>
-      <c r="M43" s="60" t="n"/>
-      <c r="N43" s="57" t="n"/>
-      <c r="O43" s="59" t="n"/>
-      <c r="P43" s="57" t="n"/>
-      <c r="Q43" s="57" t="n"/>
-      <c r="R43" s="57" t="n"/>
-      <c r="S43" s="57" t="n"/>
-      <c r="T43" s="57" t="n"/>
-      <c r="U43" s="57" t="n"/>
-      <c r="V43" s="57" t="n"/>
-      <c r="W43" s="57">
-        <f>SUM(K43:U43)</f>
-        <v/>
-      </c>
-      <c r="X43" s="57" t="n"/>
-      <c r="Y43" s="57" t="n"/>
-      <c r="Z43" s="59" t="n"/>
-      <c r="AA43" s="57">
-        <f>SUM(X43:Z43)</f>
-        <v/>
-      </c>
-      <c r="AB43" s="57">
-        <f>+W43+AA43</f>
-        <v/>
-      </c>
-      <c r="AC43" s="63" t="n"/>
-      <c r="AD43" s="149" t="n"/>
-      <c r="AE43" s="119" t="n"/>
-      <c r="AF43" s="119" t="n"/>
-      <c r="AG43" s="119" t="n"/>
-      <c r="AH43" s="119" t="n"/>
-      <c r="AI43" s="119" t="n"/>
-      <c r="AJ43" s="119" t="n"/>
-      <c r="AK43" s="119" t="n"/>
-      <c r="AL43" s="119" t="n"/>
-      <c r="AM43" s="119" t="n"/>
-      <c r="AN43" s="119" t="n"/>
-      <c r="AO43" s="119" t="n"/>
-      <c r="AP43" s="119" t="n"/>
-      <c r="AQ43" s="119" t="n"/>
-      <c r="AR43" s="119" t="n"/>
-      <c r="AS43" s="119" t="n"/>
-      <c r="AT43" s="119" t="n"/>
-      <c r="AU43" s="119" t="n"/>
-      <c r="AV43" s="119" t="n"/>
-      <c r="AW43" s="119" t="n"/>
-      <c r="AX43" s="119" t="n"/>
-      <c r="AY43" s="119" t="n"/>
-      <c r="AZ43" s="119" t="n"/>
-      <c r="BA43" s="119" t="n"/>
-      <c r="BB43" s="119" t="n"/>
-      <c r="BC43" s="119" t="n"/>
-      <c r="BD43" s="119" t="n"/>
-      <c r="BE43" s="119" t="n"/>
-      <c r="BF43" s="119" t="n"/>
-      <c r="BG43" s="119" t="n"/>
-      <c r="BH43" s="119" t="n"/>
-      <c r="BI43" s="119" t="n"/>
-      <c r="BJ43" s="119" t="n"/>
-      <c r="BK43" s="119" t="n"/>
-      <c r="BL43" s="119" t="n"/>
-      <c r="BM43" s="119" t="n"/>
-      <c r="BN43" s="119" t="n"/>
-      <c r="BO43" s="119" t="n"/>
-      <c r="BP43" s="119" t="n"/>
-      <c r="BQ43" s="119" t="n"/>
-      <c r="BR43" s="119" t="n"/>
-      <c r="BS43" s="119" t="n"/>
-      <c r="BT43" s="119" t="n"/>
-      <c r="BU43" s="119" t="n"/>
-      <c r="BV43" s="119" t="n"/>
-      <c r="BW43" s="119" t="n"/>
-      <c r="BX43" s="119" t="n"/>
-      <c r="BY43" s="119" t="n"/>
-      <c r="BZ43" s="119" t="n"/>
-      <c r="CA43" s="119" t="n"/>
-      <c r="CB43" s="119" t="n"/>
-      <c r="CC43" s="119" t="n"/>
-      <c r="CD43" s="119" t="n"/>
-      <c r="CE43" s="119" t="n"/>
-      <c r="CF43" s="119" t="n"/>
-      <c r="CG43" s="119" t="n"/>
-      <c r="CH43" s="119" t="n"/>
-      <c r="CI43" s="119" t="n"/>
-      <c r="CJ43" s="119" t="n"/>
-      <c r="CK43" s="119" t="n"/>
-      <c r="CL43" s="119" t="n"/>
-      <c r="CM43" s="119" t="n"/>
-      <c r="CN43" s="119" t="n"/>
-      <c r="CO43" s="119" t="n"/>
-      <c r="CP43" s="119" t="n"/>
-      <c r="CQ43" s="119" t="n"/>
-      <c r="CR43" s="119" t="n"/>
-      <c r="CS43" s="119" t="n"/>
-      <c r="CT43" s="119" t="n"/>
-      <c r="CU43" s="119" t="n"/>
-      <c r="CV43" s="119" t="n"/>
-      <c r="CW43" s="119" t="n"/>
-      <c r="CX43" s="119" t="n"/>
-      <c r="CY43" s="119" t="n"/>
-      <c r="CZ43" s="119" t="n"/>
-      <c r="DA43" s="119" t="n"/>
-      <c r="DB43" s="119" t="n"/>
-      <c r="DC43" s="119" t="n"/>
-      <c r="DD43" s="119" t="n"/>
-      <c r="DE43" s="119" t="n"/>
-      <c r="DF43" s="119" t="n"/>
-      <c r="DG43" s="119" t="n"/>
-      <c r="DH43" s="119" t="n"/>
-      <c r="DI43" s="119" t="n"/>
-      <c r="DJ43" s="119" t="n"/>
-      <c r="DK43" s="119" t="n"/>
-      <c r="DL43" s="119" t="n"/>
-      <c r="DM43" s="119" t="n"/>
-      <c r="DN43" s="119" t="n"/>
-      <c r="DO43" s="119" t="n"/>
-      <c r="DP43" s="119" t="n"/>
-      <c r="DQ43" s="119" t="n"/>
-      <c r="DR43" s="119" t="n"/>
-      <c r="DS43" s="119" t="n"/>
-      <c r="DT43" s="119" t="n"/>
-      <c r="DU43" s="119" t="n"/>
-      <c r="DV43" s="119" t="n"/>
-      <c r="DW43" s="119" t="n"/>
-      <c r="DX43" s="119" t="n"/>
-      <c r="DY43" s="119" t="n"/>
-      <c r="DZ43" s="119" t="n"/>
-      <c r="EA43" s="119" t="n"/>
-      <c r="EB43" s="119" t="n"/>
-      <c r="EC43" s="119" t="n"/>
-      <c r="ED43" s="119" t="n"/>
-      <c r="EE43" s="119" t="n"/>
-      <c r="EF43" s="119" t="n"/>
-      <c r="EG43" s="119" t="n"/>
-      <c r="EH43" s="119" t="n"/>
-      <c r="EI43" s="119" t="n"/>
-      <c r="EJ43" s="119" t="n"/>
-      <c r="EK43" s="119" t="n"/>
-      <c r="EL43" s="119" t="n"/>
-      <c r="EM43" s="119" t="n"/>
-      <c r="EN43" s="119" t="n"/>
-      <c r="EO43" s="119" t="n"/>
-      <c r="EP43" s="119" t="n"/>
-      <c r="EQ43" s="119" t="n"/>
-      <c r="ER43" s="119" t="n"/>
-      <c r="ES43" s="119" t="n"/>
-      <c r="ET43" s="119" t="n"/>
-      <c r="EU43" s="119" t="n"/>
-      <c r="EV43" s="119" t="n"/>
-      <c r="EW43" s="119" t="n"/>
-      <c r="EX43" s="119" t="n"/>
-      <c r="EY43" s="119" t="n"/>
-      <c r="EZ43" s="119" t="n"/>
-      <c r="FA43" s="119" t="n"/>
-      <c r="FB43" s="119" t="n"/>
-      <c r="FC43" s="119" t="n"/>
-      <c r="FD43" s="119" t="n"/>
-      <c r="FE43" s="119" t="n"/>
-      <c r="FF43" s="119" t="n"/>
-      <c r="FG43" s="119" t="n"/>
-      <c r="FH43" s="119" t="n"/>
-      <c r="FI43" s="119" t="n"/>
-      <c r="FJ43" s="119" t="n"/>
-      <c r="FK43" s="119" t="n"/>
-      <c r="FL43" s="119" t="n"/>
-      <c r="FM43" s="119" t="n"/>
-      <c r="FN43" s="119" t="n"/>
-      <c r="FO43" s="119" t="n"/>
-      <c r="FP43" s="119" t="n"/>
-      <c r="FQ43" s="119" t="n"/>
-      <c r="FR43" s="119" t="n"/>
-      <c r="FS43" s="119" t="n"/>
-      <c r="FT43" s="119" t="n"/>
-      <c r="FU43" s="119" t="n"/>
-      <c r="FV43" s="119" t="n"/>
-      <c r="FW43" s="119" t="n"/>
-      <c r="FX43" s="119" t="n"/>
-      <c r="FY43" s="119" t="n"/>
-      <c r="FZ43" s="119" t="n"/>
-      <c r="GA43" s="119" t="n"/>
-      <c r="GB43" s="119" t="n"/>
-      <c r="GC43" s="119" t="n"/>
-      <c r="GD43" s="119" t="n"/>
-      <c r="GE43" s="119" t="n"/>
-      <c r="GF43" s="119" t="n"/>
-      <c r="GG43" s="119" t="n"/>
-      <c r="GH43" s="119" t="n"/>
-      <c r="GI43" s="119" t="n"/>
-      <c r="GJ43" s="119" t="n"/>
-      <c r="GK43" s="119" t="n"/>
-      <c r="GL43" s="119" t="n"/>
-      <c r="GM43" s="119" t="n"/>
-      <c r="GN43" s="119" t="n"/>
-      <c r="GO43" s="119" t="n"/>
-      <c r="GP43" s="119" t="n"/>
-      <c r="GQ43" s="119" t="n"/>
-      <c r="GR43" s="119" t="n"/>
-      <c r="GS43" s="119" t="n"/>
-      <c r="GT43" s="119" t="n"/>
-      <c r="GU43" s="119" t="n"/>
-      <c r="GV43" s="119" t="n"/>
-      <c r="GW43" s="119" t="n"/>
-      <c r="GX43" s="119" t="n"/>
-      <c r="GY43" s="119" t="n"/>
-      <c r="GZ43" s="119" t="n"/>
-      <c r="HA43" s="119" t="n"/>
-      <c r="HB43" s="119" t="n"/>
-      <c r="HC43" s="119" t="n"/>
-      <c r="HD43" s="119" t="n"/>
-      <c r="HE43" s="119" t="n"/>
-      <c r="HF43" s="119" t="n"/>
-      <c r="HG43" s="119" t="n"/>
-      <c r="HH43" s="119" t="n"/>
-      <c r="HI43" s="119" t="n"/>
-      <c r="HJ43" s="119" t="n"/>
-      <c r="HK43" s="119" t="n"/>
-      <c r="HL43" s="119" t="n"/>
-      <c r="HM43" s="119" t="n"/>
-      <c r="HN43" s="119" t="n"/>
-      <c r="HO43" s="119" t="n"/>
-      <c r="HP43" s="119" t="n"/>
-      <c r="HQ43" s="119" t="n"/>
-      <c r="HR43" s="119" t="n"/>
-      <c r="HS43" s="119" t="n"/>
-      <c r="HT43" s="119" t="n"/>
-      <c r="HU43" s="119" t="n"/>
-    </row>
-    <row r="44" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A44" s="58" t="n"/>
-      <c r="B44" s="121" t="n"/>
-      <c r="C44" s="122" t="n"/>
-      <c r="D44" s="123" t="n"/>
-      <c r="E44" s="124" t="n"/>
-      <c r="F44" s="55" t="n"/>
-      <c r="G44" s="125" t="n"/>
-      <c r="H44" s="56" t="n"/>
-      <c r="I44" s="57" t="n"/>
-      <c r="J44" s="125" t="n"/>
-      <c r="K44" s="126" t="n"/>
-      <c r="L44" s="59" t="n"/>
-      <c r="M44" s="60" t="n"/>
-      <c r="N44" s="57" t="n"/>
-      <c r="O44" s="59" t="n"/>
-      <c r="P44" s="57" t="n"/>
-      <c r="Q44" s="57" t="n"/>
-      <c r="R44" s="57" t="n"/>
-      <c r="S44" s="57" t="n"/>
-      <c r="T44" s="57" t="n"/>
-      <c r="U44" s="57" t="n"/>
-      <c r="V44" s="57" t="n"/>
-      <c r="W44" s="57">
-        <f>SUM(K44:U44)</f>
-        <v/>
-      </c>
-      <c r="X44" s="57" t="n"/>
-      <c r="Y44" s="57" t="n"/>
-      <c r="Z44" s="59" t="n"/>
-      <c r="AA44" s="57">
-        <f>SUM(X44:Z44)</f>
-        <v/>
-      </c>
-      <c r="AB44" s="57">
-        <f>+W44+AA44</f>
-        <v/>
-      </c>
-      <c r="AC44" s="63" t="n"/>
-      <c r="AD44" s="149" t="n"/>
-      <c r="AE44" s="119" t="n"/>
-      <c r="AF44" s="119" t="n"/>
-      <c r="AG44" s="119" t="n"/>
-      <c r="AH44" s="119" t="n"/>
-      <c r="AI44" s="119" t="n"/>
-      <c r="AJ44" s="119" t="n"/>
-      <c r="AK44" s="119" t="n"/>
-      <c r="AL44" s="119" t="n"/>
-      <c r="AM44" s="119" t="n"/>
-      <c r="AN44" s="119" t="n"/>
-      <c r="AO44" s="119" t="n"/>
-      <c r="AP44" s="119" t="n"/>
-      <c r="AQ44" s="119" t="n"/>
-      <c r="AR44" s="119" t="n"/>
-      <c r="AS44" s="119" t="n"/>
-      <c r="AT44" s="119" t="n"/>
-      <c r="AU44" s="119" t="n"/>
-      <c r="AV44" s="119" t="n"/>
-      <c r="AW44" s="119" t="n"/>
-      <c r="AX44" s="119" t="n"/>
-      <c r="AY44" s="119" t="n"/>
-      <c r="AZ44" s="119" t="n"/>
-      <c r="BA44" s="119" t="n"/>
-      <c r="BB44" s="119" t="n"/>
-      <c r="BC44" s="119" t="n"/>
-      <c r="BD44" s="119" t="n"/>
-      <c r="BE44" s="119" t="n"/>
-      <c r="BF44" s="119" t="n"/>
-      <c r="BG44" s="119" t="n"/>
-      <c r="BH44" s="119" t="n"/>
-      <c r="BI44" s="119" t="n"/>
-      <c r="BJ44" s="119" t="n"/>
-      <c r="BK44" s="119" t="n"/>
-      <c r="BL44" s="119" t="n"/>
-      <c r="BM44" s="119" t="n"/>
-      <c r="BN44" s="119" t="n"/>
-      <c r="BO44" s="119" t="n"/>
-      <c r="BP44" s="119" t="n"/>
-      <c r="BQ44" s="119" t="n"/>
-      <c r="BR44" s="119" t="n"/>
-      <c r="BS44" s="119" t="n"/>
-      <c r="BT44" s="119" t="n"/>
-      <c r="BU44" s="119" t="n"/>
-      <c r="BV44" s="119" t="n"/>
-      <c r="BW44" s="119" t="n"/>
-      <c r="BX44" s="119" t="n"/>
-      <c r="BY44" s="119" t="n"/>
-      <c r="BZ44" s="119" t="n"/>
-      <c r="CA44" s="119" t="n"/>
-      <c r="CB44" s="119" t="n"/>
-      <c r="CC44" s="119" t="n"/>
-      <c r="CD44" s="119" t="n"/>
-      <c r="CE44" s="119" t="n"/>
-      <c r="CF44" s="119" t="n"/>
-      <c r="CG44" s="119" t="n"/>
-      <c r="CH44" s="119" t="n"/>
-      <c r="CI44" s="119" t="n"/>
-      <c r="CJ44" s="119" t="n"/>
-      <c r="CK44" s="119" t="n"/>
-      <c r="CL44" s="119" t="n"/>
-      <c r="CM44" s="119" t="n"/>
-      <c r="CN44" s="119" t="n"/>
-      <c r="CO44" s="119" t="n"/>
-      <c r="CP44" s="119" t="n"/>
-      <c r="CQ44" s="119" t="n"/>
-      <c r="CR44" s="119" t="n"/>
-      <c r="CS44" s="119" t="n"/>
-      <c r="CT44" s="119" t="n"/>
-      <c r="CU44" s="119" t="n"/>
-      <c r="CV44" s="119" t="n"/>
-      <c r="CW44" s="119" t="n"/>
-      <c r="CX44" s="119" t="n"/>
-      <c r="CY44" s="119" t="n"/>
-      <c r="CZ44" s="119" t="n"/>
-      <c r="DA44" s="119" t="n"/>
-      <c r="DB44" s="119" t="n"/>
-      <c r="DC44" s="119" t="n"/>
-      <c r="DD44" s="119" t="n"/>
-      <c r="DE44" s="119" t="n"/>
-      <c r="DF44" s="119" t="n"/>
-      <c r="DG44" s="119" t="n"/>
-      <c r="DH44" s="119" t="n"/>
-      <c r="DI44" s="119" t="n"/>
-      <c r="DJ44" s="119" t="n"/>
-      <c r="DK44" s="119" t="n"/>
-      <c r="DL44" s="119" t="n"/>
-      <c r="DM44" s="119" t="n"/>
-      <c r="DN44" s="119" t="n"/>
-      <c r="DO44" s="119" t="n"/>
-      <c r="DP44" s="119" t="n"/>
-      <c r="DQ44" s="119" t="n"/>
-      <c r="DR44" s="119" t="n"/>
-      <c r="DS44" s="119" t="n"/>
-      <c r="DT44" s="119" t="n"/>
-      <c r="DU44" s="119" t="n"/>
-      <c r="DV44" s="119" t="n"/>
-      <c r="DW44" s="119" t="n"/>
-      <c r="DX44" s="119" t="n"/>
-      <c r="DY44" s="119" t="n"/>
-      <c r="DZ44" s="119" t="n"/>
-      <c r="EA44" s="119" t="n"/>
-      <c r="EB44" s="119" t="n"/>
-      <c r="EC44" s="119" t="n"/>
-      <c r="ED44" s="119" t="n"/>
-      <c r="EE44" s="119" t="n"/>
-      <c r="EF44" s="119" t="n"/>
-      <c r="EG44" s="119" t="n"/>
-      <c r="EH44" s="119" t="n"/>
-      <c r="EI44" s="119" t="n"/>
-      <c r="EJ44" s="119" t="n"/>
-      <c r="EK44" s="119" t="n"/>
-      <c r="EL44" s="119" t="n"/>
-      <c r="EM44" s="119" t="n"/>
-      <c r="EN44" s="119" t="n"/>
-      <c r="EO44" s="119" t="n"/>
-      <c r="EP44" s="119" t="n"/>
-      <c r="EQ44" s="119" t="n"/>
-      <c r="ER44" s="119" t="n"/>
-      <c r="ES44" s="119" t="n"/>
-      <c r="ET44" s="119" t="n"/>
-      <c r="EU44" s="119" t="n"/>
-      <c r="EV44" s="119" t="n"/>
-      <c r="EW44" s="119" t="n"/>
-      <c r="EX44" s="119" t="n"/>
-      <c r="EY44" s="119" t="n"/>
-      <c r="EZ44" s="119" t="n"/>
-      <c r="FA44" s="119" t="n"/>
-      <c r="FB44" s="119" t="n"/>
-      <c r="FC44" s="119" t="n"/>
-      <c r="FD44" s="119" t="n"/>
-      <c r="FE44" s="119" t="n"/>
-      <c r="FF44" s="119" t="n"/>
-      <c r="FG44" s="119" t="n"/>
-      <c r="FH44" s="119" t="n"/>
-      <c r="FI44" s="119" t="n"/>
-      <c r="FJ44" s="119" t="n"/>
-      <c r="FK44" s="119" t="n"/>
-      <c r="FL44" s="119" t="n"/>
-      <c r="FM44" s="119" t="n"/>
-      <c r="FN44" s="119" t="n"/>
-      <c r="FO44" s="119" t="n"/>
-      <c r="FP44" s="119" t="n"/>
-      <c r="FQ44" s="119" t="n"/>
-      <c r="FR44" s="119" t="n"/>
-      <c r="FS44" s="119" t="n"/>
-      <c r="FT44" s="119" t="n"/>
-      <c r="FU44" s="119" t="n"/>
-      <c r="FV44" s="119" t="n"/>
-      <c r="FW44" s="119" t="n"/>
-      <c r="FX44" s="119" t="n"/>
-      <c r="FY44" s="119" t="n"/>
-      <c r="FZ44" s="119" t="n"/>
-      <c r="GA44" s="119" t="n"/>
-      <c r="GB44" s="119" t="n"/>
-      <c r="GC44" s="119" t="n"/>
-      <c r="GD44" s="119" t="n"/>
-      <c r="GE44" s="119" t="n"/>
-      <c r="GF44" s="119" t="n"/>
-      <c r="GG44" s="119" t="n"/>
-      <c r="GH44" s="119" t="n"/>
-      <c r="GI44" s="119" t="n"/>
-      <c r="GJ44" s="119" t="n"/>
-      <c r="GK44" s="119" t="n"/>
-      <c r="GL44" s="119" t="n"/>
-      <c r="GM44" s="119" t="n"/>
-      <c r="GN44" s="119" t="n"/>
-      <c r="GO44" s="119" t="n"/>
-      <c r="GP44" s="119" t="n"/>
-      <c r="GQ44" s="119" t="n"/>
-      <c r="GR44" s="119" t="n"/>
-      <c r="GS44" s="119" t="n"/>
-      <c r="GT44" s="119" t="n"/>
-      <c r="GU44" s="119" t="n"/>
-      <c r="GV44" s="119" t="n"/>
-      <c r="GW44" s="119" t="n"/>
-      <c r="GX44" s="119" t="n"/>
-      <c r="GY44" s="119" t="n"/>
-      <c r="GZ44" s="119" t="n"/>
-      <c r="HA44" s="119" t="n"/>
-      <c r="HB44" s="119" t="n"/>
-      <c r="HC44" s="119" t="n"/>
-      <c r="HD44" s="119" t="n"/>
-      <c r="HE44" s="119" t="n"/>
-      <c r="HF44" s="119" t="n"/>
-      <c r="HG44" s="119" t="n"/>
-      <c r="HH44" s="119" t="n"/>
-      <c r="HI44" s="119" t="n"/>
-      <c r="HJ44" s="119" t="n"/>
-      <c r="HK44" s="119" t="n"/>
-      <c r="HL44" s="119" t="n"/>
-      <c r="HM44" s="119" t="n"/>
-      <c r="HN44" s="119" t="n"/>
-      <c r="HO44" s="119" t="n"/>
-      <c r="HP44" s="119" t="n"/>
-      <c r="HQ44" s="119" t="n"/>
-      <c r="HR44" s="119" t="n"/>
-      <c r="HS44" s="119" t="n"/>
-      <c r="HT44" s="119" t="n"/>
-      <c r="HU44" s="119" t="n"/>
-    </row>
-    <row r="45" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A45" s="58" t="n"/>
-      <c r="B45" s="121" t="n"/>
-      <c r="C45" s="122" t="n"/>
-      <c r="D45" s="123" t="n"/>
-      <c r="E45" s="124" t="n"/>
-      <c r="F45" s="55" t="n"/>
-      <c r="G45" s="125" t="n"/>
-      <c r="H45" s="56" t="n"/>
-      <c r="I45" s="57" t="n"/>
-      <c r="J45" s="125" t="n"/>
-      <c r="K45" s="126" t="n"/>
-      <c r="L45" s="59" t="n"/>
-      <c r="M45" s="60" t="n"/>
-      <c r="N45" s="57" t="n"/>
-      <c r="O45" s="59" t="n"/>
-      <c r="P45" s="57" t="n"/>
-      <c r="Q45" s="57" t="n"/>
-      <c r="R45" s="57" t="n"/>
-      <c r="S45" s="57" t="n"/>
-      <c r="T45" s="57" t="n"/>
-      <c r="U45" s="57" t="n"/>
-      <c r="V45" s="57" t="n"/>
-      <c r="W45" s="57">
-        <f>SUM(K45:U45)</f>
-        <v/>
-      </c>
-      <c r="X45" s="57" t="n"/>
-      <c r="Y45" s="57" t="n"/>
-      <c r="Z45" s="59" t="n"/>
-      <c r="AA45" s="57">
-        <f>SUM(X45:Z45)</f>
-        <v/>
-      </c>
-      <c r="AB45" s="57">
-        <f>+W45+AA45</f>
-        <v/>
-      </c>
-      <c r="AC45" s="63" t="n"/>
-      <c r="AD45" s="149" t="n"/>
-      <c r="AE45" s="119" t="n"/>
-      <c r="AF45" s="119" t="n"/>
-      <c r="AG45" s="119" t="n"/>
-      <c r="AH45" s="119" t="n"/>
-      <c r="AI45" s="119" t="n"/>
-      <c r="AJ45" s="119" t="n"/>
-      <c r="AK45" s="119" t="n"/>
-      <c r="AL45" s="119" t="n"/>
-      <c r="AM45" s="119" t="n"/>
-      <c r="AN45" s="119" t="n"/>
-      <c r="AO45" s="119" t="n"/>
-      <c r="AP45" s="119" t="n"/>
-      <c r="AQ45" s="119" t="n"/>
-      <c r="AR45" s="119" t="n"/>
-      <c r="AS45" s="119" t="n"/>
-      <c r="AT45" s="119" t="n"/>
-      <c r="AU45" s="119" t="n"/>
-      <c r="AV45" s="119" t="n"/>
-      <c r="AW45" s="119" t="n"/>
-      <c r="AX45" s="119" t="n"/>
-      <c r="AY45" s="119" t="n"/>
-      <c r="AZ45" s="119" t="n"/>
-      <c r="BA45" s="119" t="n"/>
-      <c r="BB45" s="119" t="n"/>
-      <c r="BC45" s="119" t="n"/>
-      <c r="BD45" s="119" t="n"/>
-      <c r="BE45" s="119" t="n"/>
-      <c r="BF45" s="119" t="n"/>
-      <c r="BG45" s="119" t="n"/>
-      <c r="BH45" s="119" t="n"/>
-      <c r="BI45" s="119" t="n"/>
-      <c r="BJ45" s="119" t="n"/>
-      <c r="BK45" s="119" t="n"/>
-      <c r="BL45" s="119" t="n"/>
-      <c r="BM45" s="119" t="n"/>
-      <c r="BN45" s="119" t="n"/>
-      <c r="BO45" s="119" t="n"/>
-      <c r="BP45" s="119" t="n"/>
-      <c r="BQ45" s="119" t="n"/>
-      <c r="BR45" s="119" t="n"/>
-      <c r="BS45" s="119" t="n"/>
-      <c r="BT45" s="119" t="n"/>
-      <c r="BU45" s="119" t="n"/>
-      <c r="BV45" s="119" t="n"/>
-      <c r="BW45" s="119" t="n"/>
-      <c r="BX45" s="119" t="n"/>
-      <c r="BY45" s="119" t="n"/>
-      <c r="BZ45" s="119" t="n"/>
-      <c r="CA45" s="119" t="n"/>
-      <c r="CB45" s="119" t="n"/>
-      <c r="CC45" s="119" t="n"/>
-      <c r="CD45" s="119" t="n"/>
-      <c r="CE45" s="119" t="n"/>
-      <c r="CF45" s="119" t="n"/>
-      <c r="CG45" s="119" t="n"/>
-      <c r="CH45" s="119" t="n"/>
-      <c r="CI45" s="119" t="n"/>
-      <c r="CJ45" s="119" t="n"/>
-      <c r="CK45" s="119" t="n"/>
-      <c r="CL45" s="119" t="n"/>
-      <c r="CM45" s="119" t="n"/>
-      <c r="CN45" s="119" t="n"/>
-      <c r="CO45" s="119" t="n"/>
-      <c r="CP45" s="119" t="n"/>
-      <c r="CQ45" s="119" t="n"/>
-      <c r="CR45" s="119" t="n"/>
-      <c r="CS45" s="119" t="n"/>
-      <c r="CT45" s="119" t="n"/>
-      <c r="CU45" s="119" t="n"/>
-      <c r="CV45" s="119" t="n"/>
-      <c r="CW45" s="119" t="n"/>
-      <c r="CX45" s="119" t="n"/>
-      <c r="CY45" s="119" t="n"/>
-      <c r="CZ45" s="119" t="n"/>
-      <c r="DA45" s="119" t="n"/>
-      <c r="DB45" s="119" t="n"/>
-      <c r="DC45" s="119" t="n"/>
-      <c r="DD45" s="119" t="n"/>
-      <c r="DE45" s="119" t="n"/>
-      <c r="DF45" s="119" t="n"/>
-      <c r="DG45" s="119" t="n"/>
-      <c r="DH45" s="119" t="n"/>
-      <c r="DI45" s="119" t="n"/>
-      <c r="DJ45" s="119" t="n"/>
-      <c r="DK45" s="119" t="n"/>
-      <c r="DL45" s="119" t="n"/>
-      <c r="DM45" s="119" t="n"/>
-      <c r="DN45" s="119" t="n"/>
-      <c r="DO45" s="119" t="n"/>
-      <c r="DP45" s="119" t="n"/>
-      <c r="DQ45" s="119" t="n"/>
-      <c r="DR45" s="119" t="n"/>
-      <c r="DS45" s="119" t="n"/>
-      <c r="DT45" s="119" t="n"/>
-      <c r="DU45" s="119" t="n"/>
-      <c r="DV45" s="119" t="n"/>
-      <c r="DW45" s="119" t="n"/>
-      <c r="DX45" s="119" t="n"/>
-      <c r="DY45" s="119" t="n"/>
-      <c r="DZ45" s="119" t="n"/>
-      <c r="EA45" s="119" t="n"/>
-      <c r="EB45" s="119" t="n"/>
-      <c r="EC45" s="119" t="n"/>
-      <c r="ED45" s="119" t="n"/>
-      <c r="EE45" s="119" t="n"/>
-      <c r="EF45" s="119" t="n"/>
-      <c r="EG45" s="119" t="n"/>
-      <c r="EH45" s="119" t="n"/>
-      <c r="EI45" s="119" t="n"/>
-      <c r="EJ45" s="119" t="n"/>
-      <c r="EK45" s="119" t="n"/>
-      <c r="EL45" s="119" t="n"/>
-      <c r="EM45" s="119" t="n"/>
-      <c r="EN45" s="119" t="n"/>
-      <c r="EO45" s="119" t="n"/>
-      <c r="EP45" s="119" t="n"/>
-      <c r="EQ45" s="119" t="n"/>
-      <c r="ER45" s="119" t="n"/>
-      <c r="ES45" s="119" t="n"/>
-      <c r="ET45" s="119" t="n"/>
-      <c r="EU45" s="119" t="n"/>
-      <c r="EV45" s="119" t="n"/>
-      <c r="EW45" s="119" t="n"/>
-      <c r="EX45" s="119" t="n"/>
-      <c r="EY45" s="119" t="n"/>
-      <c r="EZ45" s="119" t="n"/>
-      <c r="FA45" s="119" t="n"/>
-      <c r="FB45" s="119" t="n"/>
-      <c r="FC45" s="119" t="n"/>
-      <c r="FD45" s="119" t="n"/>
-      <c r="FE45" s="119" t="n"/>
-      <c r="FF45" s="119" t="n"/>
-      <c r="FG45" s="119" t="n"/>
-      <c r="FH45" s="119" t="n"/>
-      <c r="FI45" s="119" t="n"/>
-      <c r="FJ45" s="119" t="n"/>
-      <c r="FK45" s="119" t="n"/>
-      <c r="FL45" s="119" t="n"/>
-      <c r="FM45" s="119" t="n"/>
-      <c r="FN45" s="119" t="n"/>
-      <c r="FO45" s="119" t="n"/>
-      <c r="FP45" s="119" t="n"/>
-      <c r="FQ45" s="119" t="n"/>
-      <c r="FR45" s="119" t="n"/>
-      <c r="FS45" s="119" t="n"/>
-      <c r="FT45" s="119" t="n"/>
-      <c r="FU45" s="119" t="n"/>
-      <c r="FV45" s="119" t="n"/>
-      <c r="FW45" s="119" t="n"/>
-      <c r="FX45" s="119" t="n"/>
-      <c r="FY45" s="119" t="n"/>
-      <c r="FZ45" s="119" t="n"/>
-      <c r="GA45" s="119" t="n"/>
-      <c r="GB45" s="119" t="n"/>
-      <c r="GC45" s="119" t="n"/>
-      <c r="GD45" s="119" t="n"/>
-      <c r="GE45" s="119" t="n"/>
-      <c r="GF45" s="119" t="n"/>
-      <c r="GG45" s="119" t="n"/>
-      <c r="GH45" s="119" t="n"/>
-      <c r="GI45" s="119" t="n"/>
-      <c r="GJ45" s="119" t="n"/>
-      <c r="GK45" s="119" t="n"/>
-      <c r="GL45" s="119" t="n"/>
-      <c r="GM45" s="119" t="n"/>
-      <c r="GN45" s="119" t="n"/>
-      <c r="GO45" s="119" t="n"/>
-      <c r="GP45" s="119" t="n"/>
-      <c r="GQ45" s="119" t="n"/>
-      <c r="GR45" s="119" t="n"/>
-      <c r="GS45" s="119" t="n"/>
-      <c r="GT45" s="119" t="n"/>
-      <c r="GU45" s="119" t="n"/>
-      <c r="GV45" s="119" t="n"/>
-      <c r="GW45" s="119" t="n"/>
-      <c r="GX45" s="119" t="n"/>
-      <c r="GY45" s="119" t="n"/>
-      <c r="GZ45" s="119" t="n"/>
-      <c r="HA45" s="119" t="n"/>
-      <c r="HB45" s="119" t="n"/>
-      <c r="HC45" s="119" t="n"/>
-      <c r="HD45" s="119" t="n"/>
-      <c r="HE45" s="119" t="n"/>
-      <c r="HF45" s="119" t="n"/>
-      <c r="HG45" s="119" t="n"/>
-      <c r="HH45" s="119" t="n"/>
-      <c r="HI45" s="119" t="n"/>
-      <c r="HJ45" s="119" t="n"/>
-      <c r="HK45" s="119" t="n"/>
-      <c r="HL45" s="119" t="n"/>
-      <c r="HM45" s="119" t="n"/>
-      <c r="HN45" s="119" t="n"/>
-      <c r="HO45" s="119" t="n"/>
-      <c r="HP45" s="119" t="n"/>
-      <c r="HQ45" s="119" t="n"/>
-      <c r="HR45" s="119" t="n"/>
-      <c r="HS45" s="119" t="n"/>
-      <c r="HT45" s="119" t="n"/>
-      <c r="HU45" s="119" t="n"/>
-    </row>
-    <row r="46" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A46" s="58" t="n"/>
-      <c r="B46" s="121" t="n"/>
-      <c r="C46" s="122" t="n"/>
-      <c r="D46" s="123" t="n"/>
-      <c r="E46" s="124" t="n"/>
-      <c r="F46" s="55" t="n"/>
-      <c r="G46" s="125" t="n"/>
-      <c r="H46" s="56" t="n"/>
-      <c r="I46" s="57" t="n"/>
-      <c r="J46" s="125" t="n"/>
-      <c r="K46" s="126" t="n"/>
-      <c r="L46" s="59" t="n"/>
-      <c r="M46" s="60" t="n"/>
-      <c r="N46" s="57" t="n"/>
-      <c r="O46" s="59" t="n"/>
-      <c r="P46" s="57" t="n"/>
-      <c r="Q46" s="57" t="n"/>
-      <c r="R46" s="57" t="n"/>
-      <c r="S46" s="57" t="n"/>
-      <c r="T46" s="57" t="n"/>
-      <c r="U46" s="57" t="n"/>
-      <c r="V46" s="57" t="n"/>
-      <c r="W46" s="57">
-        <f>SUM(K46:U46)</f>
-        <v/>
-      </c>
-      <c r="X46" s="57" t="n"/>
-      <c r="Y46" s="57" t="n">
-        <v>20000</v>
-      </c>
-      <c r="Z46" s="59" t="n"/>
-      <c r="AA46" s="57">
-        <f>SUM(X46:Z46)</f>
-        <v/>
-      </c>
-      <c r="AB46" s="57">
-        <f>+W46+AA46</f>
-        <v/>
-      </c>
-      <c r="AC46" s="63" t="inlineStr">
-        <is>
-          <t>0318082</t>
-        </is>
-      </c>
-      <c r="AD46" s="149" t="n"/>
-      <c r="AE46" s="119" t="n"/>
-      <c r="AF46" s="119" t="n"/>
-      <c r="AG46" s="119" t="n"/>
-      <c r="AH46" s="119" t="n"/>
-      <c r="AI46" s="119" t="n"/>
-      <c r="AJ46" s="119" t="n"/>
-      <c r="AK46" s="119" t="n"/>
-      <c r="AL46" s="119" t="n"/>
-      <c r="AM46" s="119" t="n"/>
-      <c r="AN46" s="119" t="n"/>
-      <c r="AO46" s="119" t="n"/>
-      <c r="AP46" s="119" t="n"/>
-      <c r="AQ46" s="119" t="n"/>
-      <c r="AR46" s="119" t="n"/>
-      <c r="AS46" s="119" t="n"/>
-      <c r="AT46" s="119" t="n"/>
-      <c r="AU46" s="119" t="n"/>
-      <c r="AV46" s="119" t="n"/>
-      <c r="AW46" s="119" t="n"/>
-      <c r="AX46" s="119" t="n"/>
-      <c r="AY46" s="119" t="n"/>
-      <c r="AZ46" s="119" t="n"/>
-      <c r="BA46" s="119" t="n"/>
-      <c r="BB46" s="119" t="n"/>
-      <c r="BC46" s="119" t="n"/>
-      <c r="BD46" s="119" t="n"/>
-      <c r="BE46" s="119" t="n"/>
-      <c r="BF46" s="119" t="n"/>
-      <c r="BG46" s="119" t="n"/>
-      <c r="BH46" s="119" t="n"/>
-      <c r="BI46" s="119" t="n"/>
-      <c r="BJ46" s="119" t="n"/>
-      <c r="BK46" s="119" t="n"/>
-      <c r="BL46" s="119" t="n"/>
-      <c r="BM46" s="119" t="n"/>
-      <c r="BN46" s="119" t="n"/>
-      <c r="BO46" s="119" t="n"/>
-      <c r="BP46" s="119" t="n"/>
-      <c r="BQ46" s="119" t="n"/>
-      <c r="BR46" s="119" t="n"/>
-      <c r="BS46" s="119" t="n"/>
-      <c r="BT46" s="119" t="n"/>
-      <c r="BU46" s="119" t="n"/>
-      <c r="BV46" s="119" t="n"/>
-      <c r="BW46" s="119" t="n"/>
-      <c r="BX46" s="119" t="n"/>
-      <c r="BY46" s="119" t="n"/>
-      <c r="BZ46" s="119" t="n"/>
-      <c r="CA46" s="119" t="n"/>
-      <c r="CB46" s="119" t="n"/>
-      <c r="CC46" s="119" t="n"/>
-      <c r="CD46" s="119" t="n"/>
-      <c r="CE46" s="119" t="n"/>
-      <c r="CF46" s="119" t="n"/>
-      <c r="CG46" s="119" t="n"/>
-      <c r="CH46" s="119" t="n"/>
-      <c r="CI46" s="119" t="n"/>
-      <c r="CJ46" s="119" t="n"/>
-      <c r="CK46" s="119" t="n"/>
-      <c r="CL46" s="119" t="n"/>
-      <c r="CM46" s="119" t="n"/>
-      <c r="CN46" s="119" t="n"/>
-      <c r="CO46" s="119" t="n"/>
-      <c r="CP46" s="119" t="n"/>
-      <c r="CQ46" s="119" t="n"/>
-      <c r="CR46" s="119" t="n"/>
-      <c r="CS46" s="119" t="n"/>
-      <c r="CT46" s="119" t="n"/>
-      <c r="CU46" s="119" t="n"/>
-      <c r="CV46" s="119" t="n"/>
-      <c r="CW46" s="119" t="n"/>
-      <c r="CX46" s="119" t="n"/>
-      <c r="CY46" s="119" t="n"/>
-      <c r="CZ46" s="119" t="n"/>
-      <c r="DA46" s="119" t="n"/>
-      <c r="DB46" s="119" t="n"/>
-      <c r="DC46" s="119" t="n"/>
-      <c r="DD46" s="119" t="n"/>
-      <c r="DE46" s="119" t="n"/>
-      <c r="DF46" s="119" t="n"/>
-      <c r="DG46" s="119" t="n"/>
-      <c r="DH46" s="119" t="n"/>
-      <c r="DI46" s="119" t="n"/>
-      <c r="DJ46" s="119" t="n"/>
-      <c r="DK46" s="119" t="n"/>
-      <c r="DL46" s="119" t="n"/>
-      <c r="DM46" s="119" t="n"/>
-      <c r="DN46" s="119" t="n"/>
-      <c r="DO46" s="119" t="n"/>
-      <c r="DP46" s="119" t="n"/>
-      <c r="DQ46" s="119" t="n"/>
-      <c r="DR46" s="119" t="n"/>
-      <c r="DS46" s="119" t="n"/>
-      <c r="DT46" s="119" t="n"/>
-      <c r="DU46" s="119" t="n"/>
-      <c r="DV46" s="119" t="n"/>
-      <c r="DW46" s="119" t="n"/>
-      <c r="DX46" s="119" t="n"/>
-      <c r="DY46" s="119" t="n"/>
-      <c r="DZ46" s="119" t="n"/>
-      <c r="EA46" s="119" t="n"/>
-      <c r="EB46" s="119" t="n"/>
-      <c r="EC46" s="119" t="n"/>
-      <c r="ED46" s="119" t="n"/>
-      <c r="EE46" s="119" t="n"/>
-      <c r="EF46" s="119" t="n"/>
-      <c r="EG46" s="119" t="n"/>
-      <c r="EH46" s="119" t="n"/>
-      <c r="EI46" s="119" t="n"/>
-      <c r="EJ46" s="119" t="n"/>
-      <c r="EK46" s="119" t="n"/>
-      <c r="EL46" s="119" t="n"/>
-      <c r="EM46" s="119" t="n"/>
-      <c r="EN46" s="119" t="n"/>
-      <c r="EO46" s="119" t="n"/>
-      <c r="EP46" s="119" t="n"/>
-      <c r="EQ46" s="119" t="n"/>
-      <c r="ER46" s="119" t="n"/>
-      <c r="ES46" s="119" t="n"/>
-      <c r="ET46" s="119" t="n"/>
-      <c r="EU46" s="119" t="n"/>
-      <c r="EV46" s="119" t="n"/>
-      <c r="EW46" s="119" t="n"/>
-      <c r="EX46" s="119" t="n"/>
-      <c r="EY46" s="119" t="n"/>
-      <c r="EZ46" s="119" t="n"/>
-      <c r="FA46" s="119" t="n"/>
-      <c r="FB46" s="119" t="n"/>
-      <c r="FC46" s="119" t="n"/>
-      <c r="FD46" s="119" t="n"/>
-      <c r="FE46" s="119" t="n"/>
-      <c r="FF46" s="119" t="n"/>
-      <c r="FG46" s="119" t="n"/>
-      <c r="FH46" s="119" t="n"/>
-      <c r="FI46" s="119" t="n"/>
-      <c r="FJ46" s="119" t="n"/>
-      <c r="FK46" s="119" t="n"/>
-      <c r="FL46" s="119" t="n"/>
-      <c r="FM46" s="119" t="n"/>
-      <c r="FN46" s="119" t="n"/>
-      <c r="FO46" s="119" t="n"/>
-      <c r="FP46" s="119" t="n"/>
-      <c r="FQ46" s="119" t="n"/>
-      <c r="FR46" s="119" t="n"/>
-      <c r="FS46" s="119" t="n"/>
-      <c r="FT46" s="119" t="n"/>
-      <c r="FU46" s="119" t="n"/>
-      <c r="FV46" s="119" t="n"/>
-      <c r="FW46" s="119" t="n"/>
-      <c r="FX46" s="119" t="n"/>
-      <c r="FY46" s="119" t="n"/>
-      <c r="FZ46" s="119" t="n"/>
-      <c r="GA46" s="119" t="n"/>
-      <c r="GB46" s="119" t="n"/>
-      <c r="GC46" s="119" t="n"/>
-      <c r="GD46" s="119" t="n"/>
-      <c r="GE46" s="119" t="n"/>
-      <c r="GF46" s="119" t="n"/>
-      <c r="GG46" s="119" t="n"/>
-      <c r="GH46" s="119" t="n"/>
-      <c r="GI46" s="119" t="n"/>
-      <c r="GJ46" s="119" t="n"/>
-      <c r="GK46" s="119" t="n"/>
-      <c r="GL46" s="119" t="n"/>
-      <c r="GM46" s="119" t="n"/>
-      <c r="GN46" s="119" t="n"/>
-      <c r="GO46" s="119" t="n"/>
-      <c r="GP46" s="119" t="n"/>
-      <c r="GQ46" s="119" t="n"/>
-      <c r="GR46" s="119" t="n"/>
-      <c r="GS46" s="119" t="n"/>
-      <c r="GT46" s="119" t="n"/>
-      <c r="GU46" s="119" t="n"/>
-      <c r="GV46" s="119" t="n"/>
-      <c r="GW46" s="119" t="n"/>
-      <c r="GX46" s="119" t="n"/>
-      <c r="GY46" s="119" t="n"/>
-      <c r="GZ46" s="119" t="n"/>
-      <c r="HA46" s="119" t="n"/>
-      <c r="HB46" s="119" t="n"/>
-      <c r="HC46" s="119" t="n"/>
-      <c r="HD46" s="119" t="n"/>
-      <c r="HE46" s="119" t="n"/>
-      <c r="HF46" s="119" t="n"/>
-      <c r="HG46" s="119" t="n"/>
-      <c r="HH46" s="119" t="n"/>
-      <c r="HI46" s="119" t="n"/>
-      <c r="HJ46" s="119" t="n"/>
-      <c r="HK46" s="119" t="n"/>
-      <c r="HL46" s="119" t="n"/>
-      <c r="HM46" s="119" t="n"/>
-      <c r="HN46" s="119" t="n"/>
-      <c r="HO46" s="119" t="n"/>
-      <c r="HP46" s="119" t="n"/>
-      <c r="HQ46" s="119" t="n"/>
-      <c r="HR46" s="119" t="n"/>
-      <c r="HS46" s="119" t="n"/>
-      <c r="HT46" s="119" t="n"/>
-      <c r="HU46" s="119" t="n"/>
-    </row>
-    <row r="47" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A47" s="58" t="n"/>
-      <c r="B47" s="121" t="n"/>
-      <c r="C47" s="122" t="n"/>
-      <c r="D47" s="123" t="n"/>
-      <c r="E47" s="124" t="n"/>
-      <c r="F47" s="55" t="n"/>
-      <c r="G47" s="125" t="n"/>
-      <c r="H47" s="56" t="n"/>
-      <c r="I47" s="57" t="n"/>
-      <c r="J47" s="125" t="n"/>
-      <c r="K47" s="126" t="n"/>
-      <c r="L47" s="59" t="n"/>
-      <c r="M47" s="60" t="n"/>
-      <c r="N47" s="57" t="n"/>
-      <c r="O47" s="59" t="n"/>
-      <c r="P47" s="57" t="n"/>
-      <c r="Q47" s="57" t="n"/>
-      <c r="R47" s="57" t="n"/>
-      <c r="S47" s="57" t="n"/>
-      <c r="T47" s="57" t="n"/>
-      <c r="U47" s="57" t="n"/>
-      <c r="V47" s="57" t="n"/>
-      <c r="W47" s="57">
-        <f>SUM(K47:U47)</f>
-        <v/>
-      </c>
-      <c r="X47" s="57" t="n"/>
-      <c r="Y47" s="57" t="n">
-        <v>20000</v>
-      </c>
-      <c r="Z47" s="59" t="n"/>
-      <c r="AA47" s="57">
-        <f>SUM(X47:Z47)</f>
-        <v/>
-      </c>
-      <c r="AB47" s="57">
-        <f>+W47+AA47</f>
-        <v/>
-      </c>
-      <c r="AC47" s="63" t="inlineStr">
-        <is>
-          <t>0318092</t>
-        </is>
-      </c>
-      <c r="AD47" s="149" t="n"/>
-      <c r="AE47" s="119" t="n"/>
-      <c r="AF47" s="119" t="n"/>
-      <c r="AG47" s="119" t="n"/>
-      <c r="AH47" s="119" t="n"/>
-      <c r="AI47" s="119" t="n"/>
-      <c r="AJ47" s="119" t="n"/>
-      <c r="AK47" s="119" t="n"/>
-      <c r="AL47" s="119" t="n"/>
-      <c r="AM47" s="119" t="n"/>
-      <c r="AN47" s="119" t="n"/>
-      <c r="AO47" s="119" t="n"/>
-      <c r="AP47" s="119" t="n"/>
-      <c r="AQ47" s="119" t="n"/>
-      <c r="AR47" s="119" t="n"/>
-      <c r="AS47" s="119" t="n"/>
-      <c r="AT47" s="119" t="n"/>
-      <c r="AU47" s="119" t="n"/>
-      <c r="AV47" s="119" t="n"/>
-      <c r="AW47" s="119" t="n"/>
-      <c r="AX47" s="119" t="n"/>
-      <c r="AY47" s="119" t="n"/>
-      <c r="AZ47" s="119" t="n"/>
-      <c r="BA47" s="119" t="n"/>
-      <c r="BB47" s="119" t="n"/>
-      <c r="BC47" s="119" t="n"/>
-      <c r="BD47" s="119" t="n"/>
-      <c r="BE47" s="119" t="n"/>
-      <c r="BF47" s="119" t="n"/>
-      <c r="BG47" s="119" t="n"/>
-      <c r="BH47" s="119" t="n"/>
-      <c r="BI47" s="119" t="n"/>
-      <c r="BJ47" s="119" t="n"/>
-      <c r="BK47" s="119" t="n"/>
-      <c r="BL47" s="119" t="n"/>
-      <c r="BM47" s="119" t="n"/>
-      <c r="BN47" s="119" t="n"/>
-      <c r="BO47" s="119" t="n"/>
-      <c r="BP47" s="119" t="n"/>
-      <c r="BQ47" s="119" t="n"/>
-      <c r="BR47" s="119" t="n"/>
-      <c r="BS47" s="119" t="n"/>
-      <c r="BT47" s="119" t="n"/>
-      <c r="BU47" s="119" t="n"/>
-      <c r="BV47" s="119" t="n"/>
-      <c r="BW47" s="119" t="n"/>
-      <c r="BX47" s="119" t="n"/>
-      <c r="BY47" s="119" t="n"/>
-      <c r="BZ47" s="119" t="n"/>
-      <c r="CA47" s="119" t="n"/>
-      <c r="CB47" s="119" t="n"/>
-      <c r="CC47" s="119" t="n"/>
-      <c r="CD47" s="119" t="n"/>
-      <c r="CE47" s="119" t="n"/>
-      <c r="CF47" s="119" t="n"/>
-      <c r="CG47" s="119" t="n"/>
-      <c r="CH47" s="119" t="n"/>
-      <c r="CI47" s="119" t="n"/>
-      <c r="CJ47" s="119" t="n"/>
-      <c r="CK47" s="119" t="n"/>
-      <c r="CL47" s="119" t="n"/>
-      <c r="CM47" s="119" t="n"/>
-      <c r="CN47" s="119" t="n"/>
-      <c r="CO47" s="119" t="n"/>
-      <c r="CP47" s="119" t="n"/>
-      <c r="CQ47" s="119" t="n"/>
-      <c r="CR47" s="119" t="n"/>
-      <c r="CS47" s="119" t="n"/>
-      <c r="CT47" s="119" t="n"/>
-      <c r="CU47" s="119" t="n"/>
-      <c r="CV47" s="119" t="n"/>
-      <c r="CW47" s="119" t="n"/>
-      <c r="CX47" s="119" t="n"/>
-      <c r="CY47" s="119" t="n"/>
-      <c r="CZ47" s="119" t="n"/>
-      <c r="DA47" s="119" t="n"/>
-      <c r="DB47" s="119" t="n"/>
-      <c r="DC47" s="119" t="n"/>
-      <c r="DD47" s="119" t="n"/>
-      <c r="DE47" s="119" t="n"/>
-      <c r="DF47" s="119" t="n"/>
-      <c r="DG47" s="119" t="n"/>
-      <c r="DH47" s="119" t="n"/>
-      <c r="DI47" s="119" t="n"/>
-      <c r="DJ47" s="119" t="n"/>
-      <c r="DK47" s="119" t="n"/>
-      <c r="DL47" s="119" t="n"/>
-      <c r="DM47" s="119" t="n"/>
-      <c r="DN47" s="119" t="n"/>
-      <c r="DO47" s="119" t="n"/>
-      <c r="DP47" s="119" t="n"/>
-      <c r="DQ47" s="119" t="n"/>
-      <c r="DR47" s="119" t="n"/>
-      <c r="DS47" s="119" t="n"/>
-      <c r="DT47" s="119" t="n"/>
-      <c r="DU47" s="119" t="n"/>
-      <c r="DV47" s="119" t="n"/>
-      <c r="DW47" s="119" t="n"/>
-      <c r="DX47" s="119" t="n"/>
-      <c r="DY47" s="119" t="n"/>
-      <c r="DZ47" s="119" t="n"/>
-      <c r="EA47" s="119" t="n"/>
-      <c r="EB47" s="119" t="n"/>
-      <c r="EC47" s="119" t="n"/>
-      <c r="ED47" s="119" t="n"/>
-      <c r="EE47" s="119" t="n"/>
-      <c r="EF47" s="119" t="n"/>
-      <c r="EG47" s="119" t="n"/>
-      <c r="EH47" s="119" t="n"/>
-      <c r="EI47" s="119" t="n"/>
-      <c r="EJ47" s="119" t="n"/>
-      <c r="EK47" s="119" t="n"/>
-      <c r="EL47" s="119" t="n"/>
-      <c r="EM47" s="119" t="n"/>
-      <c r="EN47" s="119" t="n"/>
-      <c r="EO47" s="119" t="n"/>
-      <c r="EP47" s="119" t="n"/>
-      <c r="EQ47" s="119" t="n"/>
-      <c r="ER47" s="119" t="n"/>
-      <c r="ES47" s="119" t="n"/>
-      <c r="ET47" s="119" t="n"/>
-      <c r="EU47" s="119" t="n"/>
-      <c r="EV47" s="119" t="n"/>
-      <c r="EW47" s="119" t="n"/>
-      <c r="EX47" s="119" t="n"/>
-      <c r="EY47" s="119" t="n"/>
-      <c r="EZ47" s="119" t="n"/>
-      <c r="FA47" s="119" t="n"/>
-      <c r="FB47" s="119" t="n"/>
-      <c r="FC47" s="119" t="n"/>
-      <c r="FD47" s="119" t="n"/>
-      <c r="FE47" s="119" t="n"/>
-      <c r="FF47" s="119" t="n"/>
-      <c r="FG47" s="119" t="n"/>
-      <c r="FH47" s="119" t="n"/>
-      <c r="FI47" s="119" t="n"/>
-      <c r="FJ47" s="119" t="n"/>
-      <c r="FK47" s="119" t="n"/>
-      <c r="FL47" s="119" t="n"/>
-      <c r="FM47" s="119" t="n"/>
-      <c r="FN47" s="119" t="n"/>
-      <c r="FO47" s="119" t="n"/>
-      <c r="FP47" s="119" t="n"/>
-      <c r="FQ47" s="119" t="n"/>
-      <c r="FR47" s="119" t="n"/>
-      <c r="FS47" s="119" t="n"/>
-      <c r="FT47" s="119" t="n"/>
-      <c r="FU47" s="119" t="n"/>
-      <c r="FV47" s="119" t="n"/>
-      <c r="FW47" s="119" t="n"/>
-      <c r="FX47" s="119" t="n"/>
-      <c r="FY47" s="119" t="n"/>
-      <c r="FZ47" s="119" t="n"/>
-      <c r="GA47" s="119" t="n"/>
-      <c r="GB47" s="119" t="n"/>
-      <c r="GC47" s="119" t="n"/>
-      <c r="GD47" s="119" t="n"/>
-      <c r="GE47" s="119" t="n"/>
-      <c r="GF47" s="119" t="n"/>
-      <c r="GG47" s="119" t="n"/>
-      <c r="GH47" s="119" t="n"/>
-      <c r="GI47" s="119" t="n"/>
-      <c r="GJ47" s="119" t="n"/>
-      <c r="GK47" s="119" t="n"/>
-      <c r="GL47" s="119" t="n"/>
-      <c r="GM47" s="119" t="n"/>
-      <c r="GN47" s="119" t="n"/>
-      <c r="GO47" s="119" t="n"/>
-      <c r="GP47" s="119" t="n"/>
-      <c r="GQ47" s="119" t="n"/>
-      <c r="GR47" s="119" t="n"/>
-      <c r="GS47" s="119" t="n"/>
-      <c r="GT47" s="119" t="n"/>
-      <c r="GU47" s="119" t="n"/>
-      <c r="GV47" s="119" t="n"/>
-      <c r="GW47" s="119" t="n"/>
-      <c r="GX47" s="119" t="n"/>
-      <c r="GY47" s="119" t="n"/>
-      <c r="GZ47" s="119" t="n"/>
-      <c r="HA47" s="119" t="n"/>
-      <c r="HB47" s="119" t="n"/>
-      <c r="HC47" s="119" t="n"/>
-      <c r="HD47" s="119" t="n"/>
-      <c r="HE47" s="119" t="n"/>
-      <c r="HF47" s="119" t="n"/>
-      <c r="HG47" s="119" t="n"/>
-      <c r="HH47" s="119" t="n"/>
-      <c r="HI47" s="119" t="n"/>
-      <c r="HJ47" s="119" t="n"/>
-      <c r="HK47" s="119" t="n"/>
-      <c r="HL47" s="119" t="n"/>
-      <c r="HM47" s="119" t="n"/>
-      <c r="HN47" s="119" t="n"/>
-      <c r="HO47" s="119" t="n"/>
-      <c r="HP47" s="119" t="n"/>
-      <c r="HQ47" s="119" t="n"/>
-      <c r="HR47" s="119" t="n"/>
-      <c r="HS47" s="119" t="n"/>
-      <c r="HT47" s="119" t="n"/>
-      <c r="HU47" s="119" t="n"/>
-    </row>
-    <row r="48" ht="52" customFormat="1" customHeight="1" s="120">
-      <c r="A48" s="58" t="n"/>
-      <c r="B48" s="121" t="n"/>
-      <c r="C48" s="122" t="n"/>
-      <c r="D48" s="123" t="n"/>
-      <c r="E48" s="124" t="n"/>
-      <c r="F48" s="55" t="n"/>
-      <c r="G48" s="125" t="n"/>
-      <c r="H48" s="56" t="n"/>
-      <c r="I48" s="57" t="n"/>
-      <c r="J48" s="125" t="n"/>
-      <c r="K48" s="126" t="n"/>
-      <c r="L48" s="59" t="n"/>
-      <c r="M48" s="60" t="n"/>
-      <c r="N48" s="57" t="n"/>
-      <c r="O48" s="59" t="n"/>
-      <c r="P48" s="57" t="n"/>
-      <c r="Q48" s="57" t="n"/>
-      <c r="R48" s="57" t="n"/>
-      <c r="S48" s="57" t="n"/>
-      <c r="T48" s="57" t="n"/>
-      <c r="U48" s="57" t="n"/>
-      <c r="V48" s="57" t="n"/>
-      <c r="W48" s="57">
-        <f>SUM(K48:U48)</f>
-        <v/>
-      </c>
-      <c r="X48" s="57" t="n"/>
-      <c r="Y48" s="57" t="n">
-        <v>20000</v>
-      </c>
-      <c r="Z48" s="59" t="n"/>
-      <c r="AA48" s="57">
-        <f>SUM(X48:Z48)</f>
-        <v/>
-      </c>
-      <c r="AB48" s="57">
-        <f>+W48+AA48</f>
-        <v/>
-      </c>
-      <c r="AC48" s="63" t="inlineStr">
-        <is>
-          <t>0318086</t>
-        </is>
-      </c>
-      <c r="AD48" s="149" t="n"/>
-      <c r="AE48" s="119" t="n"/>
-      <c r="AF48" s="119" t="n"/>
-      <c r="AG48" s="119" t="n"/>
-      <c r="AH48" s="119" t="n"/>
-      <c r="AI48" s="119" t="n"/>
-      <c r="AJ48" s="119" t="n"/>
-      <c r="AK48" s="119" t="n"/>
-      <c r="AL48" s="119" t="n"/>
-      <c r="AM48" s="119" t="n"/>
-      <c r="AN48" s="119" t="n"/>
-      <c r="AO48" s="119" t="n"/>
-      <c r="AP48" s="119" t="n"/>
-      <c r="AQ48" s="119" t="n"/>
-      <c r="AR48" s="119" t="n"/>
-      <c r="AS48" s="119" t="n"/>
-      <c r="AT48" s="119" t="n"/>
-      <c r="AU48" s="119" t="n"/>
-      <c r="AV48" s="119" t="n"/>
-      <c r="AW48" s="119" t="n"/>
-      <c r="AX48" s="119" t="n"/>
-      <c r="AY48" s="119" t="n"/>
-      <c r="AZ48" s="119" t="n"/>
-      <c r="BA48" s="119" t="n"/>
-      <c r="BB48" s="119" t="n"/>
-      <c r="BC48" s="119" t="n"/>
-      <c r="BD48" s="119" t="n"/>
-      <c r="BE48" s="119" t="n"/>
-      <c r="BF48" s="119" t="n"/>
-      <c r="BG48" s="119" t="n"/>
-      <c r="BH48" s="119" t="n"/>
-      <c r="BI48" s="119" t="n"/>
-      <c r="BJ48" s="119" t="n"/>
-      <c r="BK48" s="119" t="n"/>
-      <c r="BL48" s="119" t="n"/>
-      <c r="BM48" s="119" t="n"/>
-      <c r="BN48" s="119" t="n"/>
-      <c r="BO48" s="119" t="n"/>
-      <c r="BP48" s="119" t="n"/>
-      <c r="BQ48" s="119" t="n"/>
-      <c r="BR48" s="119" t="n"/>
-      <c r="BS48" s="119" t="n"/>
-      <c r="BT48" s="119" t="n"/>
-      <c r="BU48" s="119" t="n"/>
-      <c r="BV48" s="119" t="n"/>
-      <c r="BW48" s="119" t="n"/>
-      <c r="BX48" s="119" t="n"/>
-      <c r="BY48" s="119" t="n"/>
-      <c r="BZ48" s="119" t="n"/>
-      <c r="CA48" s="119" t="n"/>
-      <c r="CB48" s="119" t="n"/>
-      <c r="CC48" s="119" t="n"/>
-      <c r="CD48" s="119" t="n"/>
-      <c r="CE48" s="119" t="n"/>
-      <c r="CF48" s="119" t="n"/>
-      <c r="CG48" s="119" t="n"/>
-      <c r="CH48" s="119" t="n"/>
-      <c r="CI48" s="119" t="n"/>
-      <c r="CJ48" s="119" t="n"/>
-      <c r="CK48" s="119" t="n"/>
-      <c r="CL48" s="119" t="n"/>
-      <c r="CM48" s="119" t="n"/>
-      <c r="CN48" s="119" t="n"/>
-      <c r="CO48" s="119" t="n"/>
-      <c r="CP48" s="119" t="n"/>
-      <c r="CQ48" s="119" t="n"/>
-      <c r="CR48" s="119" t="n"/>
-      <c r="CS48" s="119" t="n"/>
-      <c r="CT48" s="119" t="n"/>
-      <c r="CU48" s="119" t="n"/>
-      <c r="CV48" s="119" t="n"/>
-      <c r="CW48" s="119" t="n"/>
-      <c r="CX48" s="119" t="n"/>
-      <c r="CY48" s="119" t="n"/>
-      <c r="CZ48" s="119" t="n"/>
-      <c r="DA48" s="119" t="n"/>
-      <c r="DB48" s="119" t="n"/>
-      <c r="DC48" s="119" t="n"/>
-      <c r="DD48" s="119" t="n"/>
-      <c r="DE48" s="119" t="n"/>
-      <c r="DF48" s="119" t="n"/>
-      <c r="DG48" s="119" t="n"/>
-      <c r="DH48" s="119" t="n"/>
-      <c r="DI48" s="119" t="n"/>
-      <c r="DJ48" s="119" t="n"/>
-      <c r="DK48" s="119" t="n"/>
-      <c r="DL48" s="119" t="n"/>
-      <c r="DM48" s="119" t="n"/>
-      <c r="DN48" s="119" t="n"/>
-      <c r="DO48" s="119" t="n"/>
-      <c r="DP48" s="119" t="n"/>
-      <c r="DQ48" s="119" t="n"/>
-      <c r="DR48" s="119" t="n"/>
-      <c r="DS48" s="119" t="n"/>
-      <c r="DT48" s="119" t="n"/>
-      <c r="DU48" s="119" t="n"/>
-      <c r="DV48" s="119" t="n"/>
-      <c r="DW48" s="119" t="n"/>
-      <c r="DX48" s="119" t="n"/>
-      <c r="DY48" s="119" t="n"/>
-      <c r="DZ48" s="119" t="n"/>
-      <c r="EA48" s="119" t="n"/>
-      <c r="EB48" s="119" t="n"/>
-      <c r="EC48" s="119" t="n"/>
-      <c r="ED48" s="119" t="n"/>
-      <c r="EE48" s="119" t="n"/>
-      <c r="EF48" s="119" t="n"/>
-      <c r="EG48" s="119" t="n"/>
-      <c r="EH48" s="119" t="n"/>
-      <c r="EI48" s="119" t="n"/>
-      <c r="EJ48" s="119" t="n"/>
-      <c r="EK48" s="119" t="n"/>
-      <c r="EL48" s="119" t="n"/>
-      <c r="EM48" s="119" t="n"/>
-      <c r="EN48" s="119" t="n"/>
-      <c r="EO48" s="119" t="n"/>
-      <c r="EP48" s="119" t="n"/>
-      <c r="EQ48" s="119" t="n"/>
-      <c r="ER48" s="119" t="n"/>
-      <c r="ES48" s="119" t="n"/>
-      <c r="ET48" s="119" t="n"/>
-      <c r="EU48" s="119" t="n"/>
-      <c r="EV48" s="119" t="n"/>
-      <c r="EW48" s="119" t="n"/>
-      <c r="EX48" s="119" t="n"/>
-      <c r="EY48" s="119" t="n"/>
-      <c r="EZ48" s="119" t="n"/>
-      <c r="FA48" s="119" t="n"/>
-      <c r="FB48" s="119" t="n"/>
-      <c r="FC48" s="119" t="n"/>
-      <c r="FD48" s="119" t="n"/>
-      <c r="FE48" s="119" t="n"/>
-      <c r="FF48" s="119" t="n"/>
-      <c r="FG48" s="119" t="n"/>
-      <c r="FH48" s="119" t="n"/>
-      <c r="FI48" s="119" t="n"/>
-      <c r="FJ48" s="119" t="n"/>
-      <c r="FK48" s="119" t="n"/>
-      <c r="FL48" s="119" t="n"/>
-      <c r="FM48" s="119" t="n"/>
-      <c r="FN48" s="119" t="n"/>
-      <c r="FO48" s="119" t="n"/>
-      <c r="FP48" s="119" t="n"/>
-      <c r="FQ48" s="119" t="n"/>
-      <c r="FR48" s="119" t="n"/>
-      <c r="FS48" s="119" t="n"/>
-      <c r="FT48" s="119" t="n"/>
-      <c r="FU48" s="119" t="n"/>
-      <c r="FV48" s="119" t="n"/>
-      <c r="FW48" s="119" t="n"/>
-      <c r="FX48" s="119" t="n"/>
-      <c r="FY48" s="119" t="n"/>
-      <c r="FZ48" s="119" t="n"/>
-      <c r="GA48" s="119" t="n"/>
-      <c r="GB48" s="119" t="n"/>
-      <c r="GC48" s="119" t="n"/>
-      <c r="GD48" s="119" t="n"/>
-      <c r="GE48" s="119" t="n"/>
-      <c r="GF48" s="119" t="n"/>
-      <c r="GG48" s="119" t="n"/>
-      <c r="GH48" s="119" t="n"/>
-      <c r="GI48" s="119" t="n"/>
-      <c r="GJ48" s="119" t="n"/>
-      <c r="GK48" s="119" t="n"/>
-      <c r="GL48" s="119" t="n"/>
-      <c r="GM48" s="119" t="n"/>
-      <c r="GN48" s="119" t="n"/>
-      <c r="GO48" s="119" t="n"/>
-      <c r="GP48" s="119" t="n"/>
-      <c r="GQ48" s="119" t="n"/>
-      <c r="GR48" s="119" t="n"/>
-      <c r="GS48" s="119" t="n"/>
-      <c r="GT48" s="119" t="n"/>
-      <c r="GU48" s="119" t="n"/>
-      <c r="GV48" s="119" t="n"/>
-      <c r="GW48" s="119" t="n"/>
-      <c r="GX48" s="119" t="n"/>
-      <c r="GY48" s="119" t="n"/>
-      <c r="GZ48" s="119" t="n"/>
-      <c r="HA48" s="119" t="n"/>
-      <c r="HB48" s="119" t="n"/>
-      <c r="HC48" s="119" t="n"/>
-      <c r="HD48" s="119" t="n"/>
-      <c r="HE48" s="119" t="n"/>
-      <c r="HF48" s="119" t="n"/>
-      <c r="HG48" s="119" t="n"/>
-      <c r="HH48" s="119" t="n"/>
-      <c r="HI48" s="119" t="n"/>
-      <c r="HJ48" s="119" t="n"/>
-      <c r="HK48" s="119" t="n"/>
-      <c r="HL48" s="119" t="n"/>
-      <c r="HM48" s="119" t="n"/>
-      <c r="HN48" s="119" t="n"/>
-      <c r="HO48" s="119" t="n"/>
-      <c r="HP48" s="119" t="n"/>
-      <c r="HQ48" s="119" t="n"/>
-      <c r="HR48" s="119" t="n"/>
-      <c r="HS48" s="119" t="n"/>
-      <c r="HT48" s="119" t="n"/>
-      <c r="HU48" s="119" t="n"/>
-    </row>
-    <row r="49" ht="52" customFormat="1" customHeight="1" s="120" thickBot="1">
-      <c r="A49" s="129" t="n"/>
-      <c r="B49" s="130" t="n"/>
-      <c r="C49" s="131" t="n"/>
-      <c r="D49" s="132" t="n"/>
-      <c r="E49" s="133" t="n"/>
-      <c r="F49" s="134" t="n"/>
-      <c r="G49" s="135" t="n"/>
-      <c r="H49" s="136" t="n"/>
-      <c r="I49" s="137" t="n"/>
-      <c r="J49" s="135" t="n"/>
-      <c r="K49" s="138" t="n"/>
-      <c r="L49" s="139" t="n"/>
-      <c r="M49" s="140" t="n"/>
-      <c r="N49" s="137" t="n"/>
-      <c r="O49" s="139" t="n"/>
-      <c r="P49" s="137" t="n"/>
-      <c r="Q49" s="137" t="n"/>
-      <c r="R49" s="137" t="n"/>
-      <c r="S49" s="137" t="n"/>
-      <c r="T49" s="137" t="n"/>
-      <c r="U49" s="137" t="n"/>
-      <c r="V49" s="137" t="n"/>
-      <c r="W49" s="137">
-        <f>SUM(K49:U49)</f>
-        <v/>
-      </c>
-      <c r="X49" s="137" t="n"/>
-      <c r="Y49" s="137" t="n">
-        <v>20000</v>
-      </c>
-      <c r="Z49" s="139" t="n"/>
-      <c r="AA49" s="137">
-        <f>SUM(X49:Z49)</f>
-        <v/>
-      </c>
-      <c r="AB49" s="137">
-        <f>+W49+AA49</f>
-        <v/>
-      </c>
-      <c r="AC49" s="128" t="inlineStr">
-        <is>
-          <t>0318084</t>
-        </is>
-      </c>
-      <c r="AD49" s="150" t="n"/>
-      <c r="AE49" s="119" t="n"/>
-      <c r="AF49" s="119" t="n"/>
-      <c r="AG49" s="119" t="n"/>
-      <c r="AH49" s="119" t="n"/>
-      <c r="AI49" s="119" t="n"/>
-      <c r="AJ49" s="119" t="n"/>
-      <c r="AK49" s="119" t="n"/>
-      <c r="AL49" s="119" t="n"/>
-      <c r="AM49" s="119" t="n"/>
-      <c r="AN49" s="119" t="n"/>
-      <c r="AO49" s="119" t="n"/>
-      <c r="AP49" s="119" t="n"/>
-      <c r="AQ49" s="119" t="n"/>
-      <c r="AR49" s="119" t="n"/>
-      <c r="AS49" s="119" t="n"/>
-      <c r="AT49" s="119" t="n"/>
-      <c r="AU49" s="119" t="n"/>
-      <c r="AV49" s="119" t="n"/>
-      <c r="AW49" s="119" t="n"/>
-      <c r="AX49" s="119" t="n"/>
-      <c r="AY49" s="119" t="n"/>
-      <c r="AZ49" s="119" t="n"/>
-      <c r="BA49" s="119" t="n"/>
-      <c r="BB49" s="119" t="n"/>
-      <c r="BC49" s="119" t="n"/>
-      <c r="BD49" s="119" t="n"/>
-      <c r="BE49" s="119" t="n"/>
-      <c r="BF49" s="119" t="n"/>
-      <c r="BG49" s="119" t="n"/>
-      <c r="BH49" s="119" t="n"/>
-      <c r="BI49" s="119" t="n"/>
-      <c r="BJ49" s="119" t="n"/>
-      <c r="BK49" s="119" t="n"/>
-      <c r="BL49" s="119" t="n"/>
-      <c r="BM49" s="119" t="n"/>
-      <c r="BN49" s="119" t="n"/>
-      <c r="BO49" s="119" t="n"/>
-      <c r="BP49" s="119" t="n"/>
-      <c r="BQ49" s="119" t="n"/>
-      <c r="BR49" s="119" t="n"/>
-      <c r="BS49" s="119" t="n"/>
-      <c r="BT49" s="119" t="n"/>
-      <c r="BU49" s="119" t="n"/>
-      <c r="BV49" s="119" t="n"/>
-      <c r="BW49" s="119" t="n"/>
-      <c r="BX49" s="119" t="n"/>
-      <c r="BY49" s="119" t="n"/>
-      <c r="BZ49" s="119" t="n"/>
-      <c r="CA49" s="119" t="n"/>
-      <c r="CB49" s="119" t="n"/>
-      <c r="CC49" s="119" t="n"/>
-      <c r="CD49" s="119" t="n"/>
-      <c r="CE49" s="119" t="n"/>
-      <c r="CF49" s="119" t="n"/>
-      <c r="CG49" s="119" t="n"/>
-      <c r="CH49" s="119" t="n"/>
-      <c r="CI49" s="119" t="n"/>
-      <c r="CJ49" s="119" t="n"/>
-      <c r="CK49" s="119" t="n"/>
-      <c r="CL49" s="119" t="n"/>
-      <c r="CM49" s="119" t="n"/>
-      <c r="CN49" s="119" t="n"/>
-      <c r="CO49" s="119" t="n"/>
-      <c r="CP49" s="119" t="n"/>
-      <c r="CQ49" s="119" t="n"/>
-      <c r="CR49" s="119" t="n"/>
-      <c r="CS49" s="119" t="n"/>
-      <c r="CT49" s="119" t="n"/>
-      <c r="CU49" s="119" t="n"/>
-      <c r="CV49" s="119" t="n"/>
-      <c r="CW49" s="119" t="n"/>
-      <c r="CX49" s="119" t="n"/>
-      <c r="CY49" s="119" t="n"/>
-      <c r="CZ49" s="119" t="n"/>
-      <c r="DA49" s="119" t="n"/>
-      <c r="DB49" s="119" t="n"/>
-      <c r="DC49" s="119" t="n"/>
-      <c r="DD49" s="119" t="n"/>
-      <c r="DE49" s="119" t="n"/>
-      <c r="DF49" s="119" t="n"/>
-      <c r="DG49" s="119" t="n"/>
-      <c r="DH49" s="119" t="n"/>
-      <c r="DI49" s="119" t="n"/>
-      <c r="DJ49" s="119" t="n"/>
-      <c r="DK49" s="119" t="n"/>
-      <c r="DL49" s="119" t="n"/>
-      <c r="DM49" s="119" t="n"/>
-      <c r="DN49" s="119" t="n"/>
-      <c r="DO49" s="119" t="n"/>
-      <c r="DP49" s="119" t="n"/>
-      <c r="DQ49" s="119" t="n"/>
-      <c r="DR49" s="119" t="n"/>
-      <c r="DS49" s="119" t="n"/>
-      <c r="DT49" s="119" t="n"/>
-      <c r="DU49" s="119" t="n"/>
-      <c r="DV49" s="119" t="n"/>
-      <c r="DW49" s="119" t="n"/>
-      <c r="DX49" s="119" t="n"/>
-      <c r="DY49" s="119" t="n"/>
-      <c r="DZ49" s="119" t="n"/>
-      <c r="EA49" s="119" t="n"/>
-      <c r="EB49" s="119" t="n"/>
-      <c r="EC49" s="119" t="n"/>
-      <c r="ED49" s="119" t="n"/>
-      <c r="EE49" s="119" t="n"/>
-      <c r="EF49" s="119" t="n"/>
-      <c r="EG49" s="119" t="n"/>
-      <c r="EH49" s="119" t="n"/>
-      <c r="EI49" s="119" t="n"/>
-      <c r="EJ49" s="119" t="n"/>
-      <c r="EK49" s="119" t="n"/>
-      <c r="EL49" s="119" t="n"/>
-      <c r="EM49" s="119" t="n"/>
-      <c r="EN49" s="119" t="n"/>
-      <c r="EO49" s="119" t="n"/>
-      <c r="EP49" s="119" t="n"/>
-      <c r="EQ49" s="119" t="n"/>
-      <c r="ER49" s="119" t="n"/>
-      <c r="ES49" s="119" t="n"/>
-      <c r="ET49" s="119" t="n"/>
-      <c r="EU49" s="119" t="n"/>
-      <c r="EV49" s="119" t="n"/>
-      <c r="EW49" s="119" t="n"/>
-      <c r="EX49" s="119" t="n"/>
-      <c r="EY49" s="119" t="n"/>
-      <c r="EZ49" s="119" t="n"/>
-      <c r="FA49" s="119" t="n"/>
-      <c r="FB49" s="119" t="n"/>
-      <c r="FC49" s="119" t="n"/>
-      <c r="FD49" s="119" t="n"/>
-      <c r="FE49" s="119" t="n"/>
-      <c r="FF49" s="119" t="n"/>
-      <c r="FG49" s="119" t="n"/>
-      <c r="FH49" s="119" t="n"/>
-      <c r="FI49" s="119" t="n"/>
-      <c r="FJ49" s="119" t="n"/>
-      <c r="FK49" s="119" t="n"/>
-      <c r="FL49" s="119" t="n"/>
-      <c r="FM49" s="119" t="n"/>
-      <c r="FN49" s="119" t="n"/>
-      <c r="FO49" s="119" t="n"/>
-      <c r="FP49" s="119" t="n"/>
-      <c r="FQ49" s="119" t="n"/>
-      <c r="FR49" s="119" t="n"/>
-      <c r="FS49" s="119" t="n"/>
-      <c r="FT49" s="119" t="n"/>
-      <c r="FU49" s="119" t="n"/>
-      <c r="FV49" s="119" t="n"/>
-      <c r="FW49" s="119" t="n"/>
-      <c r="FX49" s="119" t="n"/>
-      <c r="FY49" s="119" t="n"/>
-      <c r="FZ49" s="119" t="n"/>
-      <c r="GA49" s="119" t="n"/>
-      <c r="GB49" s="119" t="n"/>
-      <c r="GC49" s="119" t="n"/>
-      <c r="GD49" s="119" t="n"/>
-      <c r="GE49" s="119" t="n"/>
-      <c r="GF49" s="119" t="n"/>
-      <c r="GG49" s="119" t="n"/>
-      <c r="GH49" s="119" t="n"/>
-      <c r="GI49" s="119" t="n"/>
-      <c r="GJ49" s="119" t="n"/>
-      <c r="GK49" s="119" t="n"/>
-      <c r="GL49" s="119" t="n"/>
-      <c r="GM49" s="119" t="n"/>
-      <c r="GN49" s="119" t="n"/>
-      <c r="GO49" s="119" t="n"/>
-      <c r="GP49" s="119" t="n"/>
-      <c r="GQ49" s="119" t="n"/>
-      <c r="GR49" s="119" t="n"/>
-      <c r="GS49" s="119" t="n"/>
-      <c r="GT49" s="119" t="n"/>
-      <c r="GU49" s="119" t="n"/>
-      <c r="GV49" s="119" t="n"/>
-      <c r="GW49" s="119" t="n"/>
-      <c r="GX49" s="119" t="n"/>
-      <c r="GY49" s="119" t="n"/>
-      <c r="GZ49" s="119" t="n"/>
-      <c r="HA49" s="119" t="n"/>
-      <c r="HB49" s="119" t="n"/>
-      <c r="HC49" s="119" t="n"/>
-      <c r="HD49" s="119" t="n"/>
-      <c r="HE49" s="119" t="n"/>
-      <c r="HF49" s="119" t="n"/>
-      <c r="HG49" s="119" t="n"/>
-      <c r="HH49" s="119" t="n"/>
-      <c r="HI49" s="119" t="n"/>
-      <c r="HJ49" s="119" t="n"/>
-      <c r="HK49" s="119" t="n"/>
-      <c r="HL49" s="119" t="n"/>
-      <c r="HM49" s="119" t="n"/>
-      <c r="HN49" s="119" t="n"/>
-      <c r="HO49" s="119" t="n"/>
-      <c r="HP49" s="119" t="n"/>
-      <c r="HQ49" s="119" t="n"/>
-      <c r="HR49" s="119" t="n"/>
-      <c r="HS49" s="119" t="n"/>
-      <c r="HT49" s="119" t="n"/>
-      <c r="HU49" s="119" t="n"/>
-    </row>
-    <row r="50" ht="40.5" customHeight="1">
-      <c r="A50" s="78" t="n"/>
-      <c r="B50" s="142" t="n"/>
-      <c r="C50" s="142" t="n"/>
-      <c r="D50" s="142" t="n"/>
-      <c r="E50" s="142" t="n"/>
-      <c r="F50" s="142" t="n"/>
-      <c r="G50" s="142" t="n"/>
-      <c r="H50" s="142" t="n"/>
-      <c r="I50" s="143" t="n"/>
-      <c r="J50" s="62" t="n"/>
-      <c r="K50" s="62" t="n"/>
-      <c r="L50" s="62" t="n"/>
-      <c r="M50" s="62" t="n"/>
-      <c r="N50" s="62" t="n"/>
-      <c r="O50" s="62" t="n"/>
-      <c r="P50" s="62" t="n"/>
-      <c r="Q50" s="62" t="n"/>
-      <c r="R50" s="62" t="n"/>
-      <c r="S50" s="62" t="n"/>
-      <c r="T50" s="62" t="n"/>
-      <c r="U50" s="62">
+      <c r="A29" s="78" t="n"/>
+      <c r="B29" s="142" t="n"/>
+      <c r="C29" s="142" t="n"/>
+      <c r="D29" s="142" t="n"/>
+      <c r="E29" s="142" t="n"/>
+      <c r="F29" s="142" t="n"/>
+      <c r="G29" s="142" t="n"/>
+      <c r="H29" s="142" t="n"/>
+      <c r="I29" s="143" t="n"/>
+      <c r="J29" s="62" t="n"/>
+      <c r="K29" s="62" t="n"/>
+      <c r="L29" s="62" t="n"/>
+      <c r="M29" s="62" t="n"/>
+      <c r="N29" s="62" t="n"/>
+      <c r="O29" s="62" t="n"/>
+      <c r="P29" s="62" t="n"/>
+      <c r="Q29" s="62" t="n"/>
+      <c r="R29" s="62" t="n"/>
+      <c r="S29" s="62" t="n"/>
+      <c r="T29" s="62" t="n"/>
+      <c r="U29" s="62">
         <f>SUM(U13:U49)</f>
         <v/>
       </c>
-      <c r="V50" s="62">
+      <c r="V29" s="62">
         <f>SUM(V13:V49)</f>
         <v/>
       </c>
-      <c r="W50" s="62">
+      <c r="W29" s="62">
         <f>SUM(W13:W49)</f>
         <v/>
       </c>
-      <c r="X50" s="62">
+      <c r="X29" s="62">
         <f>SUM(X13:X29)</f>
         <v/>
       </c>
-      <c r="Y50" s="62">
+      <c r="Y29" s="62">
         <f>SUM(Y13:Y49)</f>
         <v/>
       </c>
-      <c r="Z50" s="62">
+      <c r="Z29" s="62">
         <f>SUM(Z13:Z49)</f>
         <v/>
       </c>
-      <c r="AA50" s="62">
+      <c r="AA29" s="62">
         <f>SUM(AA13:AA49)</f>
         <v/>
       </c>
-      <c r="AB50" s="61">
+      <c r="AB29" s="61">
         <f>SUM(AB13:AB49)</f>
         <v/>
       </c>
-      <c r="AC50" s="36" t="n"/>
-    </row>
-    <row r="51" ht="40.5" customHeight="1">
-      <c r="A51" s="80" t="n"/>
-      <c r="B51" s="151" t="n"/>
-      <c r="C51" s="151" t="n"/>
-      <c r="D51" s="151" t="n"/>
-      <c r="E51" s="151" t="n"/>
-      <c r="F51" s="151" t="n"/>
-      <c r="G51" s="151" t="n"/>
-      <c r="H51" s="151" t="n"/>
-      <c r="I51" s="152" t="n"/>
-      <c r="J51" s="37" t="n"/>
-      <c r="K51" s="37" t="n"/>
-      <c r="L51" s="37" t="n"/>
-      <c r="M51" s="37" t="n"/>
-      <c r="N51" s="37" t="n"/>
-      <c r="O51" s="37" t="n"/>
-      <c r="P51" s="37" t="n"/>
-      <c r="Q51" s="37" t="n"/>
-      <c r="R51" s="37" t="n"/>
-      <c r="S51" s="37" t="n"/>
-      <c r="T51" s="37" t="n"/>
-      <c r="U51" s="37" t="n">
+      <c r="AC29" s="36" t="n"/>
+    </row>
+    <row r="30" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A30" s="80" t="n"/>
+      <c r="B30" s="151" t="n"/>
+      <c r="C30" s="151" t="n"/>
+      <c r="D30" s="151" t="n"/>
+      <c r="E30" s="151" t="n"/>
+      <c r="F30" s="151" t="n"/>
+      <c r="G30" s="151" t="n"/>
+      <c r="H30" s="151" t="n"/>
+      <c r="I30" s="152" t="n"/>
+      <c r="J30" s="37" t="n"/>
+      <c r="K30" s="37" t="n"/>
+      <c r="L30" s="37" t="n"/>
+      <c r="M30" s="37" t="n"/>
+      <c r="N30" s="37" t="n"/>
+      <c r="O30" s="37" t="n"/>
+      <c r="P30" s="37" t="n"/>
+      <c r="Q30" s="37" t="n"/>
+      <c r="R30" s="37" t="n"/>
+      <c r="S30" s="37" t="n"/>
+      <c r="T30" s="37" t="n"/>
+      <c r="U30" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="37" t="n">
+      <c r="V30" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="W51" s="37" t="n">
+      <c r="W30" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="X51" s="37" t="n">
+      <c r="X30" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="Y51" s="37" t="n">
+      <c r="Y30" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="37" t="n">
+      <c r="Z30" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="AA51" s="37" t="n">
+      <c r="AA30" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="AB51" s="38" t="n">
+      <c r="AB30" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="AC51" s="39" t="n"/>
-    </row>
-    <row r="52" ht="40.5" customHeight="1" thickBot="1">
-      <c r="A52" s="91" t="n"/>
-      <c r="B52" s="153" t="n"/>
-      <c r="C52" s="153" t="n"/>
-      <c r="D52" s="153" t="n"/>
-      <c r="E52" s="153" t="n"/>
-      <c r="F52" s="153" t="n"/>
-      <c r="G52" s="153" t="n"/>
-      <c r="H52" s="153" t="n"/>
-      <c r="I52" s="154" t="n"/>
-      <c r="J52" s="40" t="n"/>
-      <c r="K52" s="40" t="n"/>
-      <c r="L52" s="40" t="n"/>
-      <c r="M52" s="40" t="n"/>
-      <c r="N52" s="40" t="n"/>
-      <c r="O52" s="40" t="n"/>
-      <c r="P52" s="40" t="n"/>
-      <c r="Q52" s="40" t="n"/>
-      <c r="R52" s="40" t="n"/>
-      <c r="S52" s="40" t="n"/>
-      <c r="T52" s="40" t="n"/>
-      <c r="U52" s="40">
+      <c r="AC30" s="39" t="n"/>
+    </row>
+    <row r="31" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A31" s="91" t="n"/>
+      <c r="B31" s="153" t="n"/>
+      <c r="C31" s="153" t="n"/>
+      <c r="D31" s="153" t="n"/>
+      <c r="E31" s="153" t="n"/>
+      <c r="F31" s="153" t="n"/>
+      <c r="G31" s="153" t="n"/>
+      <c r="H31" s="153" t="n"/>
+      <c r="I31" s="154" t="n"/>
+      <c r="J31" s="40" t="n"/>
+      <c r="K31" s="40" t="n"/>
+      <c r="L31" s="40" t="n"/>
+      <c r="M31" s="40" t="n"/>
+      <c r="N31" s="40" t="n"/>
+      <c r="O31" s="40" t="n"/>
+      <c r="P31" s="40" t="n"/>
+      <c r="Q31" s="40" t="n"/>
+      <c r="R31" s="40" t="n"/>
+      <c r="S31" s="40" t="n"/>
+      <c r="T31" s="40" t="n"/>
+      <c r="U31" s="40">
         <f>SUM(U50:U51)</f>
         <v/>
       </c>
-      <c r="V52" s="40">
+      <c r="V31" s="40">
         <f>SUM(V50:V51)</f>
         <v/>
       </c>
-      <c r="W52" s="40">
+      <c r="W31" s="40">
         <f>SUM(W50:W51)</f>
         <v/>
       </c>
-      <c r="X52" s="40">
+      <c r="X31" s="40">
         <f>SUM(X50:X51)</f>
         <v/>
       </c>
-      <c r="Y52" s="40">
+      <c r="Y31" s="40">
         <f>SUM(Y50:Y51)</f>
         <v/>
       </c>
-      <c r="Z52" s="40">
+      <c r="Z31" s="40">
         <f>SUM(Z50:Z51)</f>
         <v/>
       </c>
-      <c r="AA52" s="40">
+      <c r="AA31" s="40">
         <f>SUM(AA50:AA51)</f>
         <v/>
       </c>
-      <c r="AB52" s="41">
+      <c r="AB31" s="41">
         <f>SUM(AB50:AB51)</f>
         <v/>
       </c>
-      <c r="AC52" s="36" t="n"/>
+      <c r="AC31" s="36" t="n"/>
+    </row>
+    <row r="32" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A32" s="27" t="n"/>
+      <c r="B32" s="27" t="n"/>
+      <c r="C32" s="34" t="n"/>
+      <c r="D32" s="34" t="n"/>
+      <c r="E32" s="30" t="n"/>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="27" t="n"/>
+      <c r="H32" s="27" t="n"/>
+      <c r="I32" s="27" t="n"/>
+      <c r="J32" s="27" t="n"/>
+      <c r="K32" s="31" t="n"/>
+      <c r="L32" s="31" t="n"/>
+      <c r="M32" s="31" t="n"/>
+      <c r="N32" s="27" t="n"/>
+      <c r="O32" s="27" t="n"/>
+      <c r="P32" s="27" t="n"/>
+      <c r="Q32" s="27" t="n"/>
+      <c r="R32" s="27" t="n"/>
+      <c r="S32" s="27" t="n"/>
+      <c r="T32" s="27" t="n"/>
+      <c r="U32" s="27" t="n"/>
+      <c r="V32" s="27" t="n"/>
+      <c r="W32" s="27" t="n"/>
+      <c r="X32" s="27" t="n"/>
+      <c r="Y32" s="27" t="n"/>
+      <c r="Z32" s="27" t="n"/>
+      <c r="AA32" s="27" t="n"/>
+      <c r="AB32" s="27" t="n"/>
+      <c r="AC32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="52" customFormat="1" customHeight="1" s="120" thickBot="1">
+      <c r="A33" s="43" t="n"/>
+      <c r="B33" s="155" t="n"/>
+      <c r="C33" s="43" t="n"/>
+      <c r="D33" s="45" t="n"/>
+      <c r="E33" s="46" t="n"/>
+      <c r="F33" s="47" t="n"/>
+      <c r="G33" s="48" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="50" t="n"/>
+      <c r="J33" s="51" t="n"/>
+      <c r="K33" s="52" t="n"/>
+      <c r="L33" s="26" t="n"/>
+      <c r="M33" s="52" t="n"/>
+      <c r="N33" s="52" t="n"/>
+      <c r="O33" s="52" t="n"/>
+      <c r="P33" s="52" t="n"/>
+      <c r="Q33" s="52" t="n"/>
+      <c r="R33" s="52" t="n"/>
+      <c r="S33" s="52" t="n"/>
+      <c r="T33" s="52" t="n"/>
+      <c r="U33" s="52" t="n"/>
+      <c r="V33" s="52" t="n"/>
+      <c r="W33" s="52" t="n"/>
+      <c r="X33" s="43" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ 5P VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="Y33" s="52" t="n"/>
+      <c r="Z33" s="52" t="n"/>
+      <c r="AA33" s="52" t="n"/>
+      <c r="AB33" s="52" t="n"/>
+      <c r="AC33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A34" s="52" t="n"/>
+      <c r="B34" s="156" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="45" t="n"/>
+      <c r="E34" s="46" t="n"/>
+      <c r="F34" s="47" t="n"/>
+      <c r="G34" s="48" t="n"/>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="45" t="n"/>
+      <c r="J34" s="51" t="n"/>
+      <c r="K34" s="52" t="n"/>
+      <c r="L34" s="52" t="n"/>
+      <c r="M34" s="52" t="n"/>
+      <c r="N34" s="52" t="n"/>
+      <c r="O34" s="52" t="n"/>
+      <c r="P34" s="52" t="n"/>
+      <c r="Q34" s="52" t="n"/>
+      <c r="R34" s="52" t="n"/>
+      <c r="S34" s="52" t="n"/>
+      <c r="T34" s="52" t="n"/>
+      <c r="U34" s="52" t="n"/>
+      <c r="V34" s="52" t="n"/>
+      <c r="W34" s="52" t="n"/>
+      <c r="X34" s="52" t="n"/>
+      <c r="Y34" s="52" t="n"/>
+      <c r="Z34" s="52" t="n"/>
+      <c r="AA34" s="52" t="n"/>
+      <c r="AB34" s="52" t="n"/>
+      <c r="AC34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A35" s="52" t="n"/>
+      <c r="B35" s="156" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="45" t="n"/>
+      <c r="E35" s="46" t="n"/>
+      <c r="F35" s="47" t="n"/>
+      <c r="G35" s="48" t="n"/>
+      <c r="H35" s="49" t="n"/>
+      <c r="I35" s="45" t="n"/>
+      <c r="J35" s="51" t="n"/>
+      <c r="K35" s="52" t="n"/>
+      <c r="L35" s="52" t="n"/>
+      <c r="M35" s="52" t="n"/>
+      <c r="N35" s="52" t="n"/>
+      <c r="O35" s="52" t="n"/>
+      <c r="P35" s="52" t="n"/>
+      <c r="Q35" s="52" t="n"/>
+      <c r="R35" s="52" t="n"/>
+      <c r="S35" s="52" t="n"/>
+      <c r="T35" s="52" t="n"/>
+      <c r="U35" s="52" t="n"/>
+      <c r="V35" s="52" t="n"/>
+      <c r="W35" s="52" t="n"/>
+      <c r="X35" s="52" t="n"/>
+      <c r="Y35" s="52" t="n"/>
+      <c r="Z35" s="52" t="n"/>
+      <c r="AA35" s="52" t="n"/>
+      <c r="AB35" s="52" t="n"/>
+      <c r="AC35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A36" s="52" t="n"/>
+      <c r="B36" s="156" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="46" t="n"/>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="48" t="n"/>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="45" t="n"/>
+      <c r="J36" s="51" t="n"/>
+      <c r="K36" s="52" t="n"/>
+      <c r="L36" s="52" t="n"/>
+      <c r="M36" s="52" t="n"/>
+      <c r="N36" s="52" t="n"/>
+      <c r="O36" s="52" t="n"/>
+      <c r="P36" s="52" t="n"/>
+      <c r="Q36" s="52" t="n"/>
+      <c r="R36" s="52" t="n"/>
+      <c r="S36" s="52" t="n"/>
+      <c r="T36" s="52" t="n"/>
+      <c r="U36" s="52" t="n"/>
+      <c r="V36" s="52" t="n"/>
+      <c r="W36" s="52" t="n"/>
+      <c r="X36" s="52" t="n"/>
+      <c r="Y36" s="52" t="n"/>
+      <c r="Z36" s="52" t="n"/>
+      <c r="AA36" s="52" t="n"/>
+      <c r="AB36" s="52" t="n"/>
+      <c r="AC36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A37" s="52" t="n"/>
+      <c r="B37" s="156" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="45" t="n"/>
+      <c r="E37" s="46" t="n"/>
+      <c r="F37" s="47" t="n"/>
+      <c r="G37" s="48" t="n"/>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="45" t="n"/>
+      <c r="J37" s="51" t="n"/>
+      <c r="K37" s="52" t="n"/>
+      <c r="L37" s="52" t="n"/>
+      <c r="M37" s="52" t="n"/>
+      <c r="N37" s="52" t="n"/>
+      <c r="O37" s="52" t="n"/>
+      <c r="P37" s="52" t="n"/>
+      <c r="Q37" s="52" t="n"/>
+      <c r="R37" s="52" t="n"/>
+      <c r="S37" s="52" t="n"/>
+      <c r="T37" s="52" t="n"/>
+      <c r="U37" s="52" t="n"/>
+      <c r="V37" s="52" t="n"/>
+      <c r="W37" s="52" t="n"/>
+      <c r="X37" s="52" t="n"/>
+      <c r="Y37" s="52" t="n"/>
+      <c r="Z37" s="52" t="n"/>
+      <c r="AA37" s="52" t="n"/>
+      <c r="AB37" s="52" t="n"/>
+      <c r="AC37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A38" s="52" t="n"/>
+      <c r="B38" s="156" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="45" t="n"/>
+      <c r="E38" s="46" t="n"/>
+      <c r="F38" s="47" t="n"/>
+      <c r="G38" s="48" t="n"/>
+      <c r="H38" s="49" t="n"/>
+      <c r="I38" s="45" t="n"/>
+      <c r="J38" s="51" t="n"/>
+      <c r="K38" s="52" t="n"/>
+      <c r="L38" s="52" t="n"/>
+      <c r="M38" s="52" t="n"/>
+      <c r="N38" s="52" t="n"/>
+      <c r="O38" s="52" t="n"/>
+      <c r="P38" s="52" t="n"/>
+      <c r="Q38" s="52" t="n"/>
+      <c r="R38" s="52" t="n"/>
+      <c r="S38" s="52" t="n"/>
+      <c r="T38" s="52" t="n"/>
+      <c r="U38" s="52" t="n"/>
+      <c r="V38" s="52" t="n"/>
+      <c r="W38" s="52" t="n"/>
+      <c r="X38" s="52" t="n"/>
+      <c r="Y38" s="52" t="n"/>
+      <c r="Z38" s="52" t="n"/>
+      <c r="AA38" s="52" t="n"/>
+      <c r="AB38" s="52" t="n"/>
+      <c r="AC38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A39" s="52" t="n"/>
+      <c r="B39" s="156" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="45" t="n"/>
+      <c r="E39" s="46" t="n"/>
+      <c r="F39" s="47" t="n"/>
+      <c r="G39" s="48" t="n"/>
+      <c r="H39" s="49" t="n"/>
+      <c r="I39" s="45" t="n"/>
+      <c r="J39" s="51" t="n"/>
+      <c r="K39" s="52" t="n"/>
+      <c r="L39" s="52" t="n"/>
+      <c r="M39" s="52" t="n"/>
+      <c r="N39" s="52" t="n"/>
+      <c r="O39" s="52" t="n"/>
+      <c r="P39" s="52" t="n"/>
+      <c r="Q39" s="52" t="n"/>
+      <c r="R39" s="52" t="n"/>
+      <c r="S39" s="52" t="n"/>
+      <c r="T39" s="52" t="n"/>
+      <c r="U39" s="52" t="n"/>
+      <c r="V39" s="52" t="n"/>
+      <c r="W39" s="52" t="n"/>
+      <c r="X39" s="52" t="n"/>
+      <c r="Y39" s="52" t="n"/>
+      <c r="Z39" s="52" t="n"/>
+      <c r="AA39" s="52" t="n"/>
+      <c r="AB39" s="52" t="n"/>
+      <c r="AC39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A40" s="52" t="n"/>
+      <c r="B40" s="156" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="45" t="n"/>
+      <c r="E40" s="46" t="n"/>
+      <c r="F40" s="47" t="n"/>
+      <c r="G40" s="48" t="n"/>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="45" t="n"/>
+      <c r="J40" s="51" t="n"/>
+      <c r="K40" s="52" t="n"/>
+      <c r="L40" s="52" t="n"/>
+      <c r="M40" s="52" t="n"/>
+      <c r="N40" s="52" t="n"/>
+      <c r="O40" s="52" t="n"/>
+      <c r="P40" s="52" t="n"/>
+      <c r="Q40" s="52" t="n"/>
+      <c r="R40" s="52" t="n"/>
+      <c r="S40" s="52" t="n"/>
+      <c r="T40" s="52" t="n"/>
+      <c r="U40" s="52" t="n"/>
+      <c r="V40" s="52" t="n"/>
+      <c r="W40" s="52" t="n"/>
+      <c r="X40" s="52" t="n"/>
+      <c r="Y40" s="52" t="n"/>
+      <c r="Z40" s="52" t="n"/>
+      <c r="AA40" s="52" t="n"/>
+      <c r="AB40" s="52" t="n"/>
+      <c r="AC40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A41" s="54" t="n"/>
+      <c r="B41" s="156" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="45" t="n"/>
+      <c r="E41" s="46" t="n"/>
+      <c r="F41" s="47" t="n"/>
+      <c r="G41" s="48" t="n"/>
+      <c r="H41" s="49" t="n"/>
+      <c r="I41" s="45" t="n"/>
+      <c r="J41" s="51" t="n"/>
+      <c r="K41" s="52" t="n"/>
+      <c r="L41" s="52" t="n"/>
+      <c r="M41" s="52" t="n"/>
+      <c r="N41" s="52" t="n"/>
+      <c r="O41" s="52" t="n"/>
+      <c r="P41" s="52" t="n"/>
+      <c r="Q41" s="52" t="n"/>
+      <c r="R41" s="52" t="n"/>
+      <c r="S41" s="52" t="n"/>
+      <c r="T41" s="52" t="n"/>
+      <c r="U41" s="52" t="n"/>
+      <c r="V41" s="52" t="n"/>
+      <c r="W41" s="52" t="n"/>
+      <c r="X41" s="52" t="n"/>
+      <c r="Y41" s="52" t="n"/>
+      <c r="Z41" s="52" t="n"/>
+      <c r="AA41" s="52" t="n"/>
+      <c r="AB41" s="52" t="n"/>
+      <c r="AC41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A42" s="52" t="n"/>
+      <c r="B42" s="156" t="n"/>
+      <c r="C42" s="52" t="n"/>
+      <c r="D42" s="45" t="n"/>
+      <c r="E42" s="46" t="n"/>
+      <c r="F42" s="47" t="n"/>
+      <c r="G42" s="48" t="n"/>
+      <c r="H42" s="49" t="n"/>
+      <c r="I42" s="45" t="n"/>
+      <c r="J42" s="51" t="n"/>
+      <c r="K42" s="52" t="n"/>
+      <c r="L42" s="52" t="n"/>
+      <c r="M42" s="52" t="n"/>
+      <c r="N42" s="52" t="n"/>
+      <c r="O42" s="52" t="n"/>
+      <c r="P42" s="52" t="n"/>
+      <c r="Q42" s="52" t="n"/>
+      <c r="R42" s="52" t="n"/>
+      <c r="S42" s="52" t="n"/>
+      <c r="T42" s="52" t="n"/>
+      <c r="U42" s="52" t="n"/>
+      <c r="V42" s="52" t="n"/>
+      <c r="W42" s="52" t="n"/>
+      <c r="X42" s="52" t="n"/>
+      <c r="Y42" s="52" t="n"/>
+      <c r="Z42" s="52" t="n"/>
+      <c r="AA42" s="52" t="n"/>
+      <c r="AB42" s="52" t="n"/>
+      <c r="AC42" s="52" t="n"/>
+    </row>
+    <row r="43" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A43" s="52" t="n"/>
+      <c r="B43" s="156" t="n"/>
+      <c r="C43" s="52" t="n"/>
+      <c r="D43" s="45" t="n"/>
+      <c r="E43" s="46" t="n"/>
+      <c r="F43" s="47" t="n"/>
+      <c r="G43" s="48" t="n"/>
+      <c r="H43" s="49" t="n"/>
+      <c r="I43" s="45" t="n"/>
+      <c r="J43" s="51" t="n"/>
+      <c r="K43" s="52" t="n"/>
+      <c r="L43" s="52" t="n"/>
+      <c r="M43" s="52" t="n"/>
+      <c r="N43" s="52" t="n"/>
+      <c r="O43" s="52" t="n"/>
+      <c r="P43" s="52" t="n"/>
+      <c r="Q43" s="52" t="n"/>
+      <c r="R43" s="52" t="n"/>
+      <c r="S43" s="52" t="n"/>
+      <c r="T43" s="52" t="n"/>
+      <c r="U43" s="52" t="n"/>
+      <c r="V43" s="52" t="n"/>
+      <c r="W43" s="52" t="n"/>
+      <c r="X43" s="52" t="n"/>
+      <c r="Y43" s="52" t="n"/>
+      <c r="Z43" s="52" t="n"/>
+      <c r="AA43" s="52" t="n"/>
+      <c r="AB43" s="52" t="n"/>
+      <c r="AC43" s="52" t="n"/>
+    </row>
+    <row r="44" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="A44" s="74" t="n"/>
+      <c r="E44" s="46" t="n"/>
+      <c r="F44" s="47" t="n"/>
+      <c r="G44" s="48" t="n"/>
+      <c r="H44" s="49" t="n"/>
+      <c r="I44" s="45" t="n"/>
+      <c r="J44" s="51" t="n"/>
+      <c r="K44" s="52" t="n"/>
+      <c r="L44" s="52" t="n"/>
+      <c r="M44" s="52" t="n"/>
+      <c r="N44" s="52" t="n"/>
+      <c r="O44" s="52" t="n"/>
+      <c r="P44" s="52" t="n"/>
+      <c r="Q44" s="52" t="n"/>
+      <c r="R44" s="52" t="n"/>
+      <c r="S44" s="52" t="n"/>
+      <c r="T44" s="52" t="n"/>
+      <c r="U44" s="52" t="n"/>
+      <c r="V44" s="52" t="n"/>
+      <c r="W44" s="52" t="n"/>
+      <c r="X44" s="52" t="n"/>
+      <c r="Y44" s="52" t="n"/>
+      <c r="Z44" s="52" t="n"/>
+      <c r="AA44" s="52" t="n"/>
+      <c r="AB44" s="52" t="n"/>
+      <c r="AC44" s="52" t="n"/>
+    </row>
+    <row r="45" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="C45" s="15" t="n"/>
+      <c r="D45" s="15" t="n"/>
+      <c r="K45" s="15" t="n"/>
+      <c r="L45" s="15" t="n"/>
+      <c r="M45" s="15" t="n"/>
+      <c r="AC45" s="15" t="n"/>
+    </row>
+    <row r="46" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="K46" s="15" t="n"/>
+      <c r="L46" s="15" t="n"/>
+      <c r="M46" s="15" t="n"/>
+      <c r="AC46" s="15" t="n"/>
+    </row>
+    <row r="47" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+      <c r="K47" s="15" t="n"/>
+      <c r="L47" s="15" t="n"/>
+      <c r="M47" s="15" t="n"/>
+      <c r="AC47" s="15" t="n"/>
+    </row>
+    <row r="48" ht="52" customFormat="1" customHeight="1" s="120">
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="K48" s="15" t="n"/>
+      <c r="L48" s="15" t="n"/>
+      <c r="M48" s="15" t="n"/>
+      <c r="AC48" s="15" t="n"/>
+    </row>
+    <row r="49" ht="52" customFormat="1" customHeight="1" s="120" thickBot="1">
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="15" t="n"/>
+      <c r="K49" s="15" t="n"/>
+      <c r="L49" s="15" t="n"/>
+      <c r="M49" s="15" t="n"/>
+      <c r="AC49" s="15" t="n"/>
+    </row>
+    <row r="50" ht="40.5" customHeight="1">
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="15" t="n"/>
+      <c r="K50" s="15" t="n"/>
+      <c r="L50" s="15" t="n"/>
+      <c r="M50" s="15" t="n"/>
+      <c r="AC50" s="15" t="n"/>
+    </row>
+    <row r="51" ht="40.5" customHeight="1">
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="K51" s="15" t="n"/>
+      <c r="L51" s="15" t="n"/>
+      <c r="M51" s="15" t="n"/>
+      <c r="AC51" s="15" t="n"/>
+    </row>
+    <row r="52" ht="40.5" customHeight="1" thickBot="1">
+      <c r="C52" s="15" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="K52" s="15" t="n"/>
+      <c r="L52" s="15" t="n"/>
+      <c r="M52" s="15" t="n"/>
+      <c r="AC52" s="15" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="27" t="n"/>
-      <c r="B53" s="27" t="n"/>
-      <c r="C53" s="34" t="n"/>
-      <c r="D53" s="34" t="n"/>
-      <c r="E53" s="30" t="n"/>
-      <c r="F53" s="27" t="n"/>
-      <c r="G53" s="27" t="n"/>
-      <c r="H53" s="27" t="n"/>
-      <c r="I53" s="27" t="n"/>
-      <c r="J53" s="27" t="n"/>
-      <c r="K53" s="31" t="n"/>
-      <c r="L53" s="31" t="n"/>
-      <c r="M53" s="31" t="n"/>
-      <c r="N53" s="27" t="n"/>
-      <c r="O53" s="27" t="n"/>
-      <c r="P53" s="27" t="n"/>
-      <c r="Q53" s="27" t="n"/>
-      <c r="R53" s="27" t="n"/>
-      <c r="S53" s="27" t="n"/>
-      <c r="T53" s="27" t="n"/>
-      <c r="U53" s="27" t="n"/>
-      <c r="V53" s="27" t="n"/>
-      <c r="W53" s="27" t="n"/>
-      <c r="X53" s="27" t="n"/>
-      <c r="Y53" s="27" t="n"/>
-      <c r="Z53" s="27" t="n"/>
-      <c r="AA53" s="27" t="n"/>
-      <c r="AB53" s="27" t="n"/>
-      <c r="AC53" s="42" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="K53" s="15" t="n"/>
+      <c r="L53" s="15" t="n"/>
+      <c r="M53" s="15" t="n"/>
+      <c r="AC53" s="15" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="43" t="n"/>
-      <c r="B54" s="155" t="n"/>
-      <c r="C54" s="43" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="46" t="n"/>
-      <c r="F54" s="47" t="n"/>
-      <c r="G54" s="48" t="n"/>
-      <c r="H54" s="49" t="n"/>
-      <c r="I54" s="50" t="n"/>
-      <c r="J54" s="51" t="n"/>
-      <c r="K54" s="52" t="n"/>
-      <c r="L54" s="26" t="n"/>
-      <c r="M54" s="52" t="n"/>
-      <c r="N54" s="52" t="n"/>
-      <c r="O54" s="52" t="n"/>
-      <c r="P54" s="52" t="n"/>
-      <c r="Q54" s="52" t="n"/>
-      <c r="R54" s="52" t="n"/>
-      <c r="S54" s="52" t="n"/>
-      <c r="T54" s="52" t="n"/>
-      <c r="U54" s="52" t="n"/>
-      <c r="V54" s="52" t="n"/>
-      <c r="W54" s="52" t="n"/>
-      <c r="X54" s="43" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ 5P VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="Y54" s="52" t="n"/>
-      <c r="Z54" s="52" t="n"/>
-      <c r="AA54" s="52" t="n"/>
-      <c r="AB54" s="52" t="n"/>
-      <c r="AC54" s="52" t="n"/>
+      <c r="C54" s="15" t="n"/>
+      <c r="D54" s="15" t="n"/>
+      <c r="K54" s="15" t="n"/>
+      <c r="L54" s="15" t="n"/>
+      <c r="M54" s="15" t="n"/>
+      <c r="AC54" s="15" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="52" t="n"/>
-      <c r="B55" s="156" t="n"/>
-      <c r="C55" s="52" t="n"/>
-      <c r="D55" s="45" t="n"/>
-      <c r="E55" s="46" t="n"/>
-      <c r="F55" s="47" t="n"/>
-      <c r="G55" s="48" t="n"/>
-      <c r="H55" s="49" t="n"/>
-      <c r="I55" s="45" t="n"/>
-      <c r="J55" s="51" t="n"/>
-      <c r="K55" s="52" t="n"/>
-      <c r="L55" s="52" t="n"/>
-      <c r="M55" s="52" t="n"/>
-      <c r="N55" s="52" t="n"/>
-      <c r="O55" s="52" t="n"/>
-      <c r="P55" s="52" t="n"/>
-      <c r="Q55" s="52" t="n"/>
-      <c r="R55" s="52" t="n"/>
-      <c r="S55" s="52" t="n"/>
-      <c r="T55" s="52" t="n"/>
-      <c r="U55" s="52" t="n"/>
-      <c r="V55" s="52" t="n"/>
-      <c r="W55" s="52" t="n"/>
-      <c r="X55" s="52" t="n"/>
-      <c r="Y55" s="52" t="n"/>
-      <c r="Z55" s="52" t="n"/>
-      <c r="AA55" s="52" t="n"/>
-      <c r="AB55" s="52" t="n"/>
-      <c r="AC55" s="52" t="n"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="K55" s="15" t="n"/>
+      <c r="L55" s="15" t="n"/>
+      <c r="M55" s="15" t="n"/>
+      <c r="AC55" s="15" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="52" t="n"/>
-      <c r="B56" s="156" t="n"/>
-      <c r="C56" s="52" t="n"/>
-      <c r="D56" s="45" t="n"/>
-      <c r="E56" s="46" t="n"/>
-      <c r="F56" s="47" t="n"/>
-      <c r="G56" s="48" t="n"/>
-      <c r="H56" s="49" t="n"/>
-      <c r="I56" s="45" t="n"/>
-      <c r="J56" s="51" t="n"/>
-      <c r="K56" s="52" t="n"/>
-      <c r="L56" s="52" t="n"/>
-      <c r="M56" s="52" t="n"/>
-      <c r="N56" s="52" t="n"/>
-      <c r="O56" s="52" t="n"/>
-      <c r="P56" s="52" t="n"/>
-      <c r="Q56" s="52" t="n"/>
-      <c r="R56" s="52" t="n"/>
-      <c r="S56" s="52" t="n"/>
-      <c r="T56" s="52" t="n"/>
-      <c r="U56" s="52" t="n"/>
-      <c r="V56" s="52" t="n"/>
-      <c r="W56" s="52" t="n"/>
-      <c r="X56" s="52" t="n"/>
-      <c r="Y56" s="52" t="n"/>
-      <c r="Z56" s="52" t="n"/>
-      <c r="AA56" s="52" t="n"/>
-      <c r="AB56" s="52" t="n"/>
-      <c r="AC56" s="52" t="n"/>
+      <c r="C56" s="15" t="n"/>
+      <c r="D56" s="15" t="n"/>
+      <c r="K56" s="15" t="n"/>
+      <c r="L56" s="15" t="n"/>
+      <c r="M56" s="15" t="n"/>
+      <c r="AC56" s="15" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="52" t="n"/>
-      <c r="B57" s="156" t="n"/>
-      <c r="C57" s="52" t="n"/>
-      <c r="D57" s="45" t="n"/>
-      <c r="E57" s="46" t="n"/>
-      <c r="F57" s="47" t="n"/>
-      <c r="G57" s="48" t="n"/>
-      <c r="H57" s="49" t="n"/>
-      <c r="I57" s="45" t="n"/>
-      <c r="J57" s="51" t="n"/>
-      <c r="K57" s="52" t="n"/>
-      <c r="L57" s="52" t="n"/>
-      <c r="M57" s="52" t="n"/>
-      <c r="N57" s="52" t="n"/>
-      <c r="O57" s="52" t="n"/>
-      <c r="P57" s="52" t="n"/>
-      <c r="Q57" s="52" t="n"/>
-      <c r="R57" s="52" t="n"/>
-      <c r="S57" s="52" t="n"/>
-      <c r="T57" s="52" t="n"/>
-      <c r="U57" s="52" t="n"/>
-      <c r="V57" s="52" t="n"/>
-      <c r="W57" s="52" t="n"/>
-      <c r="X57" s="52" t="n"/>
-      <c r="Y57" s="52" t="n"/>
-      <c r="Z57" s="52" t="n"/>
-      <c r="AA57" s="52" t="n"/>
-      <c r="AB57" s="52" t="n"/>
-      <c r="AC57" s="52" t="n"/>
+      <c r="C57" s="15" t="n"/>
+      <c r="D57" s="15" t="n"/>
+      <c r="K57" s="15" t="n"/>
+      <c r="L57" s="15" t="n"/>
+      <c r="M57" s="15" t="n"/>
+      <c r="AC57" s="15" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="52" t="n"/>
-      <c r="B58" s="156" t="n"/>
-      <c r="C58" s="52" t="n"/>
-      <c r="D58" s="45" t="n"/>
-      <c r="E58" s="46" t="n"/>
-      <c r="F58" s="47" t="n"/>
-      <c r="G58" s="48" t="n"/>
-      <c r="H58" s="49" t="n"/>
-      <c r="I58" s="45" t="n"/>
-      <c r="J58" s="51" t="n"/>
-      <c r="K58" s="52" t="n"/>
-      <c r="L58" s="52" t="n"/>
-      <c r="M58" s="52" t="n"/>
-      <c r="N58" s="52" t="n"/>
-      <c r="O58" s="52" t="n"/>
-      <c r="P58" s="52" t="n"/>
-      <c r="Q58" s="52" t="n"/>
-      <c r="R58" s="52" t="n"/>
-      <c r="S58" s="52" t="n"/>
-      <c r="T58" s="52" t="n"/>
-      <c r="U58" s="52" t="n"/>
-      <c r="V58" s="52" t="n"/>
-      <c r="W58" s="52" t="n"/>
-      <c r="X58" s="52" t="n"/>
-      <c r="Y58" s="52" t="n"/>
-      <c r="Z58" s="52" t="n"/>
-      <c r="AA58" s="52" t="n"/>
-      <c r="AB58" s="52" t="n"/>
-      <c r="AC58" s="52" t="n"/>
+      <c r="C58" s="15" t="n"/>
+      <c r="D58" s="15" t="n"/>
+      <c r="K58" s="15" t="n"/>
+      <c r="L58" s="15" t="n"/>
+      <c r="M58" s="15" t="n"/>
+      <c r="AC58" s="15" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="52" t="n"/>
-      <c r="B59" s="156" t="n"/>
-      <c r="C59" s="52" t="n"/>
-      <c r="D59" s="45" t="n"/>
-      <c r="E59" s="46" t="n"/>
-      <c r="F59" s="47" t="n"/>
-      <c r="G59" s="48" t="n"/>
-      <c r="H59" s="49" t="n"/>
-      <c r="I59" s="45" t="n"/>
-      <c r="J59" s="51" t="n"/>
-      <c r="K59" s="52" t="n"/>
-      <c r="L59" s="52" t="n"/>
-      <c r="M59" s="52" t="n"/>
-      <c r="N59" s="52" t="n"/>
-      <c r="O59" s="52" t="n"/>
-      <c r="P59" s="52" t="n"/>
-      <c r="Q59" s="52" t="n"/>
-      <c r="R59" s="52" t="n"/>
-      <c r="S59" s="52" t="n"/>
-      <c r="T59" s="52" t="n"/>
-      <c r="U59" s="52" t="n"/>
-      <c r="V59" s="52" t="n"/>
-      <c r="W59" s="52" t="n"/>
-      <c r="X59" s="52" t="n"/>
-      <c r="Y59" s="52" t="n"/>
-      <c r="Z59" s="52" t="n"/>
-      <c r="AA59" s="52" t="n"/>
-      <c r="AB59" s="52" t="n"/>
-      <c r="AC59" s="52" t="n"/>
+      <c r="C59" s="15" t="n"/>
+      <c r="D59" s="15" t="n"/>
+      <c r="K59" s="15" t="n"/>
+      <c r="L59" s="15" t="n"/>
+      <c r="M59" s="15" t="n"/>
+      <c r="AC59" s="15" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="52" t="n"/>
-      <c r="B60" s="156" t="n"/>
-      <c r="C60" s="52" t="n"/>
-      <c r="D60" s="45" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="47" t="n"/>
-      <c r="G60" s="48" t="n"/>
-      <c r="H60" s="49" t="n"/>
-      <c r="I60" s="45" t="n"/>
-      <c r="J60" s="51" t="n"/>
-      <c r="K60" s="52" t="n"/>
-      <c r="L60" s="52" t="n"/>
-      <c r="M60" s="52" t="n"/>
-      <c r="N60" s="52" t="n"/>
-      <c r="O60" s="52" t="n"/>
-      <c r="P60" s="52" t="n"/>
-      <c r="Q60" s="52" t="n"/>
-      <c r="R60" s="52" t="n"/>
-      <c r="S60" s="52" t="n"/>
-      <c r="T60" s="52" t="n"/>
-      <c r="U60" s="52" t="n"/>
-      <c r="V60" s="52" t="n"/>
-      <c r="W60" s="52" t="n"/>
-      <c r="X60" s="52" t="n"/>
-      <c r="Y60" s="52" t="n"/>
-      <c r="Z60" s="52" t="n"/>
-      <c r="AA60" s="52" t="n"/>
-      <c r="AB60" s="52" t="n"/>
-      <c r="AC60" s="52" t="n"/>
+      <c r="E60" s="24" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="52" t="n"/>
-      <c r="B61" s="156" t="n"/>
-      <c r="C61" s="52" t="n"/>
-      <c r="D61" s="45" t="n"/>
-      <c r="E61" s="46" t="n"/>
-      <c r="F61" s="47" t="n"/>
-      <c r="G61" s="48" t="n"/>
-      <c r="H61" s="49" t="n"/>
-      <c r="I61" s="45" t="n"/>
-      <c r="J61" s="51" t="n"/>
-      <c r="K61" s="52" t="n"/>
-      <c r="L61" s="52" t="n"/>
-      <c r="M61" s="52" t="n"/>
-      <c r="N61" s="52" t="n"/>
-      <c r="O61" s="52" t="n"/>
-      <c r="P61" s="52" t="n"/>
-      <c r="Q61" s="52" t="n"/>
-      <c r="R61" s="52" t="n"/>
-      <c r="S61" s="52" t="n"/>
-      <c r="T61" s="52" t="n"/>
-      <c r="U61" s="52" t="n"/>
-      <c r="V61" s="52" t="n"/>
-      <c r="W61" s="52" t="n"/>
-      <c r="X61" s="52" t="n"/>
-      <c r="Y61" s="52" t="n"/>
-      <c r="Z61" s="52" t="n"/>
-      <c r="AA61" s="52" t="n"/>
-      <c r="AB61" s="52" t="n"/>
-      <c r="AC61" s="52" t="n"/>
+      <c r="E61" s="24" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="54" t="n"/>
-      <c r="B62" s="156" t="n"/>
-      <c r="C62" s="52" t="n"/>
-      <c r="D62" s="45" t="n"/>
-      <c r="E62" s="46" t="n"/>
-      <c r="F62" s="47" t="n"/>
-      <c r="G62" s="48" t="n"/>
-      <c r="H62" s="49" t="n"/>
-      <c r="I62" s="45" t="n"/>
-      <c r="J62" s="51" t="n"/>
-      <c r="K62" s="52" t="n"/>
-      <c r="L62" s="52" t="n"/>
-      <c r="M62" s="52" t="n"/>
-      <c r="N62" s="52" t="n"/>
-      <c r="O62" s="52" t="n"/>
-      <c r="P62" s="52" t="n"/>
-      <c r="Q62" s="52" t="n"/>
-      <c r="R62" s="52" t="n"/>
-      <c r="S62" s="52" t="n"/>
-      <c r="T62" s="52" t="n"/>
-      <c r="U62" s="52" t="n"/>
-      <c r="V62" s="52" t="n"/>
-      <c r="W62" s="52" t="n"/>
-      <c r="X62" s="52" t="n"/>
-      <c r="Y62" s="52" t="n"/>
-      <c r="Z62" s="52" t="n"/>
-      <c r="AA62" s="52" t="n"/>
-      <c r="AB62" s="52" t="n"/>
-      <c r="AC62" s="52" t="n"/>
+      <c r="E62" s="24" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="52" t="n"/>
-      <c r="B63" s="156" t="n"/>
-      <c r="C63" s="52" t="n"/>
-      <c r="D63" s="45" t="n"/>
-      <c r="E63" s="46" t="n"/>
-      <c r="F63" s="47" t="n"/>
-      <c r="G63" s="48" t="n"/>
-      <c r="H63" s="49" t="n"/>
-      <c r="I63" s="45" t="n"/>
-      <c r="J63" s="51" t="n"/>
-      <c r="K63" s="52" t="n"/>
-      <c r="L63" s="52" t="n"/>
-      <c r="M63" s="52" t="n"/>
-      <c r="N63" s="52" t="n"/>
-      <c r="O63" s="52" t="n"/>
-      <c r="P63" s="52" t="n"/>
-      <c r="Q63" s="52" t="n"/>
-      <c r="R63" s="52" t="n"/>
-      <c r="S63" s="52" t="n"/>
-      <c r="T63" s="52" t="n"/>
-      <c r="U63" s="52" t="n"/>
-      <c r="V63" s="52" t="n"/>
-      <c r="W63" s="52" t="n"/>
-      <c r="X63" s="52" t="n"/>
-      <c r="Y63" s="52" t="n"/>
-      <c r="Z63" s="52" t="n"/>
-      <c r="AA63" s="52" t="n"/>
-      <c r="AB63" s="52" t="n"/>
-      <c r="AC63" s="52" t="n"/>
+      <c r="E63" s="24" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="52" t="n"/>
-      <c r="B64" s="156" t="n"/>
-      <c r="C64" s="52" t="n"/>
-      <c r="D64" s="45" t="n"/>
-      <c r="E64" s="46" t="n"/>
-      <c r="F64" s="47" t="n"/>
-      <c r="G64" s="48" t="n"/>
-      <c r="H64" s="49" t="n"/>
-      <c r="I64" s="45" t="n"/>
-      <c r="J64" s="51" t="n"/>
-      <c r="K64" s="52" t="n"/>
-      <c r="L64" s="52" t="n"/>
-      <c r="M64" s="52" t="n"/>
-      <c r="N64" s="52" t="n"/>
-      <c r="O64" s="52" t="n"/>
-      <c r="P64" s="52" t="n"/>
-      <c r="Q64" s="52" t="n"/>
-      <c r="R64" s="52" t="n"/>
-      <c r="S64" s="52" t="n"/>
-      <c r="T64" s="52" t="n"/>
-      <c r="U64" s="52" t="n"/>
-      <c r="V64" s="52" t="n"/>
-      <c r="W64" s="52" t="n"/>
-      <c r="X64" s="52" t="n"/>
-      <c r="Y64" s="52" t="n"/>
-      <c r="Z64" s="52" t="n"/>
-      <c r="AA64" s="52" t="n"/>
-      <c r="AB64" s="52" t="n"/>
-      <c r="AC64" s="52" t="n"/>
+      <c r="E64" s="24" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="74" t="n"/>
-      <c r="E65" s="46" t="n"/>
-      <c r="F65" s="47" t="n"/>
-      <c r="G65" s="48" t="n"/>
-      <c r="H65" s="49" t="n"/>
-      <c r="I65" s="45" t="n"/>
-      <c r="J65" s="51" t="n"/>
-      <c r="K65" s="52" t="n"/>
-      <c r="L65" s="52" t="n"/>
-      <c r="M65" s="52" t="n"/>
-      <c r="N65" s="52" t="n"/>
-      <c r="O65" s="52" t="n"/>
-      <c r="P65" s="52" t="n"/>
-      <c r="Q65" s="52" t="n"/>
-      <c r="R65" s="52" t="n"/>
-      <c r="S65" s="52" t="n"/>
-      <c r="T65" s="52" t="n"/>
-      <c r="U65" s="52" t="n"/>
-      <c r="V65" s="52" t="n"/>
-      <c r="W65" s="52" t="n"/>
-      <c r="X65" s="52" t="n"/>
-      <c r="Y65" s="52" t="n"/>
-      <c r="Z65" s="52" t="n"/>
-      <c r="AA65" s="52" t="n"/>
-      <c r="AB65" s="52" t="n"/>
-      <c r="AC65" s="52" t="n"/>
+      <c r="E65" s="24" t="n"/>
     </row>
     <row r="66">
-      <c r="C66" s="15" t="n"/>
-      <c r="D66" s="15" t="n"/>
-      <c r="K66" s="15" t="n"/>
-      <c r="L66" s="15" t="n"/>
-      <c r="M66" s="15" t="n"/>
-      <c r="AC66" s="15" t="n"/>
+      <c r="E66" s="24" t="n"/>
     </row>
     <row r="67">
-      <c r="C67" s="15" t="n"/>
-      <c r="D67" s="15" t="n"/>
-      <c r="K67" s="15" t="n"/>
-      <c r="L67" s="15" t="n"/>
-      <c r="M67" s="15" t="n"/>
-      <c r="AC67" s="15" t="n"/>
+      <c r="E67" s="24" t="n"/>
     </row>
     <row r="68">
-      <c r="C68" s="15" t="n"/>
-      <c r="D68" s="15" t="n"/>
-      <c r="K68" s="15" t="n"/>
-      <c r="L68" s="15" t="n"/>
-      <c r="M68" s="15" t="n"/>
-      <c r="AC68" s="15" t="n"/>
+      <c r="E68" s="24" t="n"/>
     </row>
     <row r="69">
-      <c r="C69" s="15" t="n"/>
-      <c r="D69" s="15" t="n"/>
-      <c r="K69" s="15" t="n"/>
-      <c r="L69" s="15" t="n"/>
-      <c r="M69" s="15" t="n"/>
-      <c r="AC69" s="15" t="n"/>
+      <c r="E69" s="24" t="n"/>
     </row>
     <row r="70">
-      <c r="C70" s="15" t="n"/>
-      <c r="D70" s="15" t="n"/>
-      <c r="K70" s="15" t="n"/>
-      <c r="L70" s="15" t="n"/>
-      <c r="M70" s="15" t="n"/>
-      <c r="AC70" s="15" t="n"/>
+      <c r="E70" s="24" t="n"/>
     </row>
     <row r="71">
-      <c r="C71" s="15" t="n"/>
-      <c r="D71" s="15" t="n"/>
-      <c r="K71" s="15" t="n"/>
-      <c r="L71" s="15" t="n"/>
-      <c r="M71" s="15" t="n"/>
-      <c r="AC71" s="15" t="n"/>
+      <c r="E71" s="24" t="n"/>
     </row>
     <row r="72">
-      <c r="C72" s="15" t="n"/>
-      <c r="D72" s="15" t="n"/>
-      <c r="K72" s="15" t="n"/>
-      <c r="L72" s="15" t="n"/>
-      <c r="M72" s="15" t="n"/>
-      <c r="AC72" s="15" t="n"/>
+      <c r="E72" s="24" t="n"/>
     </row>
     <row r="73">
-      <c r="C73" s="15" t="n"/>
-      <c r="D73" s="15" t="n"/>
-      <c r="K73" s="15" t="n"/>
-      <c r="L73" s="15" t="n"/>
-      <c r="M73" s="15" t="n"/>
-      <c r="AC73" s="15" t="n"/>
+      <c r="E73" s="24" t="n"/>
     </row>
     <row r="74">
-      <c r="C74" s="15" t="n"/>
-      <c r="D74" s="15" t="n"/>
-      <c r="K74" s="15" t="n"/>
-      <c r="L74" s="15" t="n"/>
-      <c r="M74" s="15" t="n"/>
-      <c r="AC74" s="15" t="n"/>
+      <c r="E74" s="24" t="n"/>
     </row>
     <row r="75">
-      <c r="C75" s="15" t="n"/>
-      <c r="D75" s="15" t="n"/>
-      <c r="K75" s="15" t="n"/>
-      <c r="L75" s="15" t="n"/>
-      <c r="M75" s="15" t="n"/>
-      <c r="AC75" s="15" t="n"/>
+      <c r="E75" s="24" t="n"/>
     </row>
     <row r="76">
-      <c r="C76" s="15" t="n"/>
-      <c r="D76" s="15" t="n"/>
-      <c r="K76" s="15" t="n"/>
-      <c r="L76" s="15" t="n"/>
-      <c r="M76" s="15" t="n"/>
-      <c r="AC76" s="15" t="n"/>
+      <c r="E76" s="24" t="n"/>
     </row>
     <row r="77">
-      <c r="C77" s="15" t="n"/>
-      <c r="D77" s="15" t="n"/>
-      <c r="K77" s="15" t="n"/>
-      <c r="L77" s="15" t="n"/>
-      <c r="M77" s="15" t="n"/>
-      <c r="AC77" s="15" t="n"/>
+      <c r="E77" s="24" t="n"/>
     </row>
     <row r="78">
-      <c r="C78" s="15" t="n"/>
-      <c r="D78" s="15" t="n"/>
-      <c r="K78" s="15" t="n"/>
-      <c r="L78" s="15" t="n"/>
-      <c r="M78" s="15" t="n"/>
-      <c r="AC78" s="15" t="n"/>
+      <c r="E78" s="24" t="n"/>
     </row>
     <row r="79">
-      <c r="C79" s="15" t="n"/>
-      <c r="D79" s="15" t="n"/>
-      <c r="K79" s="15" t="n"/>
-      <c r="L79" s="15" t="n"/>
-      <c r="M79" s="15" t="n"/>
-      <c r="AC79" s="15" t="n"/>
+      <c r="E79" s="24" t="n"/>
     </row>
     <row r="80">
-      <c r="C80" s="15" t="n"/>
-      <c r="D80" s="15" t="n"/>
-      <c r="K80" s="15" t="n"/>
-      <c r="L80" s="15" t="n"/>
-      <c r="M80" s="15" t="n"/>
-      <c r="AC80" s="15" t="n"/>
+      <c r="E80" s="24" t="n"/>
     </row>
     <row r="81" customFormat="1" s="15">
       <c r="E81" s="24" t="n"/>
@@ -12316,69 +7380,27 @@
     <row r="203" customFormat="1" s="15">
       <c r="E203" s="24" t="n"/>
     </row>
-    <row r="204" customFormat="1" s="15">
-      <c r="E204" s="24" t="n"/>
-    </row>
-    <row r="205" customFormat="1" s="15">
-      <c r="E205" s="24" t="n"/>
-    </row>
-    <row r="206" customFormat="1" s="15">
-      <c r="E206" s="24" t="n"/>
-    </row>
-    <row r="207" customFormat="1" s="15">
-      <c r="E207" s="24" t="n"/>
-    </row>
-    <row r="208" customFormat="1" s="15">
-      <c r="E208" s="24" t="n"/>
-    </row>
-    <row r="209" customFormat="1" s="15">
-      <c r="E209" s="24" t="n"/>
-    </row>
-    <row r="210" customFormat="1" s="15">
-      <c r="E210" s="24" t="n"/>
-    </row>
-    <row r="211" customFormat="1" s="15">
-      <c r="E211" s="24" t="n"/>
-    </row>
-    <row r="212" customFormat="1" s="15">
-      <c r="E212" s="24" t="n"/>
-    </row>
-    <row r="213" customFormat="1" s="15">
-      <c r="E213" s="24" t="n"/>
-    </row>
-    <row r="214" customFormat="1" s="15">
-      <c r="E214" s="24" t="n"/>
-    </row>
-    <row r="215" customFormat="1" s="15">
-      <c r="E215" s="24" t="n"/>
-    </row>
-    <row r="216" customFormat="1" s="15">
-      <c r="E216" s="24" t="n"/>
-    </row>
-    <row r="217" customFormat="1" s="15">
-      <c r="E217" s="24" t="n"/>
-    </row>
-    <row r="218" customFormat="1" s="15">
-      <c r="E218" s="24" t="n"/>
-    </row>
-    <row r="219" customFormat="1" s="15">
-      <c r="E219" s="24" t="n"/>
-    </row>
-    <row r="220" customFormat="1" s="15">
-      <c r="E220" s="24" t="n"/>
-    </row>
-    <row r="221" customFormat="1" s="15">
-      <c r="E221" s="24" t="n"/>
-    </row>
-    <row r="222" customFormat="1" s="15">
-      <c r="E222" s="24" t="n"/>
-    </row>
-    <row r="223" customFormat="1" s="15">
-      <c r="E223" s="24" t="n"/>
-    </row>
-    <row r="224" customFormat="1" s="15">
-      <c r="E224" s="24" t="n"/>
-    </row>
+    <row r="204" customFormat="1" s="15"/>
+    <row r="205" customFormat="1" s="15"/>
+    <row r="206" customFormat="1" s="15"/>
+    <row r="207" customFormat="1" s="15"/>
+    <row r="208" customFormat="1" s="15"/>
+    <row r="209" customFormat="1" s="15"/>
+    <row r="210" customFormat="1" s="15"/>
+    <row r="211" customFormat="1" s="15"/>
+    <row r="212" customFormat="1" s="15"/>
+    <row r="213" customFormat="1" s="15"/>
+    <row r="214" customFormat="1" s="15"/>
+    <row r="215" customFormat="1" s="15"/>
+    <row r="216" customFormat="1" s="15"/>
+    <row r="217" customFormat="1" s="15"/>
+    <row r="218" customFormat="1" s="15"/>
+    <row r="219" customFormat="1" s="15"/>
+    <row r="220" customFormat="1" s="15"/>
+    <row r="221" customFormat="1" s="15"/>
+    <row r="222" customFormat="1" s="15"/>
+    <row r="223" customFormat="1" s="15"/>
+    <row r="224" customFormat="1" s="15"/>
   </sheetData>
   <autoFilter ref="A12:IJ27"/>
   <mergeCells count="15">
